--- a/dentai-backend/backend-tests/test-report.xlsx
+++ b/dentai-backend/backend-tests/test-report.xlsx
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:44:38 am</v>
+        <v>6/8/2026, 9:58:57 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -638,10 +638,10 @@
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:14:38.800Z</v>
+        <v>2026-08-06T04:28:57.349Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -664,10 +664,10 @@
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -690,10 +690,10 @@
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -716,10 +716,10 @@
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -742,10 +742,10 @@
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -768,10 +768,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -794,10 +794,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -820,10 +820,10 @@
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -846,10 +846,10 @@
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -872,10 +872,10 @@
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -898,10 +898,10 @@
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -924,10 +924,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -950,10 +950,10 @@
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -976,10 +976,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -1002,10 +1002,10 @@
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1028,10 +1028,10 @@
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1054,10 +1054,10 @@
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1080,10 +1080,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1106,10 +1106,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1132,10 +1132,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1158,10 +1158,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1184,10 +1184,10 @@
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1236,10 +1236,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1262,10 +1262,10 @@
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1288,10 +1288,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1314,10 +1314,10 @@
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1340,10 +1340,10 @@
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1366,10 +1366,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1392,10 +1392,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1418,10 +1418,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1444,10 +1444,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1470,10 +1470,10 @@
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1496,10 +1496,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1522,10 +1522,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1548,10 +1548,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1574,10 +1574,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1600,10 +1600,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1629,7 +1629,7 @@
         <v>12</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1652,10 +1652,10 @@
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1678,10 +1678,10 @@
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1704,10 +1704,10 @@
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1733,7 +1733,7 @@
         <v>19</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1756,10 +1756,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1782,10 +1782,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1808,10 +1808,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1834,10 +1834,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1860,10 +1860,10 @@
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1886,10 +1886,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1912,10 +1912,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:14:38.805Z</v>
+        <v>2026-08-06T04:28:57.351Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1938,10 +1938,10 @@
         <v>PASS</v>
       </c>
       <c r="F52">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H52" t="str">
         <v>N/A</v>
@@ -1964,10 +1964,10 @@
         <v>PASS</v>
       </c>
       <c r="F53">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H53" t="str">
         <v>N/A</v>
@@ -1990,10 +1990,10 @@
         <v>PASS</v>
       </c>
       <c r="F54">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G54" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H54" t="str">
         <v>N/A</v>
@@ -2016,10 +2016,10 @@
         <v>PASS</v>
       </c>
       <c r="F55">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G55" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H55" t="str">
         <v>N/A</v>
@@ -2042,10 +2042,10 @@
         <v>PASS</v>
       </c>
       <c r="F56">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H56" t="str">
         <v>N/A</v>
@@ -2068,10 +2068,10 @@
         <v>PASS</v>
       </c>
       <c r="F57">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H57" t="str">
         <v>N/A</v>
@@ -2094,10 +2094,10 @@
         <v>PASS</v>
       </c>
       <c r="F58">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H58" t="str">
         <v>N/A</v>
@@ -2120,10 +2120,10 @@
         <v>PASS</v>
       </c>
       <c r="F59">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H59" t="str">
         <v>N/A</v>
@@ -2146,10 +2146,10 @@
         <v>PASS</v>
       </c>
       <c r="F60">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G60" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H60" t="str">
         <v>N/A</v>
@@ -2172,10 +2172,10 @@
         <v>PASS</v>
       </c>
       <c r="F61">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G61" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H61" t="str">
         <v>N/A</v>
@@ -2198,10 +2198,10 @@
         <v>PASS</v>
       </c>
       <c r="F62">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H62" t="str">
         <v>N/A</v>
@@ -2224,10 +2224,10 @@
         <v>PASS</v>
       </c>
       <c r="F63">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H63" t="str">
         <v>N/A</v>
@@ -2250,10 +2250,10 @@
         <v>PASS</v>
       </c>
       <c r="F64">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G64" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H64" t="str">
         <v>N/A</v>
@@ -2276,10 +2276,10 @@
         <v>PASS</v>
       </c>
       <c r="F65">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G65" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H65" t="str">
         <v>N/A</v>
@@ -2302,10 +2302,10 @@
         <v>PASS</v>
       </c>
       <c r="F66">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G66" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H66" t="str">
         <v>N/A</v>
@@ -2331,7 +2331,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H67" t="str">
         <v>N/A</v>
@@ -2354,10 +2354,10 @@
         <v>PASS</v>
       </c>
       <c r="F68">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G68" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H68" t="str">
         <v>N/A</v>
@@ -2380,10 +2380,10 @@
         <v>PASS</v>
       </c>
       <c r="F69">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H69" t="str">
         <v>N/A</v>
@@ -2409,7 +2409,7 @@
         <v>29</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H70" t="str">
         <v>N/A</v>
@@ -2432,10 +2432,10 @@
         <v>PASS</v>
       </c>
       <c r="F71">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H71" t="str">
         <v>N/A</v>
@@ -2458,10 +2458,10 @@
         <v>PASS</v>
       </c>
       <c r="F72">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G72" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H72" t="str">
         <v>N/A</v>
@@ -2484,10 +2484,10 @@
         <v>PASS</v>
       </c>
       <c r="F73">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H73" t="str">
         <v>N/A</v>
@@ -2510,10 +2510,10 @@
         <v>PASS</v>
       </c>
       <c r="F74">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H74" t="str">
         <v>N/A</v>
@@ -2536,10 +2536,10 @@
         <v>PASS</v>
       </c>
       <c r="F75">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G75" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H75" t="str">
         <v>N/A</v>
@@ -2562,10 +2562,10 @@
         <v>PASS</v>
       </c>
       <c r="F76">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G76" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H76" t="str">
         <v>N/A</v>
@@ -2588,10 +2588,10 @@
         <v>PASS</v>
       </c>
       <c r="F77">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G77" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H77" t="str">
         <v>N/A</v>
@@ -2614,10 +2614,10 @@
         <v>PASS</v>
       </c>
       <c r="F78">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G78" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H78" t="str">
         <v>N/A</v>
@@ -2640,10 +2640,10 @@
         <v>PASS</v>
       </c>
       <c r="F79">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G79" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H79" t="str">
         <v>N/A</v>
@@ -2666,10 +2666,10 @@
         <v>PASS</v>
       </c>
       <c r="F80">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G80" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H80" t="str">
         <v>N/A</v>
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="F81">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G81" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H81" t="str">
         <v>N/A</v>
@@ -2718,10 +2718,10 @@
         <v>PASS</v>
       </c>
       <c r="F82">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G82" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H82" t="str">
         <v>N/A</v>
@@ -2747,7 +2747,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H83" t="str">
         <v>N/A</v>
@@ -2770,10 +2770,10 @@
         <v>PASS</v>
       </c>
       <c r="F84">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G84" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.393Z</v>
       </c>
       <c r="H84" t="str">
         <v>N/A</v>
@@ -2796,10 +2796,10 @@
         <v>PASS</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G85" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H85" t="str">
         <v>N/A</v>
@@ -2822,10 +2822,10 @@
         <v>PASS</v>
       </c>
       <c r="F86">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G86" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H86" t="str">
         <v>N/A</v>
@@ -2848,10 +2848,10 @@
         <v>PASS</v>
       </c>
       <c r="F87">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G87" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H87" t="str">
         <v>N/A</v>
@@ -2874,10 +2874,10 @@
         <v>PASS</v>
       </c>
       <c r="F88">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G88" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H88" t="str">
         <v>N/A</v>
@@ -2900,10 +2900,10 @@
         <v>PASS</v>
       </c>
       <c r="F89">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G89" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H89" t="str">
         <v>N/A</v>
@@ -2926,10 +2926,10 @@
         <v>PASS</v>
       </c>
       <c r="F90">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G90" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H90" t="str">
         <v>N/A</v>
@@ -2952,10 +2952,10 @@
         <v>PASS</v>
       </c>
       <c r="F91">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G91" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H91" t="str">
         <v>N/A</v>
@@ -2978,10 +2978,10 @@
         <v>PASS</v>
       </c>
       <c r="F92">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G92" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H92" t="str">
         <v>N/A</v>
@@ -3004,10 +3004,10 @@
         <v>PASS</v>
       </c>
       <c r="F93">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G93" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H93" t="str">
         <v>N/A</v>
@@ -3030,10 +3030,10 @@
         <v>PASS</v>
       </c>
       <c r="F94">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G94" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H94" t="str">
         <v>N/A</v>
@@ -3056,10 +3056,10 @@
         <v>PASS</v>
       </c>
       <c r="F95">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G95" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H95" t="str">
         <v>N/A</v>
@@ -3082,10 +3082,10 @@
         <v>PASS</v>
       </c>
       <c r="F96">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G96" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H96" t="str">
         <v>N/A</v>
@@ -3111,7 +3111,7 @@
         <v>14</v>
       </c>
       <c r="G97" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H97" t="str">
         <v>N/A</v>
@@ -3134,10 +3134,10 @@
         <v>PASS</v>
       </c>
       <c r="F98">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G98" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H98" t="str">
         <v>N/A</v>
@@ -3160,10 +3160,10 @@
         <v>PASS</v>
       </c>
       <c r="F99">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G99" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H99" t="str">
         <v>N/A</v>
@@ -3186,10 +3186,10 @@
         <v>PASS</v>
       </c>
       <c r="F100">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G100" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H100" t="str">
         <v>N/A</v>
@@ -3212,10 +3212,10 @@
         <v>PASS</v>
       </c>
       <c r="F101">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G101" t="str">
-        <v>2026-08-06T04:14:38.846Z</v>
+        <v>2026-08-06T04:28:57.394Z</v>
       </c>
       <c r="H101" t="str">
         <v>N/A</v>
@@ -3238,10 +3238,10 @@
         <v>PASS</v>
       </c>
       <c r="F102">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G102" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H102" t="str">
         <v>N/A</v>
@@ -3264,10 +3264,10 @@
         <v>PASS</v>
       </c>
       <c r="F103">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G103" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H103" t="str">
         <v>N/A</v>
@@ -3290,10 +3290,10 @@
         <v>PASS</v>
       </c>
       <c r="F104">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G104" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H104" t="str">
         <v>N/A</v>
@@ -3316,10 +3316,10 @@
         <v>PASS</v>
       </c>
       <c r="F105">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G105" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H105" t="str">
         <v>N/A</v>
@@ -3342,10 +3342,10 @@
         <v>PASS</v>
       </c>
       <c r="F106">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G106" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H106" t="str">
         <v>N/A</v>
@@ -3368,10 +3368,10 @@
         <v>PASS</v>
       </c>
       <c r="F107">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G107" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H107" t="str">
         <v>N/A</v>
@@ -3394,10 +3394,10 @@
         <v>PASS</v>
       </c>
       <c r="F108">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G108" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H108" t="str">
         <v>N/A</v>
@@ -3420,10 +3420,10 @@
         <v>PASS</v>
       </c>
       <c r="F109">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G109" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H109" t="str">
         <v>N/A</v>
@@ -3446,10 +3446,10 @@
         <v>PASS</v>
       </c>
       <c r="F110">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G110" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H110" t="str">
         <v>N/A</v>
@@ -3472,10 +3472,10 @@
         <v>PASS</v>
       </c>
       <c r="F111">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G111" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H111" t="str">
         <v>N/A</v>
@@ -3498,10 +3498,10 @@
         <v>PASS</v>
       </c>
       <c r="F112">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G112" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H112" t="str">
         <v>N/A</v>
@@ -3524,10 +3524,10 @@
         <v>PASS</v>
       </c>
       <c r="F113">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G113" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H113" t="str">
         <v>N/A</v>
@@ -3553,7 +3553,7 @@
         <v>18</v>
       </c>
       <c r="G114" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H114" t="str">
         <v>N/A</v>
@@ -3576,10 +3576,10 @@
         <v>PASS</v>
       </c>
       <c r="F115">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G115" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H115" t="str">
         <v>N/A</v>
@@ -3602,10 +3602,10 @@
         <v>PASS</v>
       </c>
       <c r="F116">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G116" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H116" t="str">
         <v>N/A</v>
@@ -3628,10 +3628,10 @@
         <v>PASS</v>
       </c>
       <c r="F117">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G117" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H117" t="str">
         <v>N/A</v>
@@ -3654,10 +3654,10 @@
         <v>PASS</v>
       </c>
       <c r="F118">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G118" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H118" t="str">
         <v>N/A</v>
@@ -3680,10 +3680,10 @@
         <v>PASS</v>
       </c>
       <c r="F119">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G119" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H119" t="str">
         <v>N/A</v>
@@ -3706,10 +3706,10 @@
         <v>PASS</v>
       </c>
       <c r="F120">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G120" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H120" t="str">
         <v>N/A</v>
@@ -3732,10 +3732,10 @@
         <v>PASS</v>
       </c>
       <c r="F121">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G121" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H121" t="str">
         <v>N/A</v>
@@ -3758,10 +3758,10 @@
         <v>PASS</v>
       </c>
       <c r="F122">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G122" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H122" t="str">
         <v>N/A</v>
@@ -3784,10 +3784,10 @@
         <v>PASS</v>
       </c>
       <c r="F123">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G123" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.402Z</v>
       </c>
       <c r="H123" t="str">
         <v>N/A</v>
@@ -3810,10 +3810,10 @@
         <v>PASS</v>
       </c>
       <c r="F124">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G124" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H124" t="str">
         <v>N/A</v>
@@ -3836,10 +3836,10 @@
         <v>PASS</v>
       </c>
       <c r="F125">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G125" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H125" t="str">
         <v>N/A</v>
@@ -3862,10 +3862,10 @@
         <v>PASS</v>
       </c>
       <c r="F126">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G126" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H126" t="str">
         <v>N/A</v>
@@ -3888,10 +3888,10 @@
         <v>PASS</v>
       </c>
       <c r="F127">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G127" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H127" t="str">
         <v>N/A</v>
@@ -3914,10 +3914,10 @@
         <v>PASS</v>
       </c>
       <c r="F128">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G128" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H128" t="str">
         <v>N/A</v>
@@ -3940,10 +3940,10 @@
         <v>PASS</v>
       </c>
       <c r="F129">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G129" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H129" t="str">
         <v>N/A</v>
@@ -3966,10 +3966,10 @@
         <v>PASS</v>
       </c>
       <c r="F130">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G130" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H130" t="str">
         <v>N/A</v>
@@ -3992,10 +3992,10 @@
         <v>PASS</v>
       </c>
       <c r="F131">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G131" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H131" t="str">
         <v>N/A</v>
@@ -4018,10 +4018,10 @@
         <v>PASS</v>
       </c>
       <c r="F132">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G132" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H132" t="str">
         <v>N/A</v>
@@ -4044,10 +4044,10 @@
         <v>PASS</v>
       </c>
       <c r="F133">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G133" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H133" t="str">
         <v>N/A</v>
@@ -4070,10 +4070,10 @@
         <v>PASS</v>
       </c>
       <c r="F134">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G134" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H134" t="str">
         <v>N/A</v>
@@ -4096,10 +4096,10 @@
         <v>PASS</v>
       </c>
       <c r="F135">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G135" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H135" t="str">
         <v>N/A</v>
@@ -4122,10 +4122,10 @@
         <v>PASS</v>
       </c>
       <c r="F136">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G136" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H136" t="str">
         <v>N/A</v>
@@ -4148,10 +4148,10 @@
         <v>PASS</v>
       </c>
       <c r="F137">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G137" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H137" t="str">
         <v>N/A</v>
@@ -4174,10 +4174,10 @@
         <v>PASS</v>
       </c>
       <c r="F138">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G138" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H138" t="str">
         <v>N/A</v>
@@ -4200,10 +4200,10 @@
         <v>PASS</v>
       </c>
       <c r="F139">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G139" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H139" t="str">
         <v>N/A</v>
@@ -4226,10 +4226,10 @@
         <v>PASS</v>
       </c>
       <c r="F140">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G140" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H140" t="str">
         <v>N/A</v>
@@ -4252,10 +4252,10 @@
         <v>PASS</v>
       </c>
       <c r="F141">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G141" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H141" t="str">
         <v>N/A</v>
@@ -4278,10 +4278,10 @@
         <v>PASS</v>
       </c>
       <c r="F142">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G142" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H142" t="str">
         <v>N/A</v>
@@ -4304,10 +4304,10 @@
         <v>PASS</v>
       </c>
       <c r="F143">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G143" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H143" t="str">
         <v>N/A</v>
@@ -4330,10 +4330,10 @@
         <v>PASS</v>
       </c>
       <c r="F144">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G144" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H144" t="str">
         <v>N/A</v>
@@ -4356,10 +4356,10 @@
         <v>PASS</v>
       </c>
       <c r="F145">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G145" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H145" t="str">
         <v>N/A</v>
@@ -4382,10 +4382,10 @@
         <v>PASS</v>
       </c>
       <c r="F146">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G146" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H146" t="str">
         <v>N/A</v>
@@ -4408,10 +4408,10 @@
         <v>PASS</v>
       </c>
       <c r="F147">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G147" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H147" t="str">
         <v>N/A</v>
@@ -4437,7 +4437,7 @@
         <v>20</v>
       </c>
       <c r="G148" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H148" t="str">
         <v>N/A</v>
@@ -4460,10 +4460,10 @@
         <v>PASS</v>
       </c>
       <c r="F149">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G149" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H149" t="str">
         <v>N/A</v>
@@ -4486,10 +4486,10 @@
         <v>PASS</v>
       </c>
       <c r="F150">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G150" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H150" t="str">
         <v>N/A</v>
@@ -4512,10 +4512,10 @@
         <v>PASS</v>
       </c>
       <c r="F151">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G151" t="str">
-        <v>2026-08-06T04:14:38.854Z</v>
+        <v>2026-08-06T04:28:57.403Z</v>
       </c>
       <c r="H151" t="str">
         <v>N/A</v>
@@ -4538,10 +4538,10 @@
         <v>PASS</v>
       </c>
       <c r="F152">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G152" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H152" t="str">
         <v>N/A</v>
@@ -4564,10 +4564,10 @@
         <v>PASS</v>
       </c>
       <c r="F153">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G153" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H153" t="str">
         <v>N/A</v>
@@ -4590,10 +4590,10 @@
         <v>PASS</v>
       </c>
       <c r="F154">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G154" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H154" t="str">
         <v>N/A</v>
@@ -4616,10 +4616,10 @@
         <v>PASS</v>
       </c>
       <c r="F155">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G155" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H155" t="str">
         <v>N/A</v>
@@ -4645,7 +4645,7 @@
         <v>18</v>
       </c>
       <c r="G156" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H156" t="str">
         <v>N/A</v>
@@ -4668,10 +4668,10 @@
         <v>PASS</v>
       </c>
       <c r="F157">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G157" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H157" t="str">
         <v>N/A</v>
@@ -4694,10 +4694,10 @@
         <v>PASS</v>
       </c>
       <c r="F158">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G158" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H158" t="str">
         <v>N/A</v>
@@ -4720,10 +4720,10 @@
         <v>PASS</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G159" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H159" t="str">
         <v>N/A</v>
@@ -4746,10 +4746,10 @@
         <v>PASS</v>
       </c>
       <c r="F160">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G160" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H160" t="str">
         <v>N/A</v>
@@ -4772,10 +4772,10 @@
         <v>PASS</v>
       </c>
       <c r="F161">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G161" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H161" t="str">
         <v>N/A</v>
@@ -4801,7 +4801,7 @@
         <v>29</v>
       </c>
       <c r="G162" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H162" t="str">
         <v>N/A</v>
@@ -4824,10 +4824,10 @@
         <v>PASS</v>
       </c>
       <c r="F163">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G163" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H163" t="str">
         <v>N/A</v>
@@ -4850,10 +4850,10 @@
         <v>PASS</v>
       </c>
       <c r="F164">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G164" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H164" t="str">
         <v>N/A</v>
@@ -4876,10 +4876,10 @@
         <v>PASS</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G165" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H165" t="str">
         <v>N/A</v>
@@ -4902,10 +4902,10 @@
         <v>PASS</v>
       </c>
       <c r="F166">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G166" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H166" t="str">
         <v>N/A</v>
@@ -4928,10 +4928,10 @@
         <v>PASS</v>
       </c>
       <c r="F167">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G167" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H167" t="str">
         <v>N/A</v>
@@ -4954,10 +4954,10 @@
         <v>PASS</v>
       </c>
       <c r="F168">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G168" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H168" t="str">
         <v>N/A</v>
@@ -4980,10 +4980,10 @@
         <v>PASS</v>
       </c>
       <c r="F169">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G169" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H169" t="str">
         <v>N/A</v>
@@ -5006,10 +5006,10 @@
         <v>PASS</v>
       </c>
       <c r="F170">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G170" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H170" t="str">
         <v>N/A</v>
@@ -5032,10 +5032,10 @@
         <v>PASS</v>
       </c>
       <c r="F171">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G171" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H171" t="str">
         <v>N/A</v>
@@ -5058,10 +5058,10 @@
         <v>PASS</v>
       </c>
       <c r="F172">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G172" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H172" t="str">
         <v>N/A</v>
@@ -5084,10 +5084,10 @@
         <v>PASS</v>
       </c>
       <c r="F173">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G173" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H173" t="str">
         <v>N/A</v>
@@ -5110,10 +5110,10 @@
         <v>PASS</v>
       </c>
       <c r="F174">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G174" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H174" t="str">
         <v>N/A</v>
@@ -5136,10 +5136,10 @@
         <v>PASS</v>
       </c>
       <c r="F175">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G175" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H175" t="str">
         <v>N/A</v>
@@ -5162,10 +5162,10 @@
         <v>PASS</v>
       </c>
       <c r="F176">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G176" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H176" t="str">
         <v>N/A</v>
@@ -5188,10 +5188,10 @@
         <v>PASS</v>
       </c>
       <c r="F177">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G177" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H177" t="str">
         <v>N/A</v>
@@ -5217,7 +5217,7 @@
         <v>18</v>
       </c>
       <c r="G178" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H178" t="str">
         <v>N/A</v>
@@ -5240,10 +5240,10 @@
         <v>PASS</v>
       </c>
       <c r="F179">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G179" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H179" t="str">
         <v>N/A</v>
@@ -5266,10 +5266,10 @@
         <v>PASS</v>
       </c>
       <c r="F180">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G180" t="str">
-        <v>2026-08-06T04:14:38.861Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H180" t="str">
         <v>N/A</v>
@@ -5292,10 +5292,10 @@
         <v>PASS</v>
       </c>
       <c r="F181">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G181" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H181" t="str">
         <v>N/A</v>
@@ -5321,7 +5321,7 @@
         <v>25</v>
       </c>
       <c r="G182" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H182" t="str">
         <v>N/A</v>
@@ -5344,10 +5344,10 @@
         <v>PASS</v>
       </c>
       <c r="F183">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G183" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H183" t="str">
         <v>N/A</v>
@@ -5370,10 +5370,10 @@
         <v>PASS</v>
       </c>
       <c r="F184">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G184" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H184" t="str">
         <v>N/A</v>
@@ -5396,10 +5396,10 @@
         <v>PASS</v>
       </c>
       <c r="F185">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G185" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H185" t="str">
         <v>N/A</v>
@@ -5422,10 +5422,10 @@
         <v>PASS</v>
       </c>
       <c r="F186">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G186" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H186" t="str">
         <v>N/A</v>
@@ -5448,10 +5448,10 @@
         <v>PASS</v>
       </c>
       <c r="F187">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G187" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H187" t="str">
         <v>N/A</v>
@@ -5474,10 +5474,10 @@
         <v>PASS</v>
       </c>
       <c r="F188">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G188" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H188" t="str">
         <v>N/A</v>
@@ -5500,10 +5500,10 @@
         <v>PASS</v>
       </c>
       <c r="F189">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G189" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H189" t="str">
         <v>N/A</v>
@@ -5526,10 +5526,10 @@
         <v>PASS</v>
       </c>
       <c r="F190">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G190" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H190" t="str">
         <v>N/A</v>
@@ -5552,10 +5552,10 @@
         <v>PASS</v>
       </c>
       <c r="F191">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G191" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H191" t="str">
         <v>N/A</v>
@@ -5578,10 +5578,10 @@
         <v>PASS</v>
       </c>
       <c r="F192">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G192" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H192" t="str">
         <v>N/A</v>
@@ -5604,10 +5604,10 @@
         <v>PASS</v>
       </c>
       <c r="F193">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G193" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H193" t="str">
         <v>N/A</v>
@@ -5630,10 +5630,10 @@
         <v>PASS</v>
       </c>
       <c r="F194">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G194" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H194" t="str">
         <v>N/A</v>
@@ -5656,10 +5656,10 @@
         <v>PASS</v>
       </c>
       <c r="F195">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G195" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H195" t="str">
         <v>N/A</v>
@@ -5682,10 +5682,10 @@
         <v>PASS</v>
       </c>
       <c r="F196">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G196" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H196" t="str">
         <v>N/A</v>
@@ -5708,10 +5708,10 @@
         <v>PASS</v>
       </c>
       <c r="F197">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G197" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H197" t="str">
         <v>N/A</v>
@@ -5737,7 +5737,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H198" t="str">
         <v>N/A</v>
@@ -5760,10 +5760,10 @@
         <v>PASS</v>
       </c>
       <c r="F199">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H199" t="str">
         <v>N/A</v>
@@ -5786,10 +5786,10 @@
         <v>PASS</v>
       </c>
       <c r="F200">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G200" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H200" t="str">
         <v>N/A</v>
@@ -5812,10 +5812,10 @@
         <v>PASS</v>
       </c>
       <c r="F201">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-08-06T04:14:38.862Z</v>
+        <v>2026-08-06T04:28:57.411Z</v>
       </c>
       <c r="H201" t="str">
         <v>N/A</v>
@@ -5838,10 +5838,10 @@
         <v>PASS</v>
       </c>
       <c r="F202">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G202" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H202" t="str">
         <v>N/A</v>
@@ -5864,10 +5864,10 @@
         <v>PASS</v>
       </c>
       <c r="F203">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G203" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H203" t="str">
         <v>N/A</v>
@@ -5890,10 +5890,10 @@
         <v>PASS</v>
       </c>
       <c r="F204">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H204" t="str">
         <v>N/A</v>
@@ -5916,10 +5916,10 @@
         <v>PASS</v>
       </c>
       <c r="F205">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H205" t="str">
         <v>N/A</v>
@@ -5942,10 +5942,10 @@
         <v>PASS</v>
       </c>
       <c r="F206">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G206" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H206" t="str">
         <v>N/A</v>
@@ -5968,10 +5968,10 @@
         <v>PASS</v>
       </c>
       <c r="F207">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G207" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H207" t="str">
         <v>N/A</v>
@@ -5994,10 +5994,10 @@
         <v>PASS</v>
       </c>
       <c r="F208">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G208" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H208" t="str">
         <v>N/A</v>
@@ -6020,10 +6020,10 @@
         <v>PASS</v>
       </c>
       <c r="F209">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G209" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H209" t="str">
         <v>N/A</v>
@@ -6046,10 +6046,10 @@
         <v>PASS</v>
       </c>
       <c r="F210">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G210" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H210" t="str">
         <v>N/A</v>
@@ -6072,10 +6072,10 @@
         <v>PASS</v>
       </c>
       <c r="F211">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G211" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H211" t="str">
         <v>N/A</v>
@@ -6098,10 +6098,10 @@
         <v>PASS</v>
       </c>
       <c r="F212">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H212" t="str">
         <v>N/A</v>
@@ -6124,10 +6124,10 @@
         <v>PASS</v>
       </c>
       <c r="F213">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H213" t="str">
         <v>N/A</v>
@@ -6153,7 +6153,7 @@
         <v>21</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H214" t="str">
         <v>N/A</v>
@@ -6176,10 +6176,10 @@
         <v>PASS</v>
       </c>
       <c r="F215">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H215" t="str">
         <v>N/A</v>
@@ -6202,10 +6202,10 @@
         <v>PASS</v>
       </c>
       <c r="F216">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H216" t="str">
         <v>N/A</v>
@@ -6228,10 +6228,10 @@
         <v>PASS</v>
       </c>
       <c r="F217">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H217" t="str">
         <v>N/A</v>
@@ -6254,10 +6254,10 @@
         <v>PASS</v>
       </c>
       <c r="F218">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H218" t="str">
         <v>N/A</v>
@@ -6280,10 +6280,10 @@
         <v>PASS</v>
       </c>
       <c r="F219">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H219" t="str">
         <v>N/A</v>
@@ -6306,10 +6306,10 @@
         <v>PASS</v>
       </c>
       <c r="F220">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G220" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H220" t="str">
         <v>N/A</v>
@@ -6332,10 +6332,10 @@
         <v>PASS</v>
       </c>
       <c r="F221">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G221" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H221" t="str">
         <v>N/A</v>
@@ -6358,10 +6358,10 @@
         <v>PASS</v>
       </c>
       <c r="F222">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H222" t="str">
         <v>N/A</v>
@@ -6384,10 +6384,10 @@
         <v>PASS</v>
       </c>
       <c r="F223">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H223" t="str">
         <v>N/A</v>
@@ -6410,10 +6410,10 @@
         <v>PASS</v>
       </c>
       <c r="F224">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G224" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H224" t="str">
         <v>N/A</v>
@@ -6436,10 +6436,10 @@
         <v>PASS</v>
       </c>
       <c r="F225">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G225" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H225" t="str">
         <v>N/A</v>
@@ -6462,10 +6462,10 @@
         <v>PASS</v>
       </c>
       <c r="F226">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H226" t="str">
         <v>N/A</v>
@@ -6488,10 +6488,10 @@
         <v>PASS</v>
       </c>
       <c r="F227">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H227" t="str">
         <v>N/A</v>
@@ -6514,10 +6514,10 @@
         <v>PASS</v>
       </c>
       <c r="F228">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H228" t="str">
         <v>N/A</v>
@@ -6540,10 +6540,10 @@
         <v>PASS</v>
       </c>
       <c r="F229">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H229" t="str">
         <v>N/A</v>
@@ -6566,10 +6566,10 @@
         <v>PASS</v>
       </c>
       <c r="F230">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H230" t="str">
         <v>N/A</v>
@@ -6592,10 +6592,10 @@
         <v>PASS</v>
       </c>
       <c r="F231">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-08-06T04:14:38.871Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H231" t="str">
         <v>N/A</v>
@@ -6618,10 +6618,10 @@
         <v>PASS</v>
       </c>
       <c r="F232">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H232" t="str">
         <v>N/A</v>
@@ -6644,10 +6644,10 @@
         <v>PASS</v>
       </c>
       <c r="F233">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G233" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H233" t="str">
         <v>N/A</v>
@@ -6673,7 +6673,7 @@
         <v>15</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H234" t="str">
         <v>N/A</v>
@@ -6696,10 +6696,10 @@
         <v>PASS</v>
       </c>
       <c r="F235">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H235" t="str">
         <v>N/A</v>
@@ -6722,10 +6722,10 @@
         <v>PASS</v>
       </c>
       <c r="F236">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H236" t="str">
         <v>N/A</v>
@@ -6748,10 +6748,10 @@
         <v>PASS</v>
       </c>
       <c r="F237">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G237" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H237" t="str">
         <v>N/A</v>
@@ -6774,10 +6774,10 @@
         <v>PASS</v>
       </c>
       <c r="F238">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G238" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H238" t="str">
         <v>N/A</v>
@@ -6800,10 +6800,10 @@
         <v>PASS</v>
       </c>
       <c r="F239">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G239" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H239" t="str">
         <v>N/A</v>
@@ -6826,10 +6826,10 @@
         <v>PASS</v>
       </c>
       <c r="F240">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G240" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H240" t="str">
         <v>N/A</v>
@@ -6852,10 +6852,10 @@
         <v>PASS</v>
       </c>
       <c r="F241">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G241" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H241" t="str">
         <v>N/A</v>
@@ -6878,10 +6878,10 @@
         <v>PASS</v>
       </c>
       <c r="F242">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G242" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H242" t="str">
         <v>N/A</v>
@@ -6904,10 +6904,10 @@
         <v>PASS</v>
       </c>
       <c r="F243">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G243" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H243" t="str">
         <v>N/A</v>
@@ -6930,10 +6930,10 @@
         <v>PASS</v>
       </c>
       <c r="F244">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G244" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H244" t="str">
         <v>N/A</v>
@@ -6956,10 +6956,10 @@
         <v>PASS</v>
       </c>
       <c r="F245">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G245" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H245" t="str">
         <v>N/A</v>
@@ -6982,10 +6982,10 @@
         <v>PASS</v>
       </c>
       <c r="F246">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G246" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H246" t="str">
         <v>N/A</v>
@@ -7008,10 +7008,10 @@
         <v>PASS</v>
       </c>
       <c r="F247">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G247" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H247" t="str">
         <v>N/A</v>
@@ -7034,10 +7034,10 @@
         <v>PASS</v>
       </c>
       <c r="F248">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G248" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H248" t="str">
         <v>N/A</v>
@@ -7060,10 +7060,10 @@
         <v>PASS</v>
       </c>
       <c r="F249">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G249" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H249" t="str">
         <v>N/A</v>
@@ -7080,16 +7080,16 @@
         <v>05_DENTAL_SCAN</v>
       </c>
       <c r="D250" t="str">
-        <v>test_api_249_post_scan_reprocess_ai_pipeline_id_re: API 249 POST SCAN REPROCESS AI PIPELINE ID RE</v>
+        <v>test_api_249_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
       </c>
       <c r="E250" t="str">
         <v>PASS</v>
       </c>
       <c r="F250">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G250" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H250" t="str">
         <v>N/A</v>
@@ -7112,10 +7112,10 @@
         <v>PASS</v>
       </c>
       <c r="F251">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G251" t="str">
-        <v>2026-08-06T04:14:38.872Z</v>
+        <v>2026-08-06T04:28:57.423Z</v>
       </c>
       <c r="H251" t="str">
         <v>N/A</v>
@@ -7138,10 +7138,10 @@
         <v>PASS</v>
       </c>
       <c r="F252">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G252" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H252" t="str">
         <v>N/A</v>
@@ -7164,10 +7164,10 @@
         <v>PASS</v>
       </c>
       <c r="F253">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G253" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H253" t="str">
         <v>N/A</v>
@@ -7190,10 +7190,10 @@
         <v>PASS</v>
       </c>
       <c r="F254">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G254" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H254" t="str">
         <v>N/A</v>
@@ -7216,10 +7216,10 @@
         <v>PASS</v>
       </c>
       <c r="F255">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G255" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H255" t="str">
         <v>N/A</v>
@@ -7242,10 +7242,10 @@
         <v>PASS</v>
       </c>
       <c r="F256">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G256" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H256" t="str">
         <v>N/A</v>
@@ -7268,10 +7268,10 @@
         <v>PASS</v>
       </c>
       <c r="F257">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G257" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H257" t="str">
         <v>N/A</v>
@@ -7294,10 +7294,10 @@
         <v>PASS</v>
       </c>
       <c r="F258">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G258" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H258" t="str">
         <v>N/A</v>
@@ -7320,10 +7320,10 @@
         <v>PASS</v>
       </c>
       <c r="F259">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G259" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.431Z</v>
       </c>
       <c r="H259" t="str">
         <v>N/A</v>
@@ -7346,10 +7346,10 @@
         <v>PASS</v>
       </c>
       <c r="F260">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G260" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H260" t="str">
         <v>N/A</v>
@@ -7372,10 +7372,10 @@
         <v>PASS</v>
       </c>
       <c r="F261">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G261" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H261" t="str">
         <v>N/A</v>
@@ -7398,10 +7398,10 @@
         <v>PASS</v>
       </c>
       <c r="F262">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G262" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H262" t="str">
         <v>N/A</v>
@@ -7424,10 +7424,10 @@
         <v>PASS</v>
       </c>
       <c r="F263">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G263" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H263" t="str">
         <v>N/A</v>
@@ -7450,10 +7450,10 @@
         <v>PASS</v>
       </c>
       <c r="F264">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G264" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H264" t="str">
         <v>N/A</v>
@@ -7476,10 +7476,10 @@
         <v>PASS</v>
       </c>
       <c r="F265">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G265" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H265" t="str">
         <v>N/A</v>
@@ -7502,10 +7502,10 @@
         <v>PASS</v>
       </c>
       <c r="F266">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G266" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H266" t="str">
         <v>N/A</v>
@@ -7528,10 +7528,10 @@
         <v>PASS</v>
       </c>
       <c r="F267">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G267" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H267" t="str">
         <v>N/A</v>
@@ -7554,10 +7554,10 @@
         <v>PASS</v>
       </c>
       <c r="F268">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G268" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H268" t="str">
         <v>N/A</v>
@@ -7580,10 +7580,10 @@
         <v>PASS</v>
       </c>
       <c r="F269">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G269" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H269" t="str">
         <v>N/A</v>
@@ -7606,10 +7606,10 @@
         <v>PASS</v>
       </c>
       <c r="F270">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G270" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H270" t="str">
         <v>N/A</v>
@@ -7632,10 +7632,10 @@
         <v>PASS</v>
       </c>
       <c r="F271">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G271" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H271" t="str">
         <v>N/A</v>
@@ -7658,10 +7658,10 @@
         <v>PASS</v>
       </c>
       <c r="F272">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G272" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H272" t="str">
         <v>N/A</v>
@@ -7684,10 +7684,10 @@
         <v>PASS</v>
       </c>
       <c r="F273">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G273" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H273" t="str">
         <v>N/A</v>
@@ -7710,10 +7710,10 @@
         <v>PASS</v>
       </c>
       <c r="F274">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G274" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H274" t="str">
         <v>N/A</v>
@@ -7736,10 +7736,10 @@
         <v>PASS</v>
       </c>
       <c r="F275">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G275" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H275" t="str">
         <v>N/A</v>
@@ -7762,10 +7762,10 @@
         <v>PASS</v>
       </c>
       <c r="F276">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G276" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H276" t="str">
         <v>N/A</v>
@@ -7788,10 +7788,10 @@
         <v>PASS</v>
       </c>
       <c r="F277">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G277" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H277" t="str">
         <v>N/A</v>
@@ -7814,10 +7814,10 @@
         <v>PASS</v>
       </c>
       <c r="F278">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G278" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H278" t="str">
         <v>N/A</v>
@@ -7840,10 +7840,10 @@
         <v>PASS</v>
       </c>
       <c r="F279">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G279" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H279" t="str">
         <v>N/A</v>
@@ -7866,10 +7866,10 @@
         <v>PASS</v>
       </c>
       <c r="F280">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G280" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H280" t="str">
         <v>N/A</v>
@@ -7892,10 +7892,10 @@
         <v>PASS</v>
       </c>
       <c r="F281">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G281" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H281" t="str">
         <v>N/A</v>
@@ -7918,10 +7918,10 @@
         <v>PASS</v>
       </c>
       <c r="F282">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G282" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H282" t="str">
         <v>N/A</v>
@@ -7944,10 +7944,10 @@
         <v>PASS</v>
       </c>
       <c r="F283">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G283" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H283" t="str">
         <v>N/A</v>
@@ -7970,10 +7970,10 @@
         <v>PASS</v>
       </c>
       <c r="F284">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G284" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H284" t="str">
         <v>N/A</v>
@@ -7996,10 +7996,10 @@
         <v>PASS</v>
       </c>
       <c r="F285">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G285" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H285" t="str">
         <v>N/A</v>
@@ -8022,10 +8022,10 @@
         <v>PASS</v>
       </c>
       <c r="F286">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G286" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H286" t="str">
         <v>N/A</v>
@@ -8048,10 +8048,10 @@
         <v>PASS</v>
       </c>
       <c r="F287">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G287" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H287" t="str">
         <v>N/A</v>
@@ -8074,10 +8074,10 @@
         <v>PASS</v>
       </c>
       <c r="F288">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G288" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H288" t="str">
         <v>N/A</v>
@@ -8100,10 +8100,10 @@
         <v>PASS</v>
       </c>
       <c r="F289">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G289" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H289" t="str">
         <v>N/A</v>
@@ -8126,10 +8126,10 @@
         <v>PASS</v>
       </c>
       <c r="F290">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G290" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H290" t="str">
         <v>N/A</v>
@@ -8152,10 +8152,10 @@
         <v>PASS</v>
       </c>
       <c r="F291">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G291" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H291" t="str">
         <v>N/A</v>
@@ -8178,10 +8178,10 @@
         <v>PASS</v>
       </c>
       <c r="F292">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G292" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H292" t="str">
         <v>N/A</v>
@@ -8204,10 +8204,10 @@
         <v>PASS</v>
       </c>
       <c r="F293">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G293" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H293" t="str">
         <v>N/A</v>
@@ -8230,10 +8230,10 @@
         <v>PASS</v>
       </c>
       <c r="F294">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G294" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H294" t="str">
         <v>N/A</v>
@@ -8256,10 +8256,10 @@
         <v>PASS</v>
       </c>
       <c r="F295">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G295" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H295" t="str">
         <v>N/A</v>
@@ -8282,10 +8282,10 @@
         <v>PASS</v>
       </c>
       <c r="F296">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G296" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H296" t="str">
         <v>N/A</v>
@@ -8308,10 +8308,10 @@
         <v>PASS</v>
       </c>
       <c r="F297">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G297" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H297" t="str">
         <v>N/A</v>
@@ -8334,10 +8334,10 @@
         <v>PASS</v>
       </c>
       <c r="F298">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G298" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H298" t="str">
         <v>N/A</v>
@@ -8360,10 +8360,10 @@
         <v>PASS</v>
       </c>
       <c r="F299">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G299" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H299" t="str">
         <v>N/A</v>
@@ -8386,10 +8386,10 @@
         <v>PASS</v>
       </c>
       <c r="F300">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G300" t="str">
-        <v>2026-08-06T04:14:38.877Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H300" t="str">
         <v>N/A</v>
@@ -8412,10 +8412,10 @@
         <v>PASS</v>
       </c>
       <c r="F301">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G301" t="str">
-        <v>2026-08-06T04:14:38.878Z</v>
+        <v>2026-08-06T04:28:57.432Z</v>
       </c>
       <c r="H301" t="str">
         <v>N/A</v>

--- a/dentai-backend/backend-tests/test-report.xlsx
+++ b/dentai-backend/backend-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:21:51 am</v>
+        <v>6/8/2026, 10:34:20 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.12 seconds</v>
+        <v>0.13 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Test Category Breakdown</v>
+        <v>Feature Module Category Breakdown</v>
       </c>
       <c r="B13" t="str">
         <v>Total Specs</v>
@@ -532,51 +532,73 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>API Endpoints Functional Tests</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="B14">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="C14" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Input Validation &amp; Security Tests</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="B15">
         <v>50</v>
       </c>
       <c r="C15" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Service Layer Logic Tests</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="B16">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>API Load &amp; Performance Benchmarks</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C17" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Dental Vision Scanner</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18" t="str">
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Educational Feed &amp; Analytics</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19" t="str">
+        <v>16.7%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,8 +609,8 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -603,10 +625,10 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Feature Category</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Suite File</v>
+        <v>Test Spec File</v>
       </c>
       <c r="E1" t="str">
         <v>Unique API Spec Function Name</v>
@@ -629,10 +651,10 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D2" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E2" t="str">
         <v>test_post_auth_register_valid_payload_returns_201_created: API 001 POST AUTH REGISTER VALID PAYLOAD RETURNS 201 CREATED</v>
@@ -641,10 +663,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.913Z</v>
       </c>
     </row>
     <row r="3">
@@ -655,10 +677,10 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D3" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E3" t="str">
         <v>test_post_auth_login_valid_credentials_returns_200_jwt_token: API 002 POST AUTH LOGIN VALID CREDENTIALS RETURNS 200 JWT TOKEN</v>
@@ -667,10 +689,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="4">
@@ -681,10 +703,10 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D4" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E4" t="str">
         <v>test_post_auth_login_invalid_password_returns_401_unauthorized: API 003 POST AUTH LOGIN INVALID PASSWORD RETURNS 401 UNAUTHORIZED</v>
@@ -693,10 +715,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="5">
@@ -707,10 +729,10 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D5" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E5" t="str">
         <v>test_post_auth_login_nonexistent_email_returns_404_not_found: API 004 POST AUTH LOGIN NONEXISTENT EMAIL RETURNS 404 NOT FOUND</v>
@@ -719,10 +741,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="6">
@@ -733,10 +755,10 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D6" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E6" t="str">
         <v>test_post_auth_register_duplicate_email_returns_409_conflict: API 005 POST AUTH REGISTER DUPLICATE EMAIL RETURNS 409 CONFLICT</v>
@@ -745,10 +767,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="7">
@@ -759,10 +781,10 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D7" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E7" t="str">
         <v>test_post_auth_refresh_valid_token_returns_200_new_access_token: API 006 POST AUTH REFRESH VALID TOKEN RETURNS 200 NEW ACCESS TOKEN</v>
@@ -774,7 +796,7 @@
         <v>18</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="8">
@@ -785,10 +807,10 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D8" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E8" t="str">
         <v>test_post_auth_refresh_expired_token_returns_401_token_expired: API 007 POST AUTH REFRESH EXPIRED TOKEN RETURNS 401 TOKEN EXPIRED</v>
@@ -797,10 +819,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="9">
@@ -811,10 +833,10 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D9" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E9" t="str">
         <v>test_post_auth_logout_revokes_refresh_token_in_redis: API 008 POST AUTH LOGOUT REVOKES REFRESH TOKEN IN REDIS</v>
@@ -823,10 +845,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="10">
@@ -837,10 +859,10 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D10" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E10" t="str">
         <v>test_post_auth_password_reset_request_sends_email_200_ok: API 009 POST AUTH PASSWORD RESET REQUEST SENDS EMAIL 200 OK</v>
@@ -849,10 +871,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +885,10 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D11" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E11" t="str">
         <v>test_post_auth_password_reset_confirm_valid_token_updates_hash: API 010 POST AUTH PASSWORD RESET CONFIRM VALID TOKEN UPDATES HASH</v>
@@ -878,7 +900,7 @@
         <v>20</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +911,10 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D12" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E12" t="str">
         <v>test_post_auth_verify_2fa_totp_code_returns_session_cookie: API 011 POST AUTH VERIFY 2FA TOTP CODE RETURNS SESSION COOKIE</v>
@@ -901,10 +923,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="13">
@@ -915,10 +937,10 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D13" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E13" t="str">
         <v>test_get_auth_me_authenticated_user_returns_user_profile_schema: API 012 GET AUTH ME AUTHENTICATED USER RETURNS USER PROFILE SCHEMA</v>
@@ -927,10 +949,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="14">
@@ -941,10 +963,10 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D14" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E14" t="str">
         <v>test_get_auth_me_missing_bearer_header_returns_401_unauthorized: API 013 GET AUTH ME MISSING BEARER HEADER RETURNS 401 UNAUTHORIZED</v>
@@ -953,10 +975,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="15">
@@ -967,10 +989,10 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D15" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E15" t="str">
         <v>test_get_auth_me_malformed_bearer_token_returns_422_validation: API 014 GET AUTH ME MALFORMED BEARER TOKEN RETURNS 422 VALIDATION</v>
@@ -979,10 +1001,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="16">
@@ -993,10 +1015,10 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D16" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E16" t="str">
         <v>test_post_auth_verify_email_valid_link_sets_is_verified_true: API 015 POST AUTH VERIFY EMAIL VALID LINK SETS IS VERIFIED TRUE</v>
@@ -1005,10 +1027,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="17">
@@ -1019,10 +1041,10 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D17" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E17" t="str">
         <v>test_put_user_profile_updates_phone_number_returns_200: API 016 PUT USER PROFILE UPDATES PHONE NUMBER RETURNS 200</v>
@@ -1031,10 +1053,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1067,10 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D18" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E18" t="str">
         <v>test_post_user_avatar_multipart_upload_saves_file_path: API 017 POST USER AVATAR MULTIPART UPLOAD SAVES FILE PATH</v>
@@ -1057,10 +1079,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="19">
@@ -1071,10 +1093,10 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D19" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E19" t="str">
         <v>test_post_user_avatar_unsupported_extension_returns_400_bad_request: API 018 POST USER AVATAR UNSUPPORTED EXTENSION RETURNS 400 BAD REQUEST</v>
@@ -1083,10 +1105,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="20">
@@ -1097,10 +1119,10 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D20" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E20" t="str">
         <v>test_get_user_sessions_returns_active_devices_array: API 019 GET USER SESSIONS RETURNS ACTIVE DEVICES ARRAY</v>
@@ -1109,10 +1131,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="21">
@@ -1123,10 +1145,10 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D21" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E21" t="str">
         <v>test_delete_user_sessions_id_terminates_target_device_session: API 020 DELETE USER SESSIONS ID TERMINATES TARGET DEVICE SESSION</v>
@@ -1135,10 +1157,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="22">
@@ -1149,10 +1171,10 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D22" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E22" t="str">
         <v>test_post_auth_change_password_valid_old_password_updates: API 021 POST AUTH CHANGE PASSWORD VALID OLD PASSWORD UPDATES</v>
@@ -1161,10 +1183,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="23">
@@ -1175,10 +1197,10 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D23" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E23" t="str">
         <v>test_post_auth_change_password_invalid_old_password_returns_400: API 022 POST AUTH CHANGE PASSWORD INVALID OLD PASSWORD RETURNS 400</v>
@@ -1187,10 +1209,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="24">
@@ -1201,10 +1223,10 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D24" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E24" t="str">
         <v>test_post_auth_passkey_register_challenge_generates_options: API 023 POST AUTH PASSKEY REGISTER CHALLENGE GENERATES OPTIONS</v>
@@ -1213,10 +1235,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="25">
@@ -1227,10 +1249,10 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D25" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E25" t="str">
         <v>test_post_auth_passkey_verify_assertion_authenticates_user: API 024 POST AUTH PASSKEY VERIFY ASSERTION AUTHENTICATES USER</v>
@@ -1242,7 +1264,7 @@
         <v>17</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="26">
@@ -1253,10 +1275,10 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D26" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E26" t="str">
         <v>test_get_auth_permissions_patient_role_returns_patient_scopes: API 025 GET AUTH PERMISSIONS PATIENT ROLE RETURNS PATIENT SCOPES</v>
@@ -1265,10 +1287,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="27">
@@ -1279,10 +1301,10 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D27" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E27" t="str">
         <v>test_get_auth_permissions_doctor_role_returns_clinical_scopes: API 026 GET AUTH PERMISSIONS DOCTOR ROLE RETURNS CLINICAL SCOPES</v>
@@ -1291,10 +1313,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="28">
@@ -1305,10 +1327,10 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D28" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E28" t="str">
         <v>test_get_auth_permissions_admin_role_returns_all_scopes: API 027 GET AUTH PERMISSIONS ADMIN ROLE RETURNS ALL SCOPES</v>
@@ -1317,10 +1339,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="29">
@@ -1331,10 +1353,10 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D29" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E29" t="str">
         <v>test_post_auth_send_sms_otp_rate_limit_1_per_minute: API 028 POST AUTH SEND SMS OTP RATE LIMIT 1 PER MINUTE</v>
@@ -1343,10 +1365,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="30">
@@ -1357,10 +1379,10 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D30" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E30" t="str">
         <v>test_post_auth_verify_sms_otp_invalid_code_returns_400: API 029 POST AUTH VERIFY SMS OTP INVALID CODE RETURNS 400</v>
@@ -1369,10 +1391,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="31">
@@ -1383,10 +1405,10 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D31" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E31" t="str">
         <v>test_put_user_locale_updates_preferred_language_setting: API 030 PUT USER LOCALE UPDATES PREFERRED LANGUAGE SETTING</v>
@@ -1395,10 +1417,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="32">
@@ -1409,10 +1431,10 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D32" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E32" t="str">
         <v>test_get_user_preferences_returns_notification_toggles: API 031 GET USER PREFERENCES RETURNS NOTIFICATION TOGGLES</v>
@@ -1421,10 +1443,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="33">
@@ -1435,10 +1457,10 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D33" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E33" t="str">
         <v>test_put_user_preferences_updates_email_sms_push_flags: API 032 PUT USER PREFERENCES UPDATES EMAIL SMS PUSH FLAGS</v>
@@ -1447,10 +1469,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="34">
@@ -1461,10 +1483,10 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D34" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E34" t="str">
         <v>test_post_user_consent_hipaa_record_writes_consent_audit: API 033 POST USER CONSENT HIPAA RECORD WRITES CONSENT AUDIT</v>
@@ -1473,10 +1495,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="35">
@@ -1487,10 +1509,10 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D35" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E35" t="str">
         <v>test_delete_user_account_initiates_30_day_soft_delete: API 034 DELETE USER ACCOUNT INITIATES 30 DAY SOFT DELETE</v>
@@ -1499,10 +1521,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="36">
@@ -1513,10 +1535,10 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D36" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E36" t="str">
         <v>test_post_auth_unlock_account_admin_overrides_lockout: API 035 POST AUTH UNLOCK ACCOUNT ADMIN OVERRIDES LOCKOUT</v>
@@ -1525,10 +1547,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="37">
@@ -1539,10 +1561,10 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D37" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E37" t="str">
         <v>test_get_health_endpoint_returns_200_status_up: API 036 GET HEALTH ENDPOINT RETURNS 200 STATUS UP</v>
@@ -1551,10 +1573,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="38">
@@ -1565,10 +1587,10 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D38" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E38" t="str">
         <v>test_options_cors_preflight_returns_access_control_headers: API 037 OPTIONS CORS PREFLIGHT RETURNS ACCESS CONTROL HEADERS</v>
@@ -1577,10 +1599,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="39">
@@ -1591,10 +1613,10 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D39" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E39" t="str">
         <v>test_security_headers_x_content_type_options_nosniff_present: API 038 SECURITY HEADERS X CONTENT TYPE OPTIONS NOSNIFF PRESENT</v>
@@ -1603,10 +1625,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="40">
@@ -1617,10 +1639,10 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D40" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E40" t="str">
         <v>test_security_headers_x_frame_options_deny_present: API 039 SECURITY HEADERS X FRAME OPTIONS DENY PRESENT</v>
@@ -1629,10 +1651,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="41">
@@ -1643,10 +1665,10 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D41" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E41" t="str">
         <v>test_security_headers_strict_transport_security_present: API 040 SECURITY HEADERS STRICT TRANSPORT SECURITY PRESENT</v>
@@ -1655,10 +1677,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="42">
@@ -1669,10 +1691,10 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D42" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E42" t="str">
         <v>test_rate_limiting_triggers_429_too_many_requests: API 041 RATE LIMITING TRIGGERS 429 TOO MANY REQUESTS</v>
@@ -1681,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="43">
@@ -1695,10 +1717,10 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D43" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E43" t="str">
         <v>test_post_notifications_fcm_token_registers_device: API 042 POST NOTIFICATIONS FCM TOKEN REGISTERS DEVICE</v>
@@ -1707,10 +1729,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="44">
@@ -1721,10 +1743,10 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D44" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E44" t="str">
         <v>test_post_notifications_apns_token_registers_apple_device: API 043 POST NOTIFICATIONS APNS TOKEN REGISTERS APPLE DEVICE</v>
@@ -1733,10 +1755,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="45">
@@ -1747,10 +1769,10 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D45" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E45" t="str">
         <v>test_put_user_emergency_contact_validates_phone_number: API 044 PUT USER EMERGENCY CONTACT VALIDATES PHONE NUMBER</v>
@@ -1759,10 +1781,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="46">
@@ -1773,10 +1795,10 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D46" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E46" t="str">
         <v>test_get_auth_lockout_status_returns_attempt_count: API 045 GET AUTH LOCKOUT STATUS RETURNS ATTEMPT COUNT</v>
@@ -1785,10 +1807,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="47">
@@ -1799,10 +1821,10 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D47" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E47" t="str">
         <v>test_post_auth_captcha_verify_valid_response_passes: API 046 POST AUTH CAPTCHA VERIFY VALID RESPONSE PASSES</v>
@@ -1811,10 +1833,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="48">
@@ -1825,10 +1847,10 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D48" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E48" t="str">
         <v>test_get_tenant_info_header_isolation_check: API 047 GET TENANT INFO HEADER ISOLATION CHECK</v>
@@ -1837,10 +1859,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="49">
@@ -1851,10 +1873,10 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D49" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E49" t="str">
         <v>test_post_auth_revoke_all_sessions_clears_user_tokens: API 048 POST AUTH REVOKE ALL SESSIONS CLEARS USER TOKENS</v>
@@ -1863,10 +1885,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="50">
@@ -1877,10 +1899,10 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D50" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E50" t="str">
         <v>test_get_auth_password_expired_check_returns_boolean: API 049 GET AUTH PASSWORD EXPIRED CHECK RETURNS BOOLEAN</v>
@@ -1889,10 +1911,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="51">
@@ -1903,10 +1925,10 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Validation &amp; Security</v>
+        <v>Authentication &amp; Security</v>
       </c>
       <c r="D51" t="str">
-        <v>01_AUTH_SECURITY</v>
+        <v>test_01_auth_security.py</v>
       </c>
       <c r="E51" t="str">
         <v>test_auth_api_integration_full_lifecycle_certification: API 050 AUTH API INTEGRATION FULL LIFECYCLE CERTIFICATION</v>
@@ -1915,10 +1937,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T04:51:51.793Z</v>
+        <v>2026-08-06T05:04:19.914Z</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1951,10 @@
         <v>API-051</v>
       </c>
       <c r="C52" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D52" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E52" t="str">
         <v>test_post_symptom_analyze_valid_payload_returns_triage_score: API 051 POST SYMPTOM ANALYZE VALID PAYLOAD RETURNS TRIAGE SCORE</v>
@@ -1941,10 +1963,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="53">
@@ -1955,10 +1977,10 @@
         <v>API-052</v>
       </c>
       <c r="C53" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D53" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E53" t="str">
         <v>test_post_symptom_analyze_empty_symptoms_returns_422: API 052 POST SYMPTOM ANALYZE EMPTY SYMPTOMS RETURNS 422</v>
@@ -1967,10 +1989,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="54">
@@ -1981,10 +2003,10 @@
         <v>API-053</v>
       </c>
       <c r="C54" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D54" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E54" t="str">
         <v>test_get_symptom_history_authenticated_returns_paginated_list: API 053 GET SYMPTOM HISTORY AUTHENTICATED RETURNS PAGINATED LIST</v>
@@ -1993,10 +2015,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="55">
@@ -2007,10 +2029,10 @@
         <v>API-054</v>
       </c>
       <c r="C55" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D55" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E55" t="str">
         <v>test_get_symptom_history_unauthenticated_returns_401: API 054 GET SYMPTOM HISTORY UNAUTHENTICATED RETURNS 401</v>
@@ -2019,10 +2041,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="56">
@@ -2033,10 +2055,10 @@
         <v>API-055</v>
       </c>
       <c r="C56" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D56" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E56" t="str">
         <v>test_get_symptom_record_id_valid_owner_returns_details: API 055 GET SYMPTOM RECORD ID VALID OWNER RETURNS DETAILS</v>
@@ -2045,10 +2067,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="57">
@@ -2059,10 +2081,10 @@
         <v>API-056</v>
       </c>
       <c r="C57" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D57" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E57" t="str">
         <v>test_get_symptom_record_id_forbidden_owner_returns_403: API 056 GET SYMPTOM RECORD ID FORBIDDEN OWNER RETURNS 403</v>
@@ -2071,10 +2093,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="58">
@@ -2085,10 +2107,10 @@
         <v>API-057</v>
       </c>
       <c r="C58" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D58" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E58" t="str">
         <v>test_delete_symptom_record_id_deletes_record_204: API 057 DELETE SYMPTOM RECORD ID DELETES RECORD 204</v>
@@ -2097,10 +2119,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="59">
@@ -2111,10 +2133,10 @@
         <v>API-058</v>
       </c>
       <c r="C59" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D59" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E59" t="str">
         <v>test_post_symptom_draft_saves_in_progress_questionnaire: API 058 POST SYMPTOM DRAFT SAVES IN PROGRESS QUESTIONNAIRE</v>
@@ -2123,10 +2145,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="60">
@@ -2137,10 +2159,10 @@
         <v>API-059</v>
       </c>
       <c r="C60" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D60" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E60" t="str">
         <v>test_get_symptom_draft_retrieves_last_draft_json: API 059 GET SYMPTOM DRAFT RETRIEVES LAST DRAFT JSON</v>
@@ -2149,10 +2171,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="61">
@@ -2163,10 +2185,10 @@
         <v>API-060</v>
       </c>
       <c r="C61" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D61" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E61" t="str">
         <v>test_post_symptom_pdf_report_generates_download_url: API 060 POST SYMPTOM PDF REPORT GENERATES DOWNLOAD URL</v>
@@ -2175,10 +2197,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="62">
@@ -2189,10 +2211,10 @@
         <v>API-061</v>
       </c>
       <c r="C62" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D62" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E62" t="str">
         <v>test_get_symptom_categories_returns_dental_anatomy_tree: API 061 GET SYMPTOM CATEGORIES RETURNS DENTAL ANATOMY TREE</v>
@@ -2201,10 +2223,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T04:51:51.847Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="63">
@@ -2215,10 +2237,10 @@
         <v>API-062</v>
       </c>
       <c r="C63" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D63" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E63" t="str">
         <v>test_get_symptom_rules_triage_matrix_returns_weights: API 062 GET SYMPTOM RULES TRIAGE MATRIX RETURNS WEIGHTS</v>
@@ -2227,10 +2249,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="64">
@@ -2241,10 +2263,10 @@
         <v>API-063</v>
       </c>
       <c r="C64" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D64" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E64" t="str">
         <v>test_post_symptom_share_generates_temporary_access_link: API 063 POST SYMPTOM SHARE GENERATES TEMPORARY ACCESS LINK</v>
@@ -2253,10 +2275,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="65">
@@ -2267,10 +2289,10 @@
         <v>API-064</v>
       </c>
       <c r="C65" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D65" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E65" t="str">
         <v>test_get_symptom_shared_token_returns_public_summary: API 064 GET SYMPTOM SHARED TOKEN RETURNS PUBLIC SUMMARY</v>
@@ -2282,7 +2304,7 @@
         <v>13</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="66">
@@ -2293,10 +2315,10 @@
         <v>API-065</v>
       </c>
       <c r="C66" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D66" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E66" t="str">
         <v>test_put_symptom_record_id_updates_notes: API 065 PUT SYMPTOM RECORD ID UPDATES NOTES</v>
@@ -2308,7 +2330,7 @@
         <v>24</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="67">
@@ -2319,10 +2341,10 @@
         <v>API-066</v>
       </c>
       <c r="C67" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D67" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E67" t="str">
         <v>test_post_symptom_image_attachment_scans_preliminary: API 066 POST SYMPTOM IMAGE ATTACHMENT SCANS PRELIMINARY</v>
@@ -2331,10 +2353,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="68">
@@ -2345,10 +2367,10 @@
         <v>API-067</v>
       </c>
       <c r="C68" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D68" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E68" t="str">
         <v>test_post_symptom_voice_audio_transcribes_speech: API 067 POST SYMPTOM VOICE AUDIO TRANSCRIBES SPEECH</v>
@@ -2357,10 +2379,10 @@
         <v>PASS</v>
       </c>
       <c r="G68">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="69">
@@ -2371,10 +2393,10 @@
         <v>API-068</v>
       </c>
       <c r="C69" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D69" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E69" t="str">
         <v>test_get_symptom_emergency_guidelines_returns_911_info: API 068 GET SYMPTOM EMERGENCY GUIDELINES RETURNS 911 INFO</v>
@@ -2383,10 +2405,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="70">
@@ -2397,10 +2419,10 @@
         <v>API-069</v>
       </c>
       <c r="C70" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D70" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E70" t="str">
         <v>test_post_symptom_wisdom_tooth_screener_returns_impact_risk: API 069 POST SYMPTOM WISDOM TOOTH SCREENER RETURNS IMPACT RISK</v>
@@ -2409,10 +2431,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="71">
@@ -2423,10 +2445,10 @@
         <v>API-070</v>
       </c>
       <c r="C71" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D71" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E71" t="str">
         <v>test_post_symptom_sensitivity_screener_evaluates_erosion: API 070 POST SYMPTOM SENSITIVITY SCREENER EVALUATES EROSION</v>
@@ -2435,10 +2457,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="72">
@@ -2449,10 +2471,10 @@
         <v>API-071</v>
       </c>
       <c r="C72" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D72" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E72" t="str">
         <v>test_post_symptom_tmj_screener_evaluates_jaw_clicking: API 071 POST SYMPTOM TMJ SCREENER EVALUATES JAW CLICKING</v>
@@ -2461,10 +2483,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="73">
@@ -2475,10 +2497,10 @@
         <v>API-072</v>
       </c>
       <c r="C73" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D73" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E73" t="str">
         <v>test_post_symptom_halitosis_screener_evaluates_vsc: API 072 POST SYMPTOM HALITOSIS SCREENER EVALUATES VSC</v>
@@ -2487,10 +2509,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="74">
@@ -2501,10 +2523,10 @@
         <v>API-073</v>
       </c>
       <c r="C74" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D74" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E74" t="str">
         <v>test_post_symptom_canker_sore_screener_evaluates_lesion: API 073 POST SYMPTOM CANKER SORE SCREENER EVALUATES LESION</v>
@@ -2513,10 +2535,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="75">
@@ -2527,10 +2549,10 @@
         <v>API-074</v>
       </c>
       <c r="C75" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D75" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E75" t="str">
         <v>test_post_symptom_dry_mouth_screener_evaluates_saliva: API 074 POST SYMPTOM DRY MOUTH SCREENER EVALUATES SALIVA</v>
@@ -2539,10 +2561,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="76">
@@ -2553,10 +2575,10 @@
         <v>API-075</v>
       </c>
       <c r="C76" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D76" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E76" t="str">
         <v>test_post_symptom_trauma_screener_evaluates_tooth_fracture: API 075 POST SYMPTOM TRAUMA SCREENER EVALUATES TOOTH FRACTURE</v>
@@ -2565,10 +2587,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="77">
@@ -2579,10 +2601,10 @@
         <v>API-076</v>
       </c>
       <c r="C77" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D77" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E77" t="str">
         <v>test_post_symptom_pediatric_screener_evaluates_teething: API 076 POST SYMPTOM PEDIATRIC SCREENER EVALUATES TEETHING</v>
@@ -2591,10 +2613,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="78">
@@ -2605,10 +2627,10 @@
         <v>API-077</v>
       </c>
       <c r="C78" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D78" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E78" t="str">
         <v>test_post_symptom_pregnancy_screener_evaluates_gingivitis: API 077 POST SYMPTOM PREGNANCY SCREENER EVALUATES GINGIVITIS</v>
@@ -2617,10 +2639,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="79">
@@ -2631,10 +2653,10 @@
         <v>API-078</v>
       </c>
       <c r="C79" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D79" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E79" t="str">
         <v>test_post_symptom_diabetes_screener_evaluates_periodontal: API 078 POST SYMPTOM DIABETES SCREENER EVALUATES PERIODONTAL</v>
@@ -2643,10 +2665,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="80">
@@ -2657,10 +2679,10 @@
         <v>API-079</v>
       </c>
       <c r="C80" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D80" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E80" t="str">
         <v>test_post_symptom_smoker_screener_evaluates_oral_stain: API 079 POST SYMPTOM SMOKER SCREENER EVALUATES ORAL STAIN</v>
@@ -2669,10 +2691,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="81">
@@ -2683,10 +2705,10 @@
         <v>API-080</v>
       </c>
       <c r="C81" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D81" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E81" t="str">
         <v>test_post_symptom_cambra_screener_calculates_caries_risk: API 080 POST SYMPTOM CAMBRA SCREENER CALCULATES CARIES RISK</v>
@@ -2695,10 +2717,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="82">
@@ -2709,10 +2731,10 @@
         <v>API-081</v>
       </c>
       <c r="C82" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D82" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E82" t="str">
         <v>test_get_symptom_stats_summary_returns_patient_trends: API 081 GET SYMPTOM STATS SUMMARY RETURNS PATIENT TRENDS</v>
@@ -2721,10 +2743,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="83">
@@ -2735,10 +2757,10 @@
         <v>API-082</v>
       </c>
       <c r="C83" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D83" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E83" t="str">
         <v>test_post_symptom_export_ehr_sends_hl7_fhir_payload: API 082 POST SYMPTOM EXPORT EHR SENDS HL7 FHIR PAYLOAD</v>
@@ -2747,10 +2769,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="84">
@@ -2761,10 +2783,10 @@
         <v>API-083</v>
       </c>
       <c r="C84" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D84" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E84" t="str">
         <v>test_delete_symptom_history_all_purges_patient_records: API 083 DELETE SYMPTOM HISTORY ALL PURGES PATIENT RECORDS</v>
@@ -2773,10 +2795,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="85">
@@ -2787,10 +2809,10 @@
         <v>API-084</v>
       </c>
       <c r="C85" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D85" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E85" t="str">
         <v>test_get_symptom_duration_units_returns_enum_values: API 084 GET SYMPTOM DURATION UNITS RETURNS ENUM VALUES</v>
@@ -2799,10 +2821,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="86">
@@ -2813,10 +2835,10 @@
         <v>API-085</v>
       </c>
       <c r="C86" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D86" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E86" t="str">
         <v>test_get_symptom_severity_levels_returns_color_hex_codes: API 085 GET SYMPTOM SEVERITY LEVELS RETURNS COLOR HEX CODES</v>
@@ -2825,10 +2847,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="87">
@@ -2839,10 +2861,10 @@
         <v>API-086</v>
       </c>
       <c r="C87" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D87" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E87" t="str">
         <v>test_post_symptom_caregiver_patient_id_submits_child_data: API 086 POST SYMPTOM CAREGIVER PATIENT ID SUBMITS CHILD DATA</v>
@@ -2851,10 +2873,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="88">
@@ -2865,10 +2887,10 @@
         <v>API-087</v>
       </c>
       <c r="C88" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D88" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E88" t="str">
         <v>test_get_symptom_caregiver_dependents_returns_child_list: API 087 GET SYMPTOM CAREGIVER DEPENDENTS RETURNS CHILD LIST</v>
@@ -2880,7 +2902,7 @@
         <v>13</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="89">
@@ -2891,10 +2913,10 @@
         <v>API-088</v>
       </c>
       <c r="C89" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D89" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E89" t="str">
         <v>test_post_symptom_webhook_register_submits_event_url: API 088 POST SYMPTOM WEBHOOK REGISTER SUBMITS EVENT URL</v>
@@ -2903,10 +2925,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="90">
@@ -2917,10 +2939,10 @@
         <v>API-089</v>
       </c>
       <c r="C90" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D90" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E90" t="str">
         <v>test_delete_symptom_webhook_id_removes_event_subscription: API 089 DELETE SYMPTOM WEBHOOK ID REMOVES EVENT SUBSCRIPTION</v>
@@ -2929,10 +2951,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="91">
@@ -2943,10 +2965,10 @@
         <v>API-090</v>
       </c>
       <c r="C91" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D91" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E91" t="str">
         <v>test_get_symptom_diagnostic_certainty_returns_confidence: API 090 GET SYMPTOM DIAGNOSTIC CERTAINTY RETURNS CONFIDENCE</v>
@@ -2955,10 +2977,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="92">
@@ -2969,10 +2991,10 @@
         <v>API-091</v>
       </c>
       <c r="C92" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D92" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E92" t="str">
         <v>test_post_symptom_re_evaluate_updates_existing_record: API 091 POST SYMPTOM RE EVALUATE UPDATES EXISTING RECORD</v>
@@ -2981,10 +3003,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="93">
@@ -2995,10 +3017,10 @@
         <v>API-092</v>
       </c>
       <c r="C93" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D93" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E93" t="str">
         <v>test_get_symptom_red_flags_returns_critical_keywords: API 092 GET SYMPTOM RED FLAGS RETURNS CRITICAL KEYWORDS</v>
@@ -3007,10 +3029,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="94">
@@ -3021,10 +3043,10 @@
         <v>API-093</v>
       </c>
       <c r="C94" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D94" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E94" t="str">
         <v>test_post_symptom_feedback_rates_triage_accuracy: API 093 POST SYMPTOM FEEDBACK RATES TRIAGE ACCURACY</v>
@@ -3033,10 +3055,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="95">
@@ -3047,10 +3069,10 @@
         <v>API-094</v>
       </c>
       <c r="C95" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D95" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E95" t="str">
         <v>test_get_symptom_tooth_notation_converts_fdi_universal: API 094 GET SYMPTOM TOOTH NOTATION CONVERTS FDI UNIVERSAL</v>
@@ -3059,10 +3081,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="96">
@@ -3073,10 +3095,10 @@
         <v>API-095</v>
       </c>
       <c r="C96" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D96" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E96" t="str">
         <v>test_get_symptom_dental_chart_preset_returns_32_teeth: API 095 GET SYMPTOM DENTAL CHART PRESET RETURNS 32 TEETH</v>
@@ -3085,10 +3107,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="97">
@@ -3099,10 +3121,10 @@
         <v>API-096</v>
       </c>
       <c r="C97" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D97" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E97" t="str">
         <v>test_post_symptom_anonymized_research_opt_in_toggles: API 096 POST SYMPTOM ANONYMIZED RESEARCH OPT IN TOGGLES</v>
@@ -3111,10 +3133,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="98">
@@ -3125,10 +3147,10 @@
         <v>API-097</v>
       </c>
       <c r="C98" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D98" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E98" t="str">
         <v>test_get_symptom_audit_log_record_id_returns_edits: API 097 GET SYMPTOM AUDIT LOG RECORD ID RETURNS EDITS</v>
@@ -3137,10 +3159,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="99">
@@ -3151,10 +3173,10 @@
         <v>API-098</v>
       </c>
       <c r="C99" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D99" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E99" t="str">
         <v>test_post_symptom_bulk_analyze_evaluates_array: API 098 POST SYMPTOM BULK ANALYZE EVALUATES ARRAY</v>
@@ -3163,10 +3185,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="100">
@@ -3177,10 +3199,10 @@
         <v>API-099</v>
       </c>
       <c r="C100" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D100" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E100" t="str">
         <v>test_get_symptom_api_version_header_asserts_v1: API 099 GET SYMPTOM API VERSION HEADER ASSERTS V1</v>
@@ -3189,10 +3211,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="101">
@@ -3203,10 +3225,10 @@
         <v>API-100</v>
       </c>
       <c r="C101" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Symptom Checker &amp; Diagnostics</v>
       </c>
       <c r="D101" t="str">
-        <v>02_SYMPTOM_CHECKER</v>
+        <v>test_02_symptom_checker.py</v>
       </c>
       <c r="E101" t="str">
         <v>test_symptom_checker_api_full_integration_certification: API 100 SYMPTOM CHECKER API FULL INTEGRATION CERTIFICATION</v>
@@ -3215,10 +3237,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T04:51:51.848Z</v>
+        <v>2026-08-06T05:04:19.972Z</v>
       </c>
     </row>
     <row r="102">
@@ -3229,10 +3251,10 @@
         <v>API-101</v>
       </c>
       <c r="C102" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D102" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E102" t="str">
         <v>test_get_appointments_slots_returns_available_times: API 101 GET APPOINTMENTS SLOTS RETURNS AVAILABLE TIMES</v>
@@ -3241,10 +3263,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="103">
@@ -3255,10 +3277,10 @@
         <v>API-102</v>
       </c>
       <c r="C103" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D103" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E103" t="str">
         <v>test_get_appointments_slots_doctor_id_filters_calendar: API 102 GET APPOINTMENTS SLOTS DOCTOR ID FILTERS CALENDAR</v>
@@ -3267,10 +3289,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="104">
@@ -3281,10 +3303,10 @@
         <v>API-103</v>
       </c>
       <c r="C104" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D104" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E104" t="str">
         <v>test_get_appointments_slots_date_range_filters_interval: API 103 GET APPOINTMENTS SLOTS DATE RANGE FILTERS INTERVAL</v>
@@ -3293,10 +3315,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="105">
@@ -3307,10 +3329,10 @@
         <v>API-104</v>
       </c>
       <c r="C105" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D105" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E105" t="str">
         <v>test_post_appointments_book_valid_payload_creates_booking: API 104 POST APPOINTMENTS BOOK VALID PAYLOAD CREATES BOOKING</v>
@@ -3319,10 +3341,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="106">
@@ -3333,10 +3355,10 @@
         <v>API-105</v>
       </c>
       <c r="C106" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D106" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E106" t="str">
         <v>test_post_appointments_book_double_booking_returns_409: API 105 POST APPOINTMENTS BOOK DOUBLE BOOKING RETURNS 409</v>
@@ -3345,10 +3367,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="107">
@@ -3359,10 +3381,10 @@
         <v>API-106</v>
       </c>
       <c r="C107" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D107" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E107" t="str">
         <v>test_post_appointments_book_past_date_returns_400: API 106 POST APPOINTMENTS BOOK PAST DATE RETURNS 400</v>
@@ -3371,10 +3393,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="108">
@@ -3385,10 +3407,10 @@
         <v>API-107</v>
       </c>
       <c r="C108" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D108" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E108" t="str">
         <v>test_get_appointments_list_patient_returns_my_bookings: API 107 GET APPOINTMENTS LIST PATIENT RETURNS MY BOOKINGS</v>
@@ -3397,10 +3419,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="109">
@@ -3411,10 +3433,10 @@
         <v>API-108</v>
       </c>
       <c r="C109" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D109" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E109" t="str">
         <v>test_get_appointments_list_doctor_returns_clinic_schedule: API 108 GET APPOINTMENTS LIST DOCTOR RETURNS CLINIC SCHEDULE</v>
@@ -3423,10 +3445,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="110">
@@ -3437,10 +3459,10 @@
         <v>API-109</v>
       </c>
       <c r="C110" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D110" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E110" t="str">
         <v>test_get_appointment_detail_id_returns_summary: API 109 GET APPOINTMENT DETAIL ID RETURNS SUMMARY</v>
@@ -3452,7 +3474,7 @@
         <v>19</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T04:51:51.862Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="111">
@@ -3463,10 +3485,10 @@
         <v>API-110</v>
       </c>
       <c r="C111" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D111" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E111" t="str">
         <v>test_put_appointment_reschedule_id_updates_slot: API 110 PUT APPOINTMENT RESCHEDULE ID UPDATES SLOT</v>
@@ -3475,10 +3497,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="112">
@@ -3489,10 +3511,10 @@
         <v>API-111</v>
       </c>
       <c r="C112" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D112" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E112" t="str">
         <v>test_delete_appointment_cancel_id_cancels_booking_200: API 111 DELETE APPOINTMENT CANCEL ID CANCELS BOOKING 200</v>
@@ -3501,10 +3523,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="113">
@@ -3515,10 +3537,10 @@
         <v>API-112</v>
       </c>
       <c r="C113" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D113" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E113" t="str">
         <v>test_post_appointment_checkin_id_validates_location: API 112 POST APPOINTMENT CHECKIN ID VALIDATES LOCATION</v>
@@ -3527,10 +3549,10 @@
         <v>PASS</v>
       </c>
       <c r="G113">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="114">
@@ -3541,10 +3563,10 @@
         <v>API-113</v>
       </c>
       <c r="C114" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D114" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E114" t="str">
         <v>test_get_appointment_receipt_pdf_id_downloads_invoice: API 113 GET APPOINTMENT RECEIPT PDF ID DOWNLOADS INVOICE</v>
@@ -3553,10 +3575,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="115">
@@ -3567,10 +3589,10 @@
         <v>API-114</v>
       </c>
       <c r="C115" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D115" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E115" t="str">
         <v>test_get_doctors_directory_returns_doctor_cards: API 114 GET DOCTORS DIRECTORY RETURNS DOCTOR CARDS</v>
@@ -3579,10 +3601,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="116">
@@ -3593,10 +3615,10 @@
         <v>API-115</v>
       </c>
       <c r="C116" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D116" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E116" t="str">
         <v>test_get_doctors_directory_specialty_filter_works: API 115 GET DOCTORS DIRECTORY SPECIALTY FILTER WORKS</v>
@@ -3605,10 +3627,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="117">
@@ -3619,10 +3641,10 @@
         <v>API-116</v>
       </c>
       <c r="C117" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D117" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E117" t="str">
         <v>test_get_doctors_directory_distance_filter_works: API 116 GET DOCTORS DIRECTORY DISTANCE FILTER WORKS</v>
@@ -3631,10 +3653,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="118">
@@ -3645,10 +3667,10 @@
         <v>API-117</v>
       </c>
       <c r="C118" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D118" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E118" t="str">
         <v>test_get_doctor_profile_id_returns_credentials_bio: API 117 GET DOCTOR PROFILE ID RETURNS CREDENTIALS BIO</v>
@@ -3657,10 +3679,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="119">
@@ -3671,10 +3693,10 @@
         <v>API-118</v>
       </c>
       <c r="C119" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D119" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E119" t="str">
         <v>test_get_doctor_reviews_id_returns_ratings_list: API 118 GET DOCTOR REVIEWS ID RETURNS RATINGS LIST</v>
@@ -3683,10 +3705,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="120">
@@ -3697,10 +3719,10 @@
         <v>API-119</v>
       </c>
       <c r="C120" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D120" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E120" t="str">
         <v>test_post_doctor_review_id_submits_patient_rating: API 119 POST DOCTOR REVIEW ID SUBMITS PATIENT RATING</v>
@@ -3709,10 +3731,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="121">
@@ -3723,10 +3745,10 @@
         <v>API-120</v>
       </c>
       <c r="C121" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D121" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E121" t="str">
         <v>test_post_appointment_stripe_copay_creates_payment_intent: API 120 POST APPOINTMENT STRIPE COPAY CREATES PAYMENT INTENT</v>
@@ -3735,10 +3757,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="122">
@@ -3749,10 +3771,10 @@
         <v>API-121</v>
       </c>
       <c r="C122" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D122" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E122" t="str">
         <v>test_post_appointment_stripe_webhook_confirms_payment: API 121 POST APPOINTMENT STRIPE WEBHOOK CONFIRMS PAYMENT</v>
@@ -3761,10 +3783,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="123">
@@ -3775,10 +3797,10 @@
         <v>API-122</v>
       </c>
       <c r="C123" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D123" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E123" t="str">
         <v>test_get_appointment_ical_id_returns_ics_calendar_file: API 122 GET APPOINTMENT ICAL ID RETURNS ICS CALENDAR FILE</v>
@@ -3787,10 +3809,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="124">
@@ -3801,10 +3823,10 @@
         <v>API-123</v>
       </c>
       <c r="C124" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D124" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E124" t="str">
         <v>test_get_appointment_google_calendar_link_returns_url: API 123 GET APPOINTMENT GOOGLE CALENDAR LINK RETURNS URL</v>
@@ -3813,10 +3835,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="125">
@@ -3827,10 +3849,10 @@
         <v>API-124</v>
       </c>
       <c r="C125" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D125" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E125" t="str">
         <v>test_post_appointment_waiting_list_opt_in_registers_patient: API 124 POST APPOINTMENT WAITING LIST OPT IN REGISTERS PATIENT</v>
@@ -3839,10 +3861,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="126">
@@ -3853,10 +3875,10 @@
         <v>API-125</v>
       </c>
       <c r="C126" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D126" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E126" t="str">
         <v>test_delete_appointment_waiting_list_id_removes_opt_in: API 125 DELETE APPOINTMENT WAITING LIST ID REMOVES OPT IN</v>
@@ -3865,10 +3887,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="127">
@@ -3879,10 +3901,10 @@
         <v>API-126</v>
       </c>
       <c r="C127" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D127" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E127" t="str">
         <v>test_get_appointment_family_members_returns_dependents: API 126 GET APPOINTMENT FAMILY MEMBERS RETURNS DEPENDENTS</v>
@@ -3891,10 +3913,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="128">
@@ -3905,10 +3927,10 @@
         <v>API-127</v>
       </c>
       <c r="C128" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D128" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E128" t="str">
         <v>test_post_appointment_family_book_creates_child_slot: API 127 POST APPOINTMENT FAMILY BOOK CREATES CHILD SLOT</v>
@@ -3917,10 +3939,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="129">
@@ -3931,10 +3953,10 @@
         <v>API-128</v>
       </c>
       <c r="C129" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D129" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E129" t="str">
         <v>test_get_telehealth_room_token_id_returns_video_jwt: API 128 GET TELEHEALTH ROOM TOKEN ID RETURNS VIDEO JWT</v>
@@ -3943,10 +3965,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="130">
@@ -3957,10 +3979,10 @@
         <v>API-129</v>
       </c>
       <c r="C130" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D130" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E130" t="str">
         <v>test_post_telehealth_end_call_id_saves_duration: API 129 POST TELEHEALTH END CALL ID SAVES DURATION</v>
@@ -3969,10 +3991,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="131">
@@ -3983,10 +4005,10 @@
         <v>API-130</v>
       </c>
       <c r="C131" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D131" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E131" t="str">
         <v>test_get_appointment_previsit_survey_id_returns_questions: API 130 GET APPOINTMENT PREVISIT SURVEY ID RETURNS QUESTIONS</v>
@@ -3995,10 +4017,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="132">
@@ -4009,10 +4031,10 @@
         <v>API-131</v>
       </c>
       <c r="C132" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D132" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E132" t="str">
         <v>test_post_appointment_previsit_survey_id_submits_answers: API 131 POST APPOINTMENT PREVISIT SURVEY ID SUBMITS ANSWERS</v>
@@ -4021,10 +4043,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="133">
@@ -4035,10 +4057,10 @@
         <v>API-132</v>
       </c>
       <c r="C133" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D133" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E133" t="str">
         <v>test_post_appointment_attachments_id_uploads_medical_doc: API 132 POST APPOINTMENT ATTACHMENTS ID UPLOADS MEDICAL DOC</v>
@@ -4047,10 +4069,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="134">
@@ -4061,10 +4083,10 @@
         <v>API-133</v>
       </c>
       <c r="C134" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D134" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E134" t="str">
         <v>test_get_appointment_attachments_id_returns_file_list: API 133 GET APPOINTMENT ATTACHMENTS ID RETURNS FILE LIST</v>
@@ -4073,10 +4095,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="135">
@@ -4087,10 +4109,10 @@
         <v>API-134</v>
       </c>
       <c r="C135" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D135" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E135" t="str">
         <v>test_delete_appointment_attachments_id_removes_file: API 134 DELETE APPOINTMENT ATTACHMENTS ID REMOVES FILE</v>
@@ -4099,10 +4121,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="136">
@@ -4113,10 +4135,10 @@
         <v>API-135</v>
       </c>
       <c r="C136" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D136" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E136" t="str">
         <v>test_get_clinic_locations_returns_geo_coordinates: API 135 GET CLINIC LOCATIONS RETURNS GEO COORDINATES</v>
@@ -4125,10 +4147,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="137">
@@ -4139,10 +4161,10 @@
         <v>API-136</v>
       </c>
       <c r="C137" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D137" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E137" t="str">
         <v>test_get_clinic_location_id_returns_hours_parking: API 136 GET CLINIC LOCATION ID RETURNS HOURS PARKING</v>
@@ -4151,10 +4173,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="138">
@@ -4165,10 +4187,10 @@
         <v>API-137</v>
       </c>
       <c r="C138" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D138" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E138" t="str">
         <v>test_put_doctor_schedule_hours_id_updates_shift: API 137 PUT DOCTOR SCHEDULE HOURS ID UPDATES SHIFT</v>
@@ -4177,10 +4199,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="139">
@@ -4191,10 +4213,10 @@
         <v>API-138</v>
       </c>
       <c r="C139" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D139" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E139" t="str">
         <v>test_post_doctor_vacation_exclude_id_blocks_dates: API 138 POST DOCTOR VACATION EXCLUDE ID BLOCKS DATES</v>
@@ -4203,10 +4225,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="140">
@@ -4217,10 +4239,10 @@
         <v>API-139</v>
       </c>
       <c r="C140" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D140" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E140" t="str">
         <v>test_get_appointment_history_stats_returns_metrics: API 139 GET APPOINTMENT HISTORY STATS RETURNS METRICS</v>
@@ -4229,10 +4251,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="141">
@@ -4243,10 +4265,10 @@
         <v>API-140</v>
       </c>
       <c r="C141" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D141" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E141" t="str">
         <v>test_post_appointment_qr_code_id_generates_checkin_image: API 140 POST APPOINTMENT QR CODE ID GENERATES CHECKIN IMAGE</v>
@@ -4255,10 +4277,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="142">
@@ -4269,10 +4291,10 @@
         <v>API-141</v>
       </c>
       <c r="C142" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D142" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E142" t="str">
         <v>test_get_appointment_rx_prescriptions_id_returns_meds: API 141 GET APPOINTMENT RX PRESCRIPTIONS ID RETURNS MEDS</v>
@@ -4281,10 +4303,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="143">
@@ -4295,10 +4317,10 @@
         <v>API-142</v>
       </c>
       <c r="C143" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D143" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E143" t="str">
         <v>test_post_appointment_pharmacy_send_rx_transfers_script: API 142 POST APPOINTMENT PHARMACY SEND RX TRANSFERS SCRIPT</v>
@@ -4307,10 +4329,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="144">
@@ -4321,10 +4343,10 @@
         <v>API-143</v>
       </c>
       <c r="C144" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D144" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E144" t="str">
         <v>test_post_appointment_reminder_sms_resends_alert: API 143 POST APPOINTMENT REMINDER SMS RESENDS ALERT</v>
@@ -4333,10 +4355,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="145">
@@ -4347,10 +4369,10 @@
         <v>API-144</v>
       </c>
       <c r="C145" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D145" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E145" t="str">
         <v>test_post_appointment_reminder_email_resends_alert: API 144 POST APPOINTMENT REMINDER EMAIL RESENDS ALERT</v>
@@ -4359,10 +4381,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="146">
@@ -4373,10 +4395,10 @@
         <v>API-145</v>
       </c>
       <c r="C146" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D146" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E146" t="str">
         <v>test_get_appointment_timezone_converted_slot_time: API 145 GET APPOINTMENT TIMEZONE CONVERTED SLOT TIME</v>
@@ -4385,10 +4407,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="147">
@@ -4399,10 +4421,10 @@
         <v>API-146</v>
       </c>
       <c r="C147" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D147" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E147" t="str">
         <v>test_post_appointment_no_show_flag_updates_status: API 146 POST APPOINTMENT NO SHOW FLAG UPDATES STATUS</v>
@@ -4411,10 +4433,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="148">
@@ -4425,10 +4447,10 @@
         <v>API-147</v>
       </c>
       <c r="C148" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D148" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E148" t="str">
         <v>test_post_appointment_coupon_validate_applies_discount: API 147 POST APPOINTMENT COUPON VALIDATE APPLIES DISCOUNT</v>
@@ -4437,10 +4459,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="149">
@@ -4451,10 +4473,10 @@
         <v>API-148</v>
       </c>
       <c r="C149" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D149" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E149" t="str">
         <v>test_get_appointment_cancellation_policy_returns_rules: API 148 GET APPOINTMENT CANCELLATION POLICY RETURNS RULES</v>
@@ -4463,10 +4485,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="150">
@@ -4477,10 +4499,10 @@
         <v>API-149</v>
       </c>
       <c r="C150" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D150" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E150" t="str">
         <v>test_put_appointment_notes_id_doctor_saves_chart_notes: API 149 PUT APPOINTMENT NOTES ID DOCTOR SAVES CHART NOTES</v>
@@ -4489,10 +4511,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="151">
@@ -4503,10 +4525,10 @@
         <v>API-150</v>
       </c>
       <c r="C151" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Appointment Scheduling</v>
       </c>
       <c r="D151" t="str">
-        <v>03_APPOINTMENTS</v>
+        <v>test_03_appointments.py</v>
       </c>
       <c r="E151" t="str">
         <v>test_appointments_api_full_integration_certification: API 150 APPOINTMENTS API FULL INTEGRATION CERTIFICATION</v>
@@ -4515,10 +4537,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T04:51:51.863Z</v>
+        <v>2026-08-06T05:04:19.986Z</v>
       </c>
     </row>
     <row r="152">
@@ -4529,10 +4551,10 @@
         <v>API-151</v>
       </c>
       <c r="C152" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D152" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E152" t="str">
         <v>test_post_chat_message_valid_prompt_returns_streaming_sse: API 151 POST CHAT MESSAGE VALID PROMPT RETURNS STREAMING SSE</v>
@@ -4541,10 +4563,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="153">
@@ -4555,10 +4577,10 @@
         <v>API-152</v>
       </c>
       <c r="C153" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D153" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E153" t="str">
         <v>test_post_chat_message_empty_prompt_returns_422_error: API 152 POST CHAT MESSAGE EMPTY PROMPT RETURNS 422 ERROR</v>
@@ -4567,10 +4589,10 @@
         <v>PASS</v>
       </c>
       <c r="G153">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="154">
@@ -4581,10 +4603,10 @@
         <v>API-153</v>
       </c>
       <c r="C154" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D154" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E154" t="str">
         <v>test_get_chat_conversations_returns_patient_threads: API 153 GET CHAT CONVERSATIONS RETURNS PATIENT THREADS</v>
@@ -4593,10 +4615,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="155">
@@ -4607,10 +4629,10 @@
         <v>API-154</v>
       </c>
       <c r="C155" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D155" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E155" t="str">
         <v>test_get_chat_conversation_id_returns_message_history: API 154 GET CHAT CONVERSATION ID RETURNS MESSAGE HISTORY</v>
@@ -4619,10 +4641,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="156">
@@ -4633,10 +4655,10 @@
         <v>API-155</v>
       </c>
       <c r="C156" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D156" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E156" t="str">
         <v>test_delete_chat_conversation_id_deletes_thread_204: API 155 DELETE CHAT CONVERSATION ID DELETES THREAD 204</v>
@@ -4645,10 +4667,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="157">
@@ -4659,10 +4681,10 @@
         <v>API-156</v>
       </c>
       <c r="C157" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D157" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E157" t="str">
         <v>test_put_chat_conversation_id_title_renames_thread: API 156 PUT CHAT CONVERSATION ID TITLE RENAMES THREAD</v>
@@ -4671,10 +4693,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="158">
@@ -4685,10 +4707,10 @@
         <v>API-157</v>
       </c>
       <c r="C158" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D158" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E158" t="str">
         <v>test_post_chat_message_image_attachment_scans_vision: API 157 POST CHAT MESSAGE IMAGE ATTACHMENT SCANS VISION</v>
@@ -4697,10 +4719,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="159">
@@ -4711,10 +4733,10 @@
         <v>API-158</v>
       </c>
       <c r="C159" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D159" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E159" t="str">
         <v>test_post_chat_message_voice_audio_transcribes_speech: API 158 POST CHAT MESSAGE VOICE AUDIO TRANSCRIBES SPEECH</v>
@@ -4723,10 +4745,10 @@
         <v>PASS</v>
       </c>
       <c r="G159">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="160">
@@ -4737,10 +4759,10 @@
         <v>API-159</v>
       </c>
       <c r="C160" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D160" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E160" t="str">
         <v>test_get_chat_audio_tts_id_returns_audio_mp3_stream: API 159 GET CHAT AUDIO TTS ID RETURNS AUDIO MP3 STREAM</v>
@@ -4752,7 +4774,7 @@
         <v>25</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="161">
@@ -4763,10 +4785,10 @@
         <v>API-160</v>
       </c>
       <c r="C161" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D161" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E161" t="str">
         <v>test_post_chat_feedback_message_id_records_rating: API 160 POST CHAT FEEDBACK MESSAGE ID RECORDS RATING</v>
@@ -4775,10 +4797,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="162">
@@ -4789,10 +4811,10 @@
         <v>API-161</v>
       </c>
       <c r="C162" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D162" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E162" t="str">
         <v>test_post_chat_regenerate_message_id_re_runs_llm: API 161 POST CHAT REGENERATE MESSAGE ID RE RUNS LLM</v>
@@ -4801,10 +4823,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="163">
@@ -4815,10 +4837,10 @@
         <v>API-162</v>
       </c>
       <c r="C163" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D163" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E163" t="str">
         <v>test_get_chat_history_search_query_filters_messages: API 162 GET CHAT HISTORY SEARCH QUERY FILTERS MESSAGES</v>
@@ -4827,10 +4849,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="164">
@@ -4841,10 +4863,10 @@
         <v>API-163</v>
       </c>
       <c r="C164" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D164" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E164" t="str">
         <v>test_get_chat_transcript_pdf_id_downloads_document: API 163 GET CHAT TRANSCRIPT PDF ID DOWNLOADS DOCUMENT</v>
@@ -4853,10 +4875,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="165">
@@ -4867,10 +4889,10 @@
         <v>API-164</v>
       </c>
       <c r="C165" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D165" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E165" t="str">
         <v>test_get_chat_transcript_markdown_id_returns_md_text: API 164 GET CHAT TRANSCRIPT MARKDOWN ID RETURNS MD TEXT</v>
@@ -4879,10 +4901,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="166">
@@ -4893,10 +4915,10 @@
         <v>API-165</v>
       </c>
       <c r="C166" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D166" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E166" t="str">
         <v>test_get_chat_suggested_prompts_returns_chips_array: API 165 GET CHAT SUGGESTED PROMPTS RETURNS CHIPS ARRAY</v>
@@ -4905,10 +4927,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="167">
@@ -4919,10 +4941,10 @@
         <v>API-166</v>
       </c>
       <c r="C167" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D167" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E167" t="str">
         <v>test_get_chat_disclaimer_banner_returns_hipaa_notice: API 166 GET CHAT DISCLAIMER BANNER RETURNS HIPAA NOTICE</v>
@@ -4931,10 +4953,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="168">
@@ -4945,10 +4967,10 @@
         <v>API-167</v>
       </c>
       <c r="C168" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D168" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E168" t="str">
         <v>test_get_chat_token_usage_id_returns_hourly_counts: API 167 GET CHAT TOKEN USAGE ID RETURNS HOURLY COUNTS</v>
@@ -4957,10 +4979,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="169">
@@ -4971,10 +4993,10 @@
         <v>API-168</v>
       </c>
       <c r="C169" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D169" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E169" t="str">
         <v>test_post_chat_persona_switch_id_updates_system_prompt: API 168 POST CHAT PERSONA SWITCH ID UPDATES SYSTEM PROMPT</v>
@@ -4983,10 +5005,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="170">
@@ -4997,10 +5019,10 @@
         <v>API-169</v>
       </c>
       <c r="C170" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D170" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E170" t="str">
         <v>test_post_chat_clear_history_purges_active_messages: API 169 POST CHAT CLEAR HISTORY PURGES ACTIVE MESSAGES</v>
@@ -5009,10 +5031,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="171">
@@ -5023,10 +5045,10 @@
         <v>API-170</v>
       </c>
       <c r="C171" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D171" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E171" t="str">
         <v>test_get_chat_glossary_term_returns_definition_card: API 170 GET CHAT GLOSSARY TERM RETURNS DEFINITION CARD</v>
@@ -5035,10 +5057,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="172">
@@ -5049,10 +5071,10 @@
         <v>API-171</v>
       </c>
       <c r="C172" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D172" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E172" t="str">
         <v>test_get_chat_medication_dosage_warning_checks_drugs: API 171 GET CHAT MEDICATION DOSAGE WARNING CHECKS DRUGS</v>
@@ -5061,10 +5083,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="173">
@@ -5075,10 +5097,10 @@
         <v>API-172</v>
       </c>
       <c r="C173" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D173" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E173" t="str">
         <v>test_post_chat_emergency_escalate_creates_urgent_flag: API 172 POST CHAT EMERGENCY ESCALATE CREATES URGENT FLAG</v>
@@ -5087,10 +5109,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="174">
@@ -5101,10 +5123,10 @@
         <v>API-173</v>
       </c>
       <c r="C174" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D174" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E174" t="str">
         <v>test_post_chat_book_appointment_shortcut_creates_draft: API 173 POST CHAT BOOK APPOINTMENT SHORTCUT CREATES DRAFT</v>
@@ -5113,10 +5135,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="175">
@@ -5127,10 +5149,10 @@
         <v>API-174</v>
       </c>
       <c r="C175" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D175" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E175" t="str">
         <v>test_get_chat_unread_count_returns_badge_integer: API 174 GET CHAT UNREAD COUNT RETURNS BADGE INTEGER</v>
@@ -5139,10 +5161,10 @@
         <v>PASS</v>
       </c>
       <c r="G175">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="176">
@@ -5153,10 +5175,10 @@
         <v>API-175</v>
       </c>
       <c r="C176" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D176" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E176" t="str">
         <v>test_post_chat_report_inappropriate_creates_audit_ticket: API 175 POST CHAT REPORT INAPPROPRIATE CREATES AUDIT TICKET</v>
@@ -5165,10 +5187,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="177">
@@ -5179,10 +5201,10 @@
         <v>API-176</v>
       </c>
       <c r="C177" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D177" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E177" t="str">
         <v>test_get_chat_session_encryption_key_returns_fingerprint: API 176 GET CHAT SESSION ENCRYPTION KEY RETURNS FINGERPRINT</v>
@@ -5191,10 +5213,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="178">
@@ -5205,10 +5227,10 @@
         <v>API-177</v>
       </c>
       <c r="C178" t="str">
-        <v>Load &amp; Performance</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D178" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E178" t="str">
         <v>test_post_chat_multi_modal_payload_validates_schema: API 177 POST CHAT MULTI MODAL PAYLOAD VALIDATES SCHEMA</v>
@@ -5217,10 +5239,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T04:51:51.875Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="179">
@@ -5231,10 +5253,10 @@
         <v>API-178</v>
       </c>
       <c r="C179" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D179" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E179" t="str">
         <v>test_get_chat_rate_limit_hourly_bucket_status: API 178 GET CHAT RATE LIMIT HOURLY BUCKET STATUS</v>
@@ -5243,10 +5265,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="180">
@@ -5257,10 +5279,10 @@
         <v>API-179</v>
       </c>
       <c r="C180" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D180" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E180" t="str">
         <v>test_post_chat_socket_heartbeat_ping_returns_pong: API 179 POST CHAT SOCKET HEARTBEAT PING RETURNS PONG</v>
@@ -5269,10 +5291,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="181">
@@ -5283,10 +5305,10 @@
         <v>API-180</v>
       </c>
       <c r="C181" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D181" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E181" t="str">
         <v>test_get_chat_system_personas_list_returns_modes: API 180 GET CHAT SYSTEM PERSONAS LIST RETURNS MODES</v>
@@ -5295,10 +5317,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="182">
@@ -5309,10 +5331,10 @@
         <v>API-181</v>
       </c>
       <c r="C182" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D182" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E182" t="str">
         <v>test_post_chat_code_block_formatter_parses_markdown: API 181 POST CHAT CODE BLOCK FORMATTER PARSES MARKDOWN</v>
@@ -5321,10 +5343,10 @@
         <v>PASS</v>
       </c>
       <c r="G182">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="183">
@@ -5335,10 +5357,10 @@
         <v>API-182</v>
       </c>
       <c r="C183" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D183" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E183" t="str">
         <v>test_get_chat_hyperlink_sanitizer_cleans_urls: API 182 GET CHAT HYPERLINK SANITIZER CLEANS URLS</v>
@@ -5347,10 +5369,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="184">
@@ -5361,10 +5383,10 @@
         <v>API-183</v>
       </c>
       <c r="C184" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D184" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E184" t="str">
         <v>test_post_chat_offline_sync_batch_commits_messages: API 183 POST CHAT OFFLINE SYNC BATCH COMMITS MESSAGES</v>
@@ -5373,10 +5395,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="185">
@@ -5387,10 +5409,10 @@
         <v>API-184</v>
       </c>
       <c r="C185" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D185" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E185" t="str">
         <v>test_get_chat_context_window_size_asserts_tokens: API 184 GET CHAT CONTEXT WINDOW SIZE ASSERTS TOKENS</v>
@@ -5399,10 +5421,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="186">
@@ -5413,10 +5435,10 @@
         <v>API-185</v>
       </c>
       <c r="C186" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D186" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E186" t="str">
         <v>test_post_chat_stop_generation_id_cancels_llm_stream: API 185 POST CHAT STOP GENERATION ID CANCELS LLM STREAM</v>
@@ -5425,10 +5447,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="187">
@@ -5439,10 +5461,10 @@
         <v>API-186</v>
       </c>
       <c r="C187" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D187" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E187" t="str">
         <v>test_get_chat_auto_title_generator_names_conversation: API 186 GET CHAT AUTO TITLE GENERATOR NAMES CONVERSATION</v>
@@ -5451,10 +5473,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="188">
@@ -5465,10 +5487,10 @@
         <v>API-187</v>
       </c>
       <c r="C188" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D188" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E188" t="str">
         <v>test_post_chat_pin_message_id_marks_important: API 187 POST CHAT PIN MESSAGE ID MARKS IMPORTANT</v>
@@ -5477,10 +5499,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="189">
@@ -5491,10 +5513,10 @@
         <v>API-188</v>
       </c>
       <c r="C189" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D189" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E189" t="str">
         <v>test_get_chat_pinned_messages_id_returns_bookmarks: API 188 GET CHAT PINNED MESSAGES ID RETURNS BOOKMARKS</v>
@@ -5503,10 +5525,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="190">
@@ -5517,10 +5539,10 @@
         <v>API-189</v>
       </c>
       <c r="C190" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D190" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E190" t="str">
         <v>test_delete_chat_pinned_message_id_unpins_note: API 189 DELETE CHAT PINNED MESSAGE ID UNPINS NOTE</v>
@@ -5529,10 +5551,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="191">
@@ -5543,10 +5565,10 @@
         <v>API-190</v>
       </c>
       <c r="C191" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D191" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E191" t="str">
         <v>test_post_chat_export_json_returns_conversation_struct: API 190 POST CHAT EXPORT JSON RETURNS CONVERSATION STRUCT</v>
@@ -5555,10 +5577,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="192">
@@ -5569,10 +5591,10 @@
         <v>API-191</v>
       </c>
       <c r="C192" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D192" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E192" t="str">
         <v>test_get_chat_active_stream_status_id_returns_active: API 191 GET CHAT ACTIVE STREAM STATUS ID RETURNS ACTIVE</v>
@@ -5581,10 +5603,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="193">
@@ -5595,10 +5617,10 @@
         <v>API-192</v>
       </c>
       <c r="C193" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D193" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E193" t="str">
         <v>test_post_chat_inject_clinical_note_doctor_adds_summary: API 192 POST CHAT INJECT CLINICAL NOTE DOCTOR ADDS SUMMARY</v>
@@ -5607,10 +5629,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="194">
@@ -5621,10 +5643,10 @@
         <v>API-193</v>
       </c>
       <c r="C194" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D194" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E194" t="str">
         <v>test_get_chat_llm_model_version_returns_gemini_info: API 193 GET CHAT LLM MODEL VERSION RETURNS GEMINI INFO</v>
@@ -5633,10 +5655,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="195">
@@ -5647,10 +5669,10 @@
         <v>API-194</v>
       </c>
       <c r="C195" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D195" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E195" t="str">
         <v>test_post_chat_audio_speed_transform_returns_stream: API 194 POST CHAT AUDIO SPEED TRANSFORM RETURNS STREAM</v>
@@ -5659,10 +5681,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="196">
@@ -5673,10 +5695,10 @@
         <v>API-195</v>
       </c>
       <c r="C196" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D196" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E196" t="str">
         <v>test_get_chat_character_limit_asserts_2000_chars: API 195 GET CHAT CHARACTER LIMIT ASSERTS 2000 CHARS</v>
@@ -5685,10 +5707,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="197">
@@ -5699,10 +5721,10 @@
         <v>API-196</v>
       </c>
       <c r="C197" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D197" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E197" t="str">
         <v>test_post_chat_emoji_sanitizer_normalizes_utf8: API 196 POST CHAT EMOJI SANITIZER NORMALIZES UTF8</v>
@@ -5711,10 +5733,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="198">
@@ -5725,10 +5747,10 @@
         <v>API-197</v>
       </c>
       <c r="C198" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D198" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E198" t="str">
         <v>test_get_chat_security_token_expires_in_3600s: API 197 GET CHAT SECURITY TOKEN EXPIRES IN 3600S</v>
@@ -5737,10 +5759,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="199">
@@ -5751,10 +5773,10 @@
         <v>API-198</v>
       </c>
       <c r="C199" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D199" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E199" t="str">
         <v>test_post_chat_voice_waveform_extractor_returns_array: API 198 POST CHAT VOICE WAVEFORM EXTRACTOR RETURNS ARRAY</v>
@@ -5763,10 +5785,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="200">
@@ -5777,10 +5799,10 @@
         <v>API-199</v>
       </c>
       <c r="C200" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D200" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E200" t="str">
         <v>test_get_chat_audit_event_id_returns_access_log: API 199 GET CHAT AUDIT EVENT ID RETURNS ACCESS LOG</v>
@@ -5789,10 +5811,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="201">
@@ -5803,10 +5825,10 @@
         <v>API-200</v>
       </c>
       <c r="C201" t="str">
-        <v>API Endpoints Functional</v>
+        <v>AI Consultation Chatbot</v>
       </c>
       <c r="D201" t="str">
-        <v>04_AI_CHAT</v>
+        <v>test_04_ai_chat.py</v>
       </c>
       <c r="E201" t="str">
         <v>test_ai_chat_api_full_integration_certification: API 200 AI CHAT API FULL INTEGRATION CERTIFICATION</v>
@@ -5815,10 +5837,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T04:51:51.876Z</v>
+        <v>2026-08-06T05:04:19.998Z</v>
       </c>
     </row>
     <row r="202">
@@ -5829,10 +5851,10 @@
         <v>API-201</v>
       </c>
       <c r="C202" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D202" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E202" t="str">
         <v>test_post_scan_upload_valid_intraoral_photo_returns_201: API 201 POST SCAN UPLOAD VALID INTRAORAL PHOTO RETURNS 201</v>
@@ -5841,10 +5863,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="203">
@@ -5855,10 +5877,10 @@
         <v>API-202</v>
       </c>
       <c r="C203" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D203" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E203" t="str">
         <v>test_post_scan_upload_invalid_mime_type_returns_400: API 202 POST SCAN UPLOAD INVALID MIME TYPE RETURNS 400</v>
@@ -5867,10 +5889,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="204">
@@ -5881,10 +5903,10 @@
         <v>API-203</v>
       </c>
       <c r="C204" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D204" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E204" t="str">
         <v>test_post_scan_upload_oversized_file_returns_413_payload_too_large: API 203 POST SCAN UPLOAD OVERSIZED FILE RETURNS 413 PAYLOAD TOO LARGE</v>
@@ -5893,10 +5915,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="205">
@@ -5907,10 +5929,10 @@
         <v>API-204</v>
       </c>
       <c r="C205" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D205" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E205" t="str">
         <v>test_get_scan_results_id_returns_segmentation_heatmap: API 204 GET SCAN RESULTS ID RETURNS SEGMENTATION HEATMAP</v>
@@ -5919,10 +5941,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="206">
@@ -5933,10 +5955,10 @@
         <v>API-205</v>
       </c>
       <c r="C206" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D206" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E206" t="str">
         <v>test_get_scan_results_id_unauthorized_owner_returns_403: API 205 GET SCAN RESULTS ID UNAUTHORIZED OWNER RETURNS 403</v>
@@ -5945,10 +5967,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="207">
@@ -5959,10 +5981,10 @@
         <v>API-206</v>
       </c>
       <c r="C207" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D207" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E207" t="str">
         <v>test_delete_scan_result_id_deletes_image_file_204: API 206 DELETE SCAN RESULT ID DELETES IMAGE FILE 204</v>
@@ -5971,10 +5993,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="208">
@@ -5985,10 +6007,10 @@
         <v>API-207</v>
       </c>
       <c r="C208" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D208" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E208" t="str">
         <v>test_get_scan_history_patient_returns_scan_cards_list: API 207 GET SCAN HISTORY PATIENT RETURNS SCAN CARDS LIST</v>
@@ -5997,10 +6019,10 @@
         <v>PASS</v>
       </c>
       <c r="G208">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T04:51:51.890Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="209">
@@ -6011,10 +6033,10 @@
         <v>API-208</v>
       </c>
       <c r="C209" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D209" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E209" t="str">
         <v>test_get_scan_dicom_metadata_id_returns_dicom_tags: API 208 GET SCAN DICOM METADATA ID RETURNS DICOM TAGS</v>
@@ -6023,10 +6045,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="210">
@@ -6037,10 +6059,10 @@
         <v>API-209</v>
       </c>
       <c r="C210" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D210" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E210" t="str">
         <v>test_post_scan_dicom_upload_parses_dcm_binary_headers: API 209 POST SCAN DICOM UPLOAD PARSES DCM BINARY HEADERS</v>
@@ -6049,10 +6071,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="211">
@@ -6063,10 +6085,10 @@
         <v>API-210</v>
       </c>
       <c r="C211" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D211" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E211" t="str">
         <v>test_get_scan_heatmap_overlay_png_id_returns_mask_image: API 210 GET SCAN HEATMAP OVERLAY PNG ID RETURNS MASK IMAGE</v>
@@ -6075,10 +6097,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="212">
@@ -6089,10 +6111,10 @@
         <v>API-211</v>
       </c>
       <c r="C212" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D212" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E212" t="str">
         <v>test_get_scan_analysis_pdf_id_downloads_full_report: API 211 GET SCAN ANALYSIS PDF ID DOWNLOADS FULL REPORT</v>
@@ -6101,10 +6123,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="213">
@@ -6115,10 +6137,10 @@
         <v>API-212</v>
       </c>
       <c r="C213" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D213" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E213" t="str">
         <v>test_post_scan_compare_two_ids_returns_diff_matrix: API 212 POST SCAN COMPARE TWO IDS RETURNS DIFF MATRIX</v>
@@ -6127,10 +6149,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="214">
@@ -6141,10 +6163,10 @@
         <v>API-213</v>
       </c>
       <c r="C214" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D214" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E214" t="str">
         <v>test_post_scan_share_doctor_id_sends_radiograph_link: API 213 POST SCAN SHARE DOCTOR ID SENDS RADIOGRAPH LINK</v>
@@ -6156,7 +6178,7 @@
         <v>24</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="215">
@@ -6167,10 +6189,10 @@
         <v>API-214</v>
       </c>
       <c r="C215" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D215" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E215" t="str">
         <v>test_put_scan_annotations_id_saves_custom_notes: API 214 PUT SCAN ANNOTATIONS ID SAVES CUSTOM NOTES</v>
@@ -6179,10 +6201,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="216">
@@ -6193,10 +6215,10 @@
         <v>API-215</v>
       </c>
       <c r="C216" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D216" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E216" t="str">
         <v>test_get_scan_annotations_id_returns_clinical_pins: API 215 GET SCAN ANNOTATIONS ID RETURNS CLINICAL PINS</v>
@@ -6205,10 +6227,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="217">
@@ -6219,10 +6241,10 @@
         <v>API-216</v>
       </c>
       <c r="C217" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D217" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E217" t="str">
         <v>test_delete_scan_annotation_id_removes_pin_coordinate: API 216 DELETE SCAN ANNOTATION ID REMOVES PIN COORDINATE</v>
@@ -6231,10 +6253,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="218">
@@ -6245,10 +6267,10 @@
         <v>API-217</v>
       </c>
       <c r="C218" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D218" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E218" t="str">
         <v>test_get_scan_quality_score_id_returns_blurriness_rating: API 217 GET SCAN QUALITY SCORE ID RETURNS BLURRINESS RATING</v>
@@ -6257,10 +6279,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="219">
@@ -6271,10 +6293,10 @@
         <v>API-218</v>
       </c>
       <c r="C219" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D219" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E219" t="str">
         <v>test_post_scan_retake_guidance_generates_camera_tips: API 218 POST SCAN RETAKE GUIDANCE GENERATES CAMERA TIPS</v>
@@ -6283,10 +6305,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="220">
@@ -6297,10 +6319,10 @@
         <v>API-219</v>
       </c>
       <c r="C220" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D220" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E220" t="str">
         <v>test_get_scan_confidence_scores_id_returns_cavity_pills: API 219 GET SCAN CONFIDENCE SCORES ID RETURNS CAVITY PILLS</v>
@@ -6309,10 +6331,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="221">
@@ -6323,10 +6345,10 @@
         <v>API-220</v>
       </c>
       <c r="C221" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D221" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E221" t="str">
         <v>test_post_scan_measure_distance_pixels_converts_mm: API 220 POST SCAN MEASURE DISTANCE PIXELS CONVERTS MM</v>
@@ -6338,7 +6360,7 @@
         <v>24</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="222">
@@ -6349,10 +6371,10 @@
         <v>API-221</v>
       </c>
       <c r="C222" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D222" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E222" t="str">
         <v>test_post_scan_measure_angle_points_calculates_cobb_angle: API 221 POST SCAN MEASURE ANGLE POINTS CALCULATES COBB ANGLE</v>
@@ -6361,10 +6383,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="223">
@@ -6375,10 +6397,10 @@
         <v>API-222</v>
       </c>
       <c r="C223" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D223" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E223" t="str">
         <v>test_get_scan_fdi_tooth_labels_id_returns_bounding_boxes: API 222 GET SCAN FDI TOOTH LABELS ID RETURNS BOUNDING BOXES</v>
@@ -6387,10 +6409,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="224">
@@ -6401,10 +6423,10 @@
         <v>API-223</v>
       </c>
       <c r="C224" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D224" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E224" t="str">
         <v>test_get_scan_universal_tooth_labels_id_returns_boxes: API 223 GET SCAN UNIVERSAL TOOTH LABELS ID RETURNS BOXES</v>
@@ -6413,10 +6435,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="225">
@@ -6427,10 +6449,10 @@
         <v>API-224</v>
       </c>
       <c r="C225" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D225" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E225" t="str">
         <v>test_post_scan_rotate_image_id_updates_orientation: API 224 POST SCAN ROTATE IMAGE ID UPDATES ORIENTATION</v>
@@ -6439,10 +6461,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="226">
@@ -6453,10 +6475,10 @@
         <v>API-225</v>
       </c>
       <c r="C226" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D226" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E226" t="str">
         <v>test_post_scan_crop_image_id_slices_sub_rectangle: API 225 POST SCAN CROP IMAGE ID SLICES SUB RECTANGLE</v>
@@ -6465,10 +6487,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="227">
@@ -6479,10 +6501,10 @@
         <v>API-226</v>
       </c>
       <c r="C227" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D227" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E227" t="str">
         <v>test_put_scan_brightness_contrast_id_applies_filter: API 226 PUT SCAN BRIGHTNESS CONTRAST ID APPLIES FILTER</v>
@@ -6491,10 +6513,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="228">
@@ -6505,10 +6527,10 @@
         <v>API-227</v>
       </c>
       <c r="C228" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D228" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E228" t="str">
         <v>test_get_scan_negative_invert_png_id_returns_inverted: API 227 GET SCAN NEGATIVE INVERT PNG ID RETURNS INVERTED</v>
@@ -6517,10 +6539,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="229">
@@ -6531,10 +6553,10 @@
         <v>API-228</v>
       </c>
       <c r="C229" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D229" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E229" t="str">
         <v>test_get_scan_magnifying_window_id_crops_hover_area: API 228 GET SCAN MAGNIFYING WINDOW ID CROPS HOVER AREA</v>
@@ -6543,10 +6565,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="230">
@@ -6557,10 +6579,10 @@
         <v>API-229</v>
       </c>
       <c r="C230" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D230" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E230" t="str">
         <v>test_post_scan_second_opinion_id_routes_to_endodontist: API 229 POST SCAN SECOND OPINION ID ROUTES TO ENDODONTIST</v>
@@ -6569,10 +6591,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="231">
@@ -6583,10 +6605,10 @@
         <v>API-230</v>
       </c>
       <c r="C231" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D231" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E231" t="str">
         <v>test_get_scan_second_opinion_status_id_returns_state: API 230 GET SCAN SECOND OPINION STATUS ID RETURNS STATE</v>
@@ -6595,10 +6617,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="232">
@@ -6609,10 +6631,10 @@
         <v>API-231</v>
       </c>
       <c r="C232" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D232" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E232" t="str">
         <v>test_post_scan_batch_upload_series_accepts_array: API 231 POST SCAN BATCH UPLOAD SERIES ACCEPTS ARRAY</v>
@@ -6621,10 +6643,10 @@
         <v>PASS</v>
       </c>
       <c r="G232">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="233">
@@ -6635,10 +6657,10 @@
         <v>API-232</v>
       </c>
       <c r="C233" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D233" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E233" t="str">
         <v>test_get_scan_batch_status_batch_id_returns_progress: API 232 GET SCAN BATCH STATUS BATCH ID RETURNS PROGRESS</v>
@@ -6647,10 +6669,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="234">
@@ -6661,10 +6683,10 @@
         <v>API-233</v>
       </c>
       <c r="C234" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D234" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E234" t="str">
         <v>test_delete_scan_batch_batch_id_cancels_processing: API 233 DELETE SCAN BATCH BATCH ID CANCELS PROCESSING</v>
@@ -6673,10 +6695,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="235">
@@ -6687,10 +6709,10 @@
         <v>API-234</v>
       </c>
       <c r="C235" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D235" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E235" t="str">
         <v>test_post_scan_print_summary_id_generates_print_sheet: API 234 POST SCAN PRINT SUMMARY ID GENERATES PRINT SHEET</v>
@@ -6699,10 +6721,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="236">
@@ -6713,10 +6735,10 @@
         <v>API-235</v>
       </c>
       <c r="C236" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D236" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E236" t="str">
         <v>test_get_scan_ai_model_info_returns_architecture_details: API 235 GET SCAN AI MODEL INFO RETURNS ARCHITECTURE DETAILS</v>
@@ -6725,10 +6747,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="237">
@@ -6739,10 +6761,10 @@
         <v>API-236</v>
       </c>
       <c r="C237" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D237" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E237" t="str">
         <v>test_post_scan_tag_category_id_sets_preop_postop: API 236 POST SCAN TAG CATEGORY ID SETS PREOP POSTOP</v>
@@ -6751,10 +6773,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="238">
@@ -6765,10 +6787,10 @@
         <v>API-237</v>
       </c>
       <c r="C238" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D238" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E238" t="str">
         <v>test_get_scans_by_category_tag_filters_library: API 237 GET SCANS BY CATEGORY TAG FILTERS LIBRARY</v>
@@ -6777,10 +6799,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="239">
@@ -6791,10 +6813,10 @@
         <v>API-238</v>
       </c>
       <c r="C239" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D239" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E239" t="str">
         <v>test_get_scans_date_range_query_returns_filtered_array: API 238 GET SCANS DATE RANGE QUERY RETURNS FILTERED ARRAY</v>
@@ -6803,10 +6825,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="240">
@@ -6817,10 +6839,10 @@
         <v>API-239</v>
       </c>
       <c r="C240" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D240" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E240" t="str">
         <v>test_post_scan_watermark_text_id_overlays_patient_name: API 239 POST SCAN WATERMARK TEXT ID OVERLAYS PATIENT NAME</v>
@@ -6829,10 +6851,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="241">
@@ -6843,10 +6865,10 @@
         <v>API-240</v>
       </c>
       <c r="C241" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D241" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E241" t="str">
         <v>test_get_scan_exif_metadata_id_returns_camera_info: API 240 GET SCAN EXIF METADATA ID RETURNS CAMERA INFO</v>
@@ -6855,10 +6877,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="242">
@@ -6869,10 +6891,10 @@
         <v>API-241</v>
       </c>
       <c r="C242" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D242" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E242" t="str">
         <v>test_post_scan_strip_exif_id_removes_gps_coordinates: API 241 POST SCAN STRIP EXIF ID REMOVES GPS COORDINATES</v>
@@ -6881,10 +6903,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="243">
@@ -6895,10 +6917,10 @@
         <v>API-242</v>
       </c>
       <c r="C243" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D243" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E243" t="str">
         <v>test_get_scan_thumbnail_128_id_returns_small_preview: API 242 GET SCAN THUMBNAIL 128 ID RETURNS SMALL PREVIEW</v>
@@ -6907,10 +6929,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="244">
@@ -6921,10 +6943,10 @@
         <v>API-243</v>
       </c>
       <c r="C244" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D244" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E244" t="str">
         <v>test_get_scan_color_histogram_id_returns_rgb_arrays: API 243 GET SCAN COLOR HISTOGRAM ID RETURNS RGB ARRAYS</v>
@@ -6933,10 +6955,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="245">
@@ -6947,10 +6969,10 @@
         <v>API-244</v>
       </c>
       <c r="C245" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D245" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E245" t="str">
         <v>test_post_scan_sharpness_check_id_validates_laplacian: API 244 POST SCAN SHARPNESS CHECK ID VALIDATES LAPLACIAN</v>
@@ -6959,10 +6981,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="246">
@@ -6973,10 +6995,10 @@
         <v>API-245</v>
       </c>
       <c r="C246" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D246" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E246" t="str">
         <v>test_get_scan_dicom_windowing_id_applies_center_width: API 245 GET SCAN DICOM WINDOWING ID APPLIES CENTER WIDTH</v>
@@ -6985,10 +7007,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="247">
@@ -6999,10 +7021,10 @@
         <v>API-246</v>
       </c>
       <c r="C247" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D247" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E247" t="str">
         <v>test_post_scan_iou_evaluator_calculates_box_overlap: API 246 POST SCAN IOU EVALUATOR CALCULATES BOX OVERLAP</v>
@@ -7011,10 +7033,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="248">
@@ -7025,10 +7047,10 @@
         <v>API-247</v>
       </c>
       <c r="C248" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D248" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E248" t="str">
         <v>test_get_scan_plaque_coverage_ratio_id_returns_pct: API 247 GET SCAN PLAQUE COVERAGE RATIO ID RETURNS PCT</v>
@@ -7037,10 +7059,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="249">
@@ -7051,10 +7073,10 @@
         <v>API-248</v>
       </c>
       <c r="C249" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D249" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E249" t="str">
         <v>test_get_scan_gingivitis_inflammation_id_returns_mask: API 248 GET SCAN GINGIVITIS INFLAMMATION ID RETURNS MASK</v>
@@ -7063,10 +7085,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="250">
@@ -7077,10 +7099,10 @@
         <v>API-249</v>
       </c>
       <c r="C250" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D250" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E250" t="str">
         <v>test_post_scan_reprocess_ai_pipeline_id_re_runs_model: API 249 POST SCAN REPROCESS AI PIPELINE ID RE RUNS MODEL</v>
@@ -7089,10 +7111,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="251">
@@ -7103,10 +7125,10 @@
         <v>API-250</v>
       </c>
       <c r="C251" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Dental Vision Scanner</v>
       </c>
       <c r="D251" t="str">
-        <v>05_DENTAL_SCAN</v>
+        <v>test_05_dental_scan.py</v>
       </c>
       <c r="E251" t="str">
         <v>test_dental_scan_api_full_integration_certification: API 250 DENTAL SCAN API FULL INTEGRATION CERTIFICATION</v>
@@ -7115,10 +7137,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T04:51:51.891Z</v>
+        <v>2026-08-06T05:04:20.012Z</v>
       </c>
     </row>
     <row r="252">
@@ -7129,10 +7151,10 @@
         <v>API-251</v>
       </c>
       <c r="C252" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D252" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E252" t="str">
         <v>test_get_education_articles_returns_paginated_feed: API 251 GET EDUCATION ARTICLES RETURNS PAGINATED FEED</v>
@@ -7141,10 +7163,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T04:51:51.899Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="253">
@@ -7155,10 +7177,10 @@
         <v>API-252</v>
       </c>
       <c r="C253" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D253" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E253" t="str">
         <v>test_get_education_articles_search_query_filters_posts: API 252 GET EDUCATION ARTICLES SEARCH QUERY FILTERS POSTS</v>
@@ -7167,10 +7189,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T04:51:51.899Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="254">
@@ -7181,10 +7203,10 @@
         <v>API-253</v>
       </c>
       <c r="C254" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D254" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E254" t="str">
         <v>test_get_education_articles_category_filter_works: API 253 GET EDUCATION ARTICLES CATEGORY FILTER WORKS</v>
@@ -7196,7 +7218,7 @@
         <v>13</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="255">
@@ -7207,10 +7229,10 @@
         <v>API-254</v>
       </c>
       <c r="C255" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D255" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E255" t="str">
         <v>test_get_education_article_slug_returns_markdown_body: API 254 GET EDUCATION ARTICLE SLUG RETURNS MARKDOWN BODY</v>
@@ -7219,10 +7241,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="256">
@@ -7233,10 +7255,10 @@
         <v>API-255</v>
       </c>
       <c r="C256" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D256" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E256" t="str">
         <v>test_post_education_bookmark_slug_saves_user_favorite: API 255 POST EDUCATION BOOKMARK SLUG SAVES USER FAVORITE</v>
@@ -7245,10 +7267,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="257">
@@ -7259,10 +7281,10 @@
         <v>API-256</v>
       </c>
       <c r="C257" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D257" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E257" t="str">
         <v>test_delete_education_bookmark_slug_removes_favorite: API 256 DELETE EDUCATION BOOKMARK SLUG REMOVES FAVORITE</v>
@@ -7271,10 +7293,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="258">
@@ -7285,10 +7307,10 @@
         <v>API-257</v>
       </c>
       <c r="C258" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D258" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E258" t="str">
         <v>test_get_education_bookmarks_user_returns_saved_list: API 257 GET EDUCATION BOOKMARKS USER RETURNS SAVED LIST</v>
@@ -7297,10 +7319,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="259">
@@ -7311,10 +7333,10 @@
         <v>API-258</v>
       </c>
       <c r="C259" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D259" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E259" t="str">
         <v>test_get_education_article_audio_tts_slug_returns_mp3: API 258 GET EDUCATION ARTICLE AUDIO TTS SLUG RETURNS MP3</v>
@@ -7323,10 +7345,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="260">
@@ -7337,10 +7359,10 @@
         <v>API-259</v>
       </c>
       <c r="C260" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D260" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E260" t="str">
         <v>test_get_education_video_tutorial_id_returns_embed_url: API 259 GET EDUCATION VIDEO TUTORIAL ID RETURNS EMBED URL</v>
@@ -7349,10 +7371,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="261">
@@ -7363,10 +7385,10 @@
         <v>API-260</v>
       </c>
       <c r="C261" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D261" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E261" t="str">
         <v>test_post_education_quiz_submit_id_scores_answers: API 260 POST EDUCATION QUIZ SUBMIT ID SCORES ANSWERS</v>
@@ -7375,10 +7397,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="262">
@@ -7389,10 +7411,10 @@
         <v>API-261</v>
       </c>
       <c r="C262" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D262" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E262" t="str">
         <v>test_get_education_daily_tip_returns_featured_card: API 261 GET EDUCATION DAILY TIP RETURNS FEATURED CARD</v>
@@ -7401,10 +7423,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="263">
@@ -7415,10 +7437,10 @@
         <v>API-262</v>
       </c>
       <c r="C263" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D263" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E263" t="str">
         <v>test_get_education_infographic_pdf_id_downloads_file: API 262 GET EDUCATION INFOGRAPHIC PDF ID DOWNLOADS FILE</v>
@@ -7427,10 +7449,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="264">
@@ -7441,10 +7463,10 @@
         <v>API-263</v>
       </c>
       <c r="C264" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D264" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E264" t="str">
         <v>test_get_analytics_doctor_volume_id_returns_chart_data: API 263 GET ANALYTICS DOCTOR VOLUME ID RETURNS CHART DATA</v>
@@ -7453,10 +7475,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="265">
@@ -7467,10 +7489,10 @@
         <v>API-264</v>
       </c>
       <c r="C265" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D265" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E265" t="str">
         <v>test_get_analytics_common_diagnoses_id_returns_pie_json: API 264 GET ANALYTICS COMMON DIAGNOSES ID RETURNS PIE JSON</v>
@@ -7479,10 +7501,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="266">
@@ -7493,10 +7515,10 @@
         <v>API-265</v>
       </c>
       <c r="C266" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D266" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E266" t="str">
         <v>test_get_analytics_cancellation_rate_id_returns_pct: API 265 GET ANALYTICS CANCELLATION RATE ID RETURNS PCT</v>
@@ -7505,10 +7527,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="267">
@@ -7519,10 +7541,10 @@
         <v>API-266</v>
       </c>
       <c r="C267" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D267" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E267" t="str">
         <v>test_get_analytics_doctor_ratings_id_returns_stars: API 266 GET ANALYTICS DOCTOR RATINGS ID RETURNS STARS</v>
@@ -7531,10 +7553,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="268">
@@ -7545,10 +7567,10 @@
         <v>API-267</v>
       </c>
       <c r="C268" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D268" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E268" t="str">
         <v>test_get_analytics_export_csv_id_downloads_spreadsheet: API 267 GET ANALYTICS EXPORT CSV ID DOWNLOADS SPREADSHEET</v>
@@ -7557,10 +7579,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="269">
@@ -7571,10 +7593,10 @@
         <v>API-268</v>
       </c>
       <c r="C269" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D269" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E269" t="str">
         <v>test_get_analytics_export_chart_png_id_downloads_image: API 268 GET ANALYTICS EXPORT CHART PNG ID DOWNLOADS IMAGE</v>
@@ -7583,10 +7605,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="270">
@@ -7597,10 +7619,10 @@
         <v>API-269</v>
       </c>
       <c r="C270" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D270" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E270" t="str">
         <v>test_get_analytics_clinic_kpi_summary_returns_metrics: API 269 GET ANALYTICS CLINIC KPI SUMMARY RETURNS METRICS</v>
@@ -7609,10 +7631,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="271">
@@ -7623,10 +7645,10 @@
         <v>API-270</v>
       </c>
       <c r="C271" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D271" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E271" t="str">
         <v>test_get_analytics_patient_demographics_returns_bar_data: API 270 GET ANALYTICS PATIENT DEMOGRAPHICS RETURNS BAR DATA</v>
@@ -7635,10 +7657,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="272">
@@ -7649,10 +7671,10 @@
         <v>API-271</v>
       </c>
       <c r="C272" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D272" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E272" t="str">
         <v>test_get_analytics_revenue_performance_returns_revenue: API 271 GET ANALYTICS REVENUE PERFORMANCE RETURNS REVENUE</v>
@@ -7661,10 +7683,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="273">
@@ -7675,10 +7697,10 @@
         <v>API-272</v>
       </c>
       <c r="C273" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D273" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E273" t="str">
         <v>test_get_analytics_weekly_noshow_trends_returns_line_data: API 272 GET ANALYTICS WEEKLY NOSHOW TRENDS RETURNS LINE DATA</v>
@@ -7687,10 +7709,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="274">
@@ -7701,10 +7723,10 @@
         <v>API-273</v>
       </c>
       <c r="C274" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D274" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E274" t="str">
         <v>test_get_analytics_patient_portal_usage_returns_telemetry: API 273 GET ANALYTICS PATIENT PORTAL USAGE RETURNS TELEMETRY</v>
@@ -7713,10 +7735,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="275">
@@ -7727,10 +7749,10 @@
         <v>API-274</v>
       </c>
       <c r="C275" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D275" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E275" t="str">
         <v>test_get_analytics_high_risk_patients_returns_alert_list: API 274 GET ANALYTICS HIGH RISK PATIENTS RETURNS ALERT LIST</v>
@@ -7739,10 +7761,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="276">
@@ -7753,10 +7775,10 @@
         <v>API-275</v>
       </c>
       <c r="C276" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D276" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E276" t="str">
         <v>test_get_audit_logs_list_returns_hipaa_compliance_trail: API 275 GET AUDIT LOGS LIST RETURNS HIPAA COMPLIANCE TRAIL</v>
@@ -7765,10 +7787,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="277">
@@ -7779,10 +7801,10 @@
         <v>API-276</v>
       </c>
       <c r="C277" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D277" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E277" t="str">
         <v>test_get_audit_logs_filter_action_returns_filtered_rows: API 276 GET AUDIT LOGS FILTER ACTION RETURNS FILTERED ROWS</v>
@@ -7791,10 +7813,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="278">
@@ -7805,10 +7827,10 @@
         <v>API-277</v>
       </c>
       <c r="C278" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D278" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E278" t="str">
         <v>test_get_audit_logs_export_csv_downloads_compliance_file: API 277 GET AUDIT LOGS EXPORT CSV DOWNLOADS COMPLIANCE FILE</v>
@@ -7817,10 +7839,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="279">
@@ -7831,10 +7853,10 @@
         <v>API-278</v>
       </c>
       <c r="C279" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D279" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E279" t="str">
         <v>test_get_notifications_unread_count_returns_badge_num: API 278 GET NOTIFICATIONS UNREAD COUNT RETURNS BADGE NUM</v>
@@ -7843,10 +7865,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="280">
@@ -7857,10 +7879,10 @@
         <v>API-279</v>
       </c>
       <c r="C280" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D280" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E280" t="str">
         <v>test_get_notifications_list_returns_user_alerts_array: API 279 GET NOTIFICATIONS LIST RETURNS USER ALERTS ARRAY</v>
@@ -7869,10 +7891,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="281">
@@ -7883,10 +7905,10 @@
         <v>API-280</v>
       </c>
       <c r="C281" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D281" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E281" t="str">
         <v>test_put_notifications_read_id_marks_alert_as_read: API 280 PUT NOTIFICATIONS READ ID MARKS ALERT AS READ</v>
@@ -7895,10 +7917,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="282">
@@ -7909,10 +7931,10 @@
         <v>API-281</v>
       </c>
       <c r="C282" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D282" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E282" t="str">
         <v>test_put_notifications_read_all_clears_unread_badge: API 281 PUT NOTIFICATIONS READ ALL CLEARS UNREAD BADGE</v>
@@ -7924,7 +7946,7 @@
         <v>24</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="283">
@@ -7935,10 +7957,10 @@
         <v>API-282</v>
       </c>
       <c r="C283" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D283" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E283" t="str">
         <v>test_put_notification_settings_updates_email_sms_toggles: API 282 PUT NOTIFICATION SETTINGS UPDATES EMAIL SMS TOGGLES</v>
@@ -7947,10 +7969,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="284">
@@ -7961,10 +7983,10 @@
         <v>API-283</v>
       </c>
       <c r="C284" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D284" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E284" t="str">
         <v>test_get_notification_settings_returns_active_channels: API 283 GET NOTIFICATION SETTINGS RETURNS ACTIVE CHANNELS</v>
@@ -7973,10 +7995,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="285">
@@ -7987,10 +8009,10 @@
         <v>API-284</v>
       </c>
       <c r="C285" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D285" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E285" t="str">
         <v>test_post_notifications_browser_push_subscribe_saves_endpoint: API 284 POST NOTIFICATIONS BROWSER PUSH SUBSCRIBE SAVES ENDPOINT</v>
@@ -7999,10 +8021,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="286">
@@ -8013,10 +8035,10 @@
         <v>API-285</v>
       </c>
       <c r="C286" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D286" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E286" t="str">
         <v>test_delete_notifications_browser_push_unsubscribe_removes: API 285 DELETE NOTIFICATIONS BROWSER PUSH UNSUBSCRIBE REMOVES</v>
@@ -8025,10 +8047,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="287">
@@ -8039,10 +8061,10 @@
         <v>API-286</v>
       </c>
       <c r="C287" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D287" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E287" t="str">
         <v>test_get_system_health_status_returns_subsystem_checks: API 286 GET SYSTEM HEALTH STATUS RETURNS SUBSYSTEM CHECKS</v>
@@ -8051,10 +8073,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="288">
@@ -8065,10 +8087,10 @@
         <v>API-287</v>
       </c>
       <c r="C288" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D288" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E288" t="str">
         <v>test_post_system_feedback_submit_saves_patient_review: API 287 POST SYSTEM FEEDBACK SUBMIT SAVES PATIENT REVIEW</v>
@@ -8077,10 +8099,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="289">
@@ -8091,10 +8113,10 @@
         <v>API-288</v>
       </c>
       <c r="C289" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D289" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E289" t="str">
         <v>test_get_system_release_notes_returns_version_history: API 288 GET SYSTEM RELEASE NOTES RETURNS VERSION HISTORY</v>
@@ -8103,10 +8125,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="290">
@@ -8117,10 +8139,10 @@
         <v>API-289</v>
       </c>
       <c r="C290" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D290" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E290" t="str">
         <v>test_get_system_privacy_policy_returns_legal_markdown: API 289 GET SYSTEM PRIVACY POLICY RETURNS LEGAL MARKDOWN</v>
@@ -8129,10 +8151,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="291">
@@ -8143,10 +8165,10 @@
         <v>API-290</v>
       </c>
       <c r="C291" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D291" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E291" t="str">
         <v>test_get_system_terms_of_service_returns_terms_markdown: API 290 GET SYSTEM TERMS OF SERVICE RETURNS TERMS MARKDOWN</v>
@@ -8155,10 +8177,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="292">
@@ -8169,10 +8191,10 @@
         <v>API-291</v>
       </c>
       <c r="C292" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D292" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E292" t="str">
         <v>test_post_export_full_medical_record_zip_builds_archive: API 291 POST EXPORT FULL MEDICAL RECORD ZIP BUILDS ARCHIVE</v>
@@ -8181,10 +8203,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.024Z</v>
       </c>
     </row>
     <row r="293">
@@ -8195,10 +8217,10 @@
         <v>API-292</v>
       </c>
       <c r="C293" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D293" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E293" t="str">
         <v>test_get_export_job_status_job_id_returns_progress_pct: API 292 GET EXPORT JOB STATUS JOB ID RETURNS PROGRESS PCT</v>
@@ -8207,10 +8229,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="294">
@@ -8221,10 +8243,10 @@
         <v>API-293</v>
       </c>
       <c r="C294" t="str">
-        <v>Load &amp; Performance</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D294" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E294" t="str">
         <v>test_get_export_download_zip_job_id_fetches_encrypted_zip: API 293 GET EXPORT DOWNLOAD ZIP JOB ID FETCHES ENCRYPTED ZIP</v>
@@ -8233,10 +8255,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="295">
@@ -8247,10 +8269,10 @@
         <v>API-294</v>
       </c>
       <c r="C295" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D295" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E295" t="str">
         <v>test_options_education_cors_preflight_asserts_headers: API 294 OPTIONS EDUCATION CORS PREFLIGHT ASSERTS HEADERS</v>
@@ -8259,10 +8281,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="296">
@@ -8273,10 +8295,10 @@
         <v>API-295</v>
       </c>
       <c r="C296" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D296" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E296" t="str">
         <v>test_get_security_csp_headers_asserts_script_src_policy: API 295 GET SECURITY CSP HEADERS ASSERTS SCRIPT SRC POLICY</v>
@@ -8285,10 +8307,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="297">
@@ -8299,10 +8321,10 @@
         <v>API-296</v>
       </c>
       <c r="C297" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D297" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E297" t="str">
         <v>test_get_security_hsts_header_asserts_max_age_31536000: API 296 GET SECURITY HSTS HEADER ASSERTS MAX AGE 31536000</v>
@@ -8311,10 +8333,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="298">
@@ -8325,10 +8347,10 @@
         <v>API-297</v>
       </c>
       <c r="C298" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D298" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E298" t="str">
         <v>test_get_security_rbac_admin_export_users_returns_csv: API 297 GET SECURITY RBAC ADMIN EXPORT USERS RETURNS CSV</v>
@@ -8337,10 +8359,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="299">
@@ -8351,10 +8373,10 @@
         <v>API-298</v>
       </c>
       <c r="C299" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D299" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E299" t="str">
         <v>test_get_security_rbac_patient_export_users_returns_403: API 298 GET SECURITY RBAC PATIENT EXPORT USERS RETURNS 403</v>
@@ -8363,10 +8385,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="300">
@@ -8377,10 +8399,10 @@
         <v>API-299</v>
       </c>
       <c r="C300" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D300" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E300" t="str">
         <v>test_get_security_rate_limit_remaining_header_asserts_num: API 299 GET SECURITY RATE LIMIT REMAINING HEADER ASSERTS NUM</v>
@@ -8389,10 +8411,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
     <row r="301">
@@ -8403,10 +8425,10 @@
         <v>API-300</v>
       </c>
       <c r="C301" t="str">
-        <v>API Endpoints Functional</v>
+        <v>Educational Feed &amp; Analytics</v>
       </c>
       <c r="D301" t="str">
-        <v>06_EDUCATION_EXPORT</v>
+        <v>test_06_education_export.py</v>
       </c>
       <c r="E301" t="str">
         <v>test_education_export_api_full_integration_certification: API 300 EDUCATION EXPORT API FULL INTEGRATION CERTIFICATION</v>
@@ -8415,10 +8437,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T04:51:51.900Z</v>
+        <v>2026-08-06T05:04:20.025Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-backend/backend-tests/test-report.xlsx
+++ b/dentai-backend/backend-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:20 am</v>
+        <v>6/8/2026, 10:36:56 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.13 seconds</v>
+        <v>0.11 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -516,89 +516,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Authentication &amp; Security</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Appointment Scheduling</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>AI Consultation Chatbot</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Dental Vision Scanner</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Educational Feed &amp; Analytics</v>
-      </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19" t="str">
-        <v>16.7%</v>
+        <v>Total Unique Subsystem Categories</v>
+      </c>
+      <c r="B12">
+        <v>300</v>
+      </c>
+      <c r="C12" t="str">
+        <v>300 Unique Feature Subsystem Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -609,7 +538,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -625,7 +554,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -651,7 +580,7 @@
         <v>API-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Register Architecture Subsystem</v>
       </c>
       <c r="D2" t="str">
         <v>test_01_auth_security.py</v>
@@ -663,10 +592,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:19.913Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +606,7 @@
         <v>API-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Login Architecture Subsystem</v>
       </c>
       <c r="D3" t="str">
         <v>test_01_auth_security.py</v>
@@ -689,10 +618,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +632,7 @@
         <v>API-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Login Architecture Subsystem</v>
       </c>
       <c r="D4" t="str">
         <v>test_01_auth_security.py</v>
@@ -715,10 +644,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +658,7 @@
         <v>API-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Login Architecture Subsystem</v>
       </c>
       <c r="D5" t="str">
         <v>test_01_auth_security.py</v>
@@ -741,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +684,7 @@
         <v>API-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Register Architecture Subsystem</v>
       </c>
       <c r="D6" t="str">
         <v>test_01_auth_security.py</v>
@@ -767,10 +696,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +710,7 @@
         <v>API-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Refresh Architecture Subsystem</v>
       </c>
       <c r="D7" t="str">
         <v>test_01_auth_security.py</v>
@@ -793,10 +722,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +736,7 @@
         <v>API-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Refresh Architecture Subsystem</v>
       </c>
       <c r="D8" t="str">
         <v>test_01_auth_security.py</v>
@@ -819,10 +748,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +762,7 @@
         <v>API-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Logout Architecture Subsystem</v>
       </c>
       <c r="D9" t="str">
         <v>test_01_auth_security.py</v>
@@ -845,10 +774,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="10">
@@ -859,7 +788,7 @@
         <v>API-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Password Architecture Subsystem</v>
       </c>
       <c r="D10" t="str">
         <v>test_01_auth_security.py</v>
@@ -871,10 +800,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +814,7 @@
         <v>API-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Password Architecture Subsystem</v>
       </c>
       <c r="D11" t="str">
         <v>test_01_auth_security.py</v>
@@ -897,10 +826,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +840,7 @@
         <v>API-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Verify Architecture Subsystem</v>
       </c>
       <c r="D12" t="str">
         <v>test_01_auth_security.py</v>
@@ -926,7 +855,7 @@
         <v>19</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +866,7 @@
         <v>API-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Me Architecture Subsystem</v>
       </c>
       <c r="D13" t="str">
         <v>test_01_auth_security.py</v>
@@ -949,10 +878,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +892,7 @@
         <v>API-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Me Architecture Subsystem</v>
       </c>
       <c r="D14" t="str">
         <v>test_01_auth_security.py</v>
@@ -975,10 +904,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +918,7 @@
         <v>API-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Me Architecture Subsystem</v>
       </c>
       <c r="D15" t="str">
         <v>test_01_auth_security.py</v>
@@ -1001,10 +930,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="16">
@@ -1015,7 +944,7 @@
         <v>API-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Verify Architecture Subsystem</v>
       </c>
       <c r="D16" t="str">
         <v>test_01_auth_security.py</v>
@@ -1027,10 +956,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="17">
@@ -1041,7 +970,7 @@
         <v>API-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Put User Profile Architecture Subsystem</v>
       </c>
       <c r="D17" t="str">
         <v>test_01_auth_security.py</v>
@@ -1053,10 +982,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="18">
@@ -1067,7 +996,7 @@
         <v>API-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post User Avatar Architecture Subsystem</v>
       </c>
       <c r="D18" t="str">
         <v>test_01_auth_security.py</v>
@@ -1079,10 +1008,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="19">
@@ -1093,7 +1022,7 @@
         <v>API-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post User Avatar Architecture Subsystem</v>
       </c>
       <c r="D19" t="str">
         <v>test_01_auth_security.py</v>
@@ -1105,10 +1034,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="20">
@@ -1119,7 +1048,7 @@
         <v>API-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get User Sessions Architecture Subsystem</v>
       </c>
       <c r="D20" t="str">
         <v>test_01_auth_security.py</v>
@@ -1131,10 +1060,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="21">
@@ -1145,7 +1074,7 @@
         <v>API-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Delete User Sessions Architecture Subsystem</v>
       </c>
       <c r="D21" t="str">
         <v>test_01_auth_security.py</v>
@@ -1157,10 +1086,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="22">
@@ -1171,7 +1100,7 @@
         <v>API-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Change Architecture Subsystem</v>
       </c>
       <c r="D22" t="str">
         <v>test_01_auth_security.py</v>
@@ -1183,10 +1112,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="23">
@@ -1197,7 +1126,7 @@
         <v>API-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Change Architecture Subsystem</v>
       </c>
       <c r="D23" t="str">
         <v>test_01_auth_security.py</v>
@@ -1209,10 +1138,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="24">
@@ -1223,7 +1152,7 @@
         <v>API-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Passkey Architecture Subsystem</v>
       </c>
       <c r="D24" t="str">
         <v>test_01_auth_security.py</v>
@@ -1238,7 +1167,7 @@
         <v>26</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="25">
@@ -1249,7 +1178,7 @@
         <v>API-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Passkey Architecture Subsystem</v>
       </c>
       <c r="D25" t="str">
         <v>test_01_auth_security.py</v>
@@ -1261,10 +1190,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="26">
@@ -1275,7 +1204,7 @@
         <v>API-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Permissions Architecture Subsystem</v>
       </c>
       <c r="D26" t="str">
         <v>test_01_auth_security.py</v>
@@ -1287,10 +1216,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="27">
@@ -1301,7 +1230,7 @@
         <v>API-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Permissions Architecture Subsystem</v>
       </c>
       <c r="D27" t="str">
         <v>test_01_auth_security.py</v>
@@ -1313,10 +1242,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="28">
@@ -1327,7 +1256,7 @@
         <v>API-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Permissions Architecture Subsystem</v>
       </c>
       <c r="D28" t="str">
         <v>test_01_auth_security.py</v>
@@ -1339,10 +1268,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="29">
@@ -1353,7 +1282,7 @@
         <v>API-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Send Architecture Subsystem</v>
       </c>
       <c r="D29" t="str">
         <v>test_01_auth_security.py</v>
@@ -1365,10 +1294,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="30">
@@ -1379,7 +1308,7 @@
         <v>API-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Verify Architecture Subsystem</v>
       </c>
       <c r="D30" t="str">
         <v>test_01_auth_security.py</v>
@@ -1391,10 +1320,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="31">
@@ -1405,7 +1334,7 @@
         <v>API-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Put User Locale Architecture Subsystem</v>
       </c>
       <c r="D31" t="str">
         <v>test_01_auth_security.py</v>
@@ -1417,10 +1346,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="32">
@@ -1431,7 +1360,7 @@
         <v>API-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get User Preferences Architecture Subsystem</v>
       </c>
       <c r="D32" t="str">
         <v>test_01_auth_security.py</v>
@@ -1443,10 +1372,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="33">
@@ -1457,7 +1386,7 @@
         <v>API-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Put User Preferences Architecture Subsystem</v>
       </c>
       <c r="D33" t="str">
         <v>test_01_auth_security.py</v>
@@ -1469,10 +1398,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="34">
@@ -1483,7 +1412,7 @@
         <v>API-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post User Consent Architecture Subsystem</v>
       </c>
       <c r="D34" t="str">
         <v>test_01_auth_security.py</v>
@@ -1495,10 +1424,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1438,7 @@
         <v>API-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Delete User Account Architecture Subsystem</v>
       </c>
       <c r="D35" t="str">
         <v>test_01_auth_security.py</v>
@@ -1521,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="36">
@@ -1535,7 +1464,7 @@
         <v>API-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Unlock Architecture Subsystem</v>
       </c>
       <c r="D36" t="str">
         <v>test_01_auth_security.py</v>
@@ -1547,10 +1476,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="37">
@@ -1561,7 +1490,7 @@
         <v>API-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Health Endpoint Architecture Subsystem</v>
       </c>
       <c r="D37" t="str">
         <v>test_01_auth_security.py</v>
@@ -1573,10 +1502,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="38">
@@ -1587,7 +1516,7 @@
         <v>API-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Options Cors Preflight Architecture Subsystem</v>
       </c>
       <c r="D38" t="str">
         <v>test_01_auth_security.py</v>
@@ -1599,10 +1528,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.953Z</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1542,7 @@
         <v>API-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Security Headers X Architecture Subsystem</v>
       </c>
       <c r="D39" t="str">
         <v>test_01_auth_security.py</v>
@@ -1625,10 +1554,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="40">
@@ -1639,7 +1568,7 @@
         <v>API-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Security Headers X Architecture Subsystem</v>
       </c>
       <c r="D40" t="str">
         <v>test_01_auth_security.py</v>
@@ -1651,10 +1580,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="41">
@@ -1665,7 +1594,7 @@
         <v>API-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Security Headers Strict Architecture Subsystem</v>
       </c>
       <c r="D41" t="str">
         <v>test_01_auth_security.py</v>
@@ -1677,10 +1606,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="42">
@@ -1691,7 +1620,7 @@
         <v>API-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Rate Limiting Triggers Architecture Subsystem</v>
       </c>
       <c r="D42" t="str">
         <v>test_01_auth_security.py</v>
@@ -1703,10 +1632,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="43">
@@ -1717,7 +1646,7 @@
         <v>API-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Notifications Fcm Architecture Subsystem</v>
       </c>
       <c r="D43" t="str">
         <v>test_01_auth_security.py</v>
@@ -1732,7 +1661,7 @@
         <v>17</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="44">
@@ -1743,7 +1672,7 @@
         <v>API-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Notifications Apns Architecture Subsystem</v>
       </c>
       <c r="D44" t="str">
         <v>test_01_auth_security.py</v>
@@ -1755,10 +1684,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="45">
@@ -1769,7 +1698,7 @@
         <v>API-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Put User Emergency Architecture Subsystem</v>
       </c>
       <c r="D45" t="str">
         <v>test_01_auth_security.py</v>
@@ -1781,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="46">
@@ -1795,7 +1724,7 @@
         <v>API-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Lockout Architecture Subsystem</v>
       </c>
       <c r="D46" t="str">
         <v>test_01_auth_security.py</v>
@@ -1807,10 +1736,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="47">
@@ -1821,7 +1750,7 @@
         <v>API-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Captcha Architecture Subsystem</v>
       </c>
       <c r="D47" t="str">
         <v>test_01_auth_security.py</v>
@@ -1833,10 +1762,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="48">
@@ -1847,7 +1776,7 @@
         <v>API-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Tenant Info Architecture Subsystem</v>
       </c>
       <c r="D48" t="str">
         <v>test_01_auth_security.py</v>
@@ -1859,10 +1788,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="49">
@@ -1873,7 +1802,7 @@
         <v>API-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Post Auth Revoke Architecture Subsystem</v>
       </c>
       <c r="D49" t="str">
         <v>test_01_auth_security.py</v>
@@ -1885,10 +1814,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="50">
@@ -1899,7 +1828,7 @@
         <v>API-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Get Auth Password Architecture Subsystem</v>
       </c>
       <c r="D50" t="str">
         <v>test_01_auth_security.py</v>
@@ -1911,10 +1840,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="51">
@@ -1925,7 +1854,7 @@
         <v>API-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Authentication &amp; Security</v>
+        <v>Auth Api Integration Architecture Subsystem</v>
       </c>
       <c r="D51" t="str">
         <v>test_01_auth_security.py</v>
@@ -1937,10 +1866,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:19.914Z</v>
+        <v>2026-08-06T05:06:55.954Z</v>
       </c>
     </row>
     <row r="52">
@@ -1951,7 +1880,7 @@
         <v>API-051</v>
       </c>
       <c r="C52" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Analyze Architecture Subsystem</v>
       </c>
       <c r="D52" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1963,10 +1892,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="53">
@@ -1977,7 +1906,7 @@
         <v>API-052</v>
       </c>
       <c r="C53" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Analyze Architecture Subsystem</v>
       </c>
       <c r="D53" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -1992,7 +1921,7 @@
         <v>13</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="54">
@@ -2003,7 +1932,7 @@
         <v>API-053</v>
       </c>
       <c r="C54" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom History Architecture Subsystem</v>
       </c>
       <c r="D54" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2015,10 +1944,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="55">
@@ -2029,7 +1958,7 @@
         <v>API-054</v>
       </c>
       <c r="C55" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom History Architecture Subsystem</v>
       </c>
       <c r="D55" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2041,10 +1970,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="56">
@@ -2055,7 +1984,7 @@
         <v>API-055</v>
       </c>
       <c r="C56" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D56" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2067,10 +1996,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="57">
@@ -2081,7 +2010,7 @@
         <v>API-056</v>
       </c>
       <c r="C57" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D57" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2093,10 +2022,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="58">
@@ -2107,7 +2036,7 @@
         <v>API-057</v>
       </c>
       <c r="C58" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D58" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2119,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="59">
@@ -2133,7 +2062,7 @@
         <v>API-058</v>
       </c>
       <c r="C59" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Draft Architecture Subsystem</v>
       </c>
       <c r="D59" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2145,10 +2074,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="60">
@@ -2159,7 +2088,7 @@
         <v>API-059</v>
       </c>
       <c r="C60" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Draft Architecture Subsystem</v>
       </c>
       <c r="D60" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2171,10 +2100,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="61">
@@ -2185,7 +2114,7 @@
         <v>API-060</v>
       </c>
       <c r="C61" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pdf Architecture Subsystem</v>
       </c>
       <c r="D61" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2197,10 +2126,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="62">
@@ -2211,7 +2140,7 @@
         <v>API-061</v>
       </c>
       <c r="C62" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Categories Architecture Subsystem</v>
       </c>
       <c r="D62" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2226,7 +2155,7 @@
         <v>18</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="63">
@@ -2237,7 +2166,7 @@
         <v>API-062</v>
       </c>
       <c r="C63" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Rules Architecture Subsystem</v>
       </c>
       <c r="D63" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2249,10 +2178,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="64">
@@ -2263,7 +2192,7 @@
         <v>API-063</v>
       </c>
       <c r="C64" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Share Architecture Subsystem</v>
       </c>
       <c r="D64" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2275,10 +2204,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="65">
@@ -2289,7 +2218,7 @@
         <v>API-064</v>
       </c>
       <c r="C65" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Shared Architecture Subsystem</v>
       </c>
       <c r="D65" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2301,10 +2230,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="66">
@@ -2315,7 +2244,7 @@
         <v>API-065</v>
       </c>
       <c r="C66" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Put Symptom Record Architecture Subsystem</v>
       </c>
       <c r="D66" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2327,10 +2256,10 @@
         <v>PASS</v>
       </c>
       <c r="G66">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="67">
@@ -2341,7 +2270,7 @@
         <v>API-066</v>
       </c>
       <c r="C67" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Image Architecture Subsystem</v>
       </c>
       <c r="D67" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2353,10 +2282,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="68">
@@ -2367,7 +2296,7 @@
         <v>API-067</v>
       </c>
       <c r="C68" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Voice Architecture Subsystem</v>
       </c>
       <c r="D68" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2379,10 +2308,10 @@
         <v>PASS</v>
       </c>
       <c r="G68">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="69">
@@ -2393,7 +2322,7 @@
         <v>API-068</v>
       </c>
       <c r="C69" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Emergency Architecture Subsystem</v>
       </c>
       <c r="D69" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2405,10 +2334,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="70">
@@ -2419,7 +2348,7 @@
         <v>API-069</v>
       </c>
       <c r="C70" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Wisdom Architecture Subsystem</v>
       </c>
       <c r="D70" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2431,10 +2360,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="71">
@@ -2445,7 +2374,7 @@
         <v>API-070</v>
       </c>
       <c r="C71" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Sensitivity Architecture Subsystem</v>
       </c>
       <c r="D71" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2457,10 +2386,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="72">
@@ -2471,7 +2400,7 @@
         <v>API-071</v>
       </c>
       <c r="C72" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Tmj Architecture Subsystem</v>
       </c>
       <c r="D72" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2483,10 +2412,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="73">
@@ -2497,7 +2426,7 @@
         <v>API-072</v>
       </c>
       <c r="C73" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Halitosis Architecture Subsystem</v>
       </c>
       <c r="D73" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2509,10 +2438,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="74">
@@ -2523,7 +2452,7 @@
         <v>API-073</v>
       </c>
       <c r="C74" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Canker Architecture Subsystem</v>
       </c>
       <c r="D74" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2535,10 +2464,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="75">
@@ -2549,7 +2478,7 @@
         <v>API-074</v>
       </c>
       <c r="C75" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Dry Architecture Subsystem</v>
       </c>
       <c r="D75" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2561,10 +2490,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="76">
@@ -2575,7 +2504,7 @@
         <v>API-075</v>
       </c>
       <c r="C76" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Trauma Architecture Subsystem</v>
       </c>
       <c r="D76" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2587,10 +2516,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="77">
@@ -2601,7 +2530,7 @@
         <v>API-076</v>
       </c>
       <c r="C77" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pediatric Architecture Subsystem</v>
       </c>
       <c r="D77" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2613,10 +2542,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="78">
@@ -2627,7 +2556,7 @@
         <v>API-077</v>
       </c>
       <c r="C78" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Pregnancy Architecture Subsystem</v>
       </c>
       <c r="D78" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2639,10 +2568,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="79">
@@ -2653,7 +2582,7 @@
         <v>API-078</v>
       </c>
       <c r="C79" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Diabetes Architecture Subsystem</v>
       </c>
       <c r="D79" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2665,10 +2594,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="80">
@@ -2679,7 +2608,7 @@
         <v>API-079</v>
       </c>
       <c r="C80" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Smoker Architecture Subsystem</v>
       </c>
       <c r="D80" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2691,10 +2620,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="81">
@@ -2705,7 +2634,7 @@
         <v>API-080</v>
       </c>
       <c r="C81" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Cambra Architecture Subsystem</v>
       </c>
       <c r="D81" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2720,7 +2649,7 @@
         <v>20</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="82">
@@ -2731,7 +2660,7 @@
         <v>API-081</v>
       </c>
       <c r="C82" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Stats Architecture Subsystem</v>
       </c>
       <c r="D82" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2743,10 +2672,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="83">
@@ -2757,7 +2686,7 @@
         <v>API-082</v>
       </c>
       <c r="C83" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Export Architecture Subsystem</v>
       </c>
       <c r="D83" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2769,10 +2698,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="84">
@@ -2783,7 +2712,7 @@
         <v>API-083</v>
       </c>
       <c r="C84" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom History Architecture Subsystem</v>
       </c>
       <c r="D84" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2795,10 +2724,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="85">
@@ -2809,7 +2738,7 @@
         <v>API-084</v>
       </c>
       <c r="C85" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Duration Architecture Subsystem</v>
       </c>
       <c r="D85" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2821,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="86">
@@ -2835,7 +2764,7 @@
         <v>API-085</v>
       </c>
       <c r="C86" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Severity Architecture Subsystem</v>
       </c>
       <c r="D86" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2847,10 +2776,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="87">
@@ -2861,7 +2790,7 @@
         <v>API-086</v>
       </c>
       <c r="C87" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Caregiver Architecture Subsystem</v>
       </c>
       <c r="D87" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2873,10 +2802,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="88">
@@ -2887,7 +2816,7 @@
         <v>API-087</v>
       </c>
       <c r="C88" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Caregiver Architecture Subsystem</v>
       </c>
       <c r="D88" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2899,10 +2828,10 @@
         <v>PASS</v>
       </c>
       <c r="G88">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="89">
@@ -2913,7 +2842,7 @@
         <v>API-088</v>
       </c>
       <c r="C89" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Webhook Architecture Subsystem</v>
       </c>
       <c r="D89" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2925,10 +2854,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="90">
@@ -2939,7 +2868,7 @@
         <v>API-089</v>
       </c>
       <c r="C90" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Delete Symptom Webhook Architecture Subsystem</v>
       </c>
       <c r="D90" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2951,10 +2880,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="91">
@@ -2965,7 +2894,7 @@
         <v>API-090</v>
       </c>
       <c r="C91" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Diagnostic Architecture Subsystem</v>
       </c>
       <c r="D91" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -2977,10 +2906,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="92">
@@ -2991,7 +2920,7 @@
         <v>API-091</v>
       </c>
       <c r="C92" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Re Architecture Subsystem</v>
       </c>
       <c r="D92" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3003,10 +2932,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="93">
@@ -3017,7 +2946,7 @@
         <v>API-092</v>
       </c>
       <c r="C93" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Red Architecture Subsystem</v>
       </c>
       <c r="D93" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3029,10 +2958,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="94">
@@ -3043,7 +2972,7 @@
         <v>API-093</v>
       </c>
       <c r="C94" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Feedback Architecture Subsystem</v>
       </c>
       <c r="D94" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3055,10 +2984,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="95">
@@ -3069,7 +2998,7 @@
         <v>API-094</v>
       </c>
       <c r="C95" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Tooth Architecture Subsystem</v>
       </c>
       <c r="D95" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3081,10 +3010,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="96">
@@ -3095,7 +3024,7 @@
         <v>API-095</v>
       </c>
       <c r="C96" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Dental Architecture Subsystem</v>
       </c>
       <c r="D96" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3107,10 +3036,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.002Z</v>
       </c>
     </row>
     <row r="97">
@@ -3121,7 +3050,7 @@
         <v>API-096</v>
       </c>
       <c r="C97" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Anonymized Architecture Subsystem</v>
       </c>
       <c r="D97" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3133,10 +3062,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="98">
@@ -3147,7 +3076,7 @@
         <v>API-097</v>
       </c>
       <c r="C98" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Audit Architecture Subsystem</v>
       </c>
       <c r="D98" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3159,10 +3088,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="99">
@@ -3173,7 +3102,7 @@
         <v>API-098</v>
       </c>
       <c r="C99" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Post Symptom Bulk Architecture Subsystem</v>
       </c>
       <c r="D99" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3185,10 +3114,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="100">
@@ -3199,7 +3128,7 @@
         <v>API-099</v>
       </c>
       <c r="C100" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Get Symptom Api Architecture Subsystem</v>
       </c>
       <c r="D100" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3214,7 +3143,7 @@
         <v>21</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="101">
@@ -3225,7 +3154,7 @@
         <v>API-100</v>
       </c>
       <c r="C101" t="str">
-        <v>Symptom Checker &amp; Diagnostics</v>
+        <v>Symptom Checker Api Architecture Subsystem</v>
       </c>
       <c r="D101" t="str">
         <v>test_02_symptom_checker.py</v>
@@ -3237,10 +3166,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T05:04:19.972Z</v>
+        <v>2026-08-06T05:06:56.003Z</v>
       </c>
     </row>
     <row r="102">
@@ -3251,7 +3180,7 @@
         <v>API-101</v>
       </c>
       <c r="C102" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointments Slots Architecture Subsystem</v>
       </c>
       <c r="D102" t="str">
         <v>test_03_appointments.py</v>
@@ -3263,10 +3192,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="103">
@@ -3277,7 +3206,7 @@
         <v>API-102</v>
       </c>
       <c r="C103" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointments Slots Architecture Subsystem</v>
       </c>
       <c r="D103" t="str">
         <v>test_03_appointments.py</v>
@@ -3289,10 +3218,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="104">
@@ -3303,7 +3232,7 @@
         <v>API-103</v>
       </c>
       <c r="C104" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointments Slots Architecture Subsystem</v>
       </c>
       <c r="D104" t="str">
         <v>test_03_appointments.py</v>
@@ -3315,10 +3244,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="105">
@@ -3329,7 +3258,7 @@
         <v>API-104</v>
       </c>
       <c r="C105" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointments Book Architecture Subsystem</v>
       </c>
       <c r="D105" t="str">
         <v>test_03_appointments.py</v>
@@ -3341,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="106">
@@ -3355,7 +3284,7 @@
         <v>API-105</v>
       </c>
       <c r="C106" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointments Book Architecture Subsystem</v>
       </c>
       <c r="D106" t="str">
         <v>test_03_appointments.py</v>
@@ -3367,10 +3296,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="107">
@@ -3381,7 +3310,7 @@
         <v>API-106</v>
       </c>
       <c r="C107" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointments Book Architecture Subsystem</v>
       </c>
       <c r="D107" t="str">
         <v>test_03_appointments.py</v>
@@ -3393,10 +3322,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="108">
@@ -3407,7 +3336,7 @@
         <v>API-107</v>
       </c>
       <c r="C108" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointments List Architecture Subsystem</v>
       </c>
       <c r="D108" t="str">
         <v>test_03_appointments.py</v>
@@ -3419,10 +3348,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="109">
@@ -3433,7 +3362,7 @@
         <v>API-108</v>
       </c>
       <c r="C109" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointments List Architecture Subsystem</v>
       </c>
       <c r="D109" t="str">
         <v>test_03_appointments.py</v>
@@ -3445,10 +3374,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="110">
@@ -3459,7 +3388,7 @@
         <v>API-109</v>
       </c>
       <c r="C110" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Detail Architecture Subsystem</v>
       </c>
       <c r="D110" t="str">
         <v>test_03_appointments.py</v>
@@ -3471,10 +3400,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="111">
@@ -3485,7 +3414,7 @@
         <v>API-110</v>
       </c>
       <c r="C111" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Put Appointment Reschedule Architecture Subsystem</v>
       </c>
       <c r="D111" t="str">
         <v>test_03_appointments.py</v>
@@ -3497,10 +3426,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="112">
@@ -3511,7 +3440,7 @@
         <v>API-111</v>
       </c>
       <c r="C112" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Delete Appointment Cancel Architecture Subsystem</v>
       </c>
       <c r="D112" t="str">
         <v>test_03_appointments.py</v>
@@ -3523,10 +3452,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="113">
@@ -3537,7 +3466,7 @@
         <v>API-112</v>
       </c>
       <c r="C113" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Checkin Architecture Subsystem</v>
       </c>
       <c r="D113" t="str">
         <v>test_03_appointments.py</v>
@@ -3552,7 +3481,7 @@
         <v>26</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="114">
@@ -3563,7 +3492,7 @@
         <v>API-113</v>
       </c>
       <c r="C114" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Receipt Architecture Subsystem</v>
       </c>
       <c r="D114" t="str">
         <v>test_03_appointments.py</v>
@@ -3575,10 +3504,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="115">
@@ -3589,7 +3518,7 @@
         <v>API-114</v>
       </c>
       <c r="C115" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Doctors Directory Architecture Subsystem</v>
       </c>
       <c r="D115" t="str">
         <v>test_03_appointments.py</v>
@@ -3601,10 +3530,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="116">
@@ -3615,7 +3544,7 @@
         <v>API-115</v>
       </c>
       <c r="C116" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Doctors Directory Architecture Subsystem</v>
       </c>
       <c r="D116" t="str">
         <v>test_03_appointments.py</v>
@@ -3627,10 +3556,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="117">
@@ -3641,7 +3570,7 @@
         <v>API-116</v>
       </c>
       <c r="C117" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Doctors Directory Architecture Subsystem</v>
       </c>
       <c r="D117" t="str">
         <v>test_03_appointments.py</v>
@@ -3653,10 +3582,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="118">
@@ -3667,7 +3596,7 @@
         <v>API-117</v>
       </c>
       <c r="C118" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Doctor Profile Architecture Subsystem</v>
       </c>
       <c r="D118" t="str">
         <v>test_03_appointments.py</v>
@@ -3679,10 +3608,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="119">
@@ -3693,7 +3622,7 @@
         <v>API-118</v>
       </c>
       <c r="C119" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Doctor Reviews Architecture Subsystem</v>
       </c>
       <c r="D119" t="str">
         <v>test_03_appointments.py</v>
@@ -3705,10 +3634,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="120">
@@ -3719,7 +3648,7 @@
         <v>API-119</v>
       </c>
       <c r="C120" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Doctor Review Architecture Subsystem</v>
       </c>
       <c r="D120" t="str">
         <v>test_03_appointments.py</v>
@@ -3731,10 +3660,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="121">
@@ -3745,7 +3674,7 @@
         <v>API-120</v>
       </c>
       <c r="C121" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Stripe Architecture Subsystem</v>
       </c>
       <c r="D121" t="str">
         <v>test_03_appointments.py</v>
@@ -3757,10 +3686,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="122">
@@ -3771,7 +3700,7 @@
         <v>API-121</v>
       </c>
       <c r="C122" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Stripe Architecture Subsystem</v>
       </c>
       <c r="D122" t="str">
         <v>test_03_appointments.py</v>
@@ -3783,10 +3712,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="123">
@@ -3797,7 +3726,7 @@
         <v>API-122</v>
       </c>
       <c r="C123" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Ical Architecture Subsystem</v>
       </c>
       <c r="D123" t="str">
         <v>test_03_appointments.py</v>
@@ -3809,10 +3738,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="124">
@@ -3823,7 +3752,7 @@
         <v>API-123</v>
       </c>
       <c r="C124" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Google Architecture Subsystem</v>
       </c>
       <c r="D124" t="str">
         <v>test_03_appointments.py</v>
@@ -3835,10 +3764,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="125">
@@ -3849,7 +3778,7 @@
         <v>API-124</v>
       </c>
       <c r="C125" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Waiting Architecture Subsystem</v>
       </c>
       <c r="D125" t="str">
         <v>test_03_appointments.py</v>
@@ -3861,10 +3790,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="126">
@@ -3875,7 +3804,7 @@
         <v>API-125</v>
       </c>
       <c r="C126" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Delete Appointment Waiting Architecture Subsystem</v>
       </c>
       <c r="D126" t="str">
         <v>test_03_appointments.py</v>
@@ -3887,10 +3816,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="127">
@@ -3901,7 +3830,7 @@
         <v>API-126</v>
       </c>
       <c r="C127" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Family Architecture Subsystem</v>
       </c>
       <c r="D127" t="str">
         <v>test_03_appointments.py</v>
@@ -3913,10 +3842,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="128">
@@ -3927,7 +3856,7 @@
         <v>API-127</v>
       </c>
       <c r="C128" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Family Architecture Subsystem</v>
       </c>
       <c r="D128" t="str">
         <v>test_03_appointments.py</v>
@@ -3939,10 +3868,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="129">
@@ -3953,7 +3882,7 @@
         <v>API-128</v>
       </c>
       <c r="C129" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Telehealth Room Architecture Subsystem</v>
       </c>
       <c r="D129" t="str">
         <v>test_03_appointments.py</v>
@@ -3965,10 +3894,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="130">
@@ -3979,7 +3908,7 @@
         <v>API-129</v>
       </c>
       <c r="C130" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Telehealth End Architecture Subsystem</v>
       </c>
       <c r="D130" t="str">
         <v>test_03_appointments.py</v>
@@ -3991,10 +3920,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="131">
@@ -4005,7 +3934,7 @@
         <v>API-130</v>
       </c>
       <c r="C131" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Previsit Architecture Subsystem</v>
       </c>
       <c r="D131" t="str">
         <v>test_03_appointments.py</v>
@@ -4017,10 +3946,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="132">
@@ -4031,7 +3960,7 @@
         <v>API-131</v>
       </c>
       <c r="C132" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Previsit Architecture Subsystem</v>
       </c>
       <c r="D132" t="str">
         <v>test_03_appointments.py</v>
@@ -4043,10 +3972,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="133">
@@ -4057,7 +3986,7 @@
         <v>API-132</v>
       </c>
       <c r="C133" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Attachments Architecture Subsystem</v>
       </c>
       <c r="D133" t="str">
         <v>test_03_appointments.py</v>
@@ -4069,10 +3998,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="134">
@@ -4083,7 +4012,7 @@
         <v>API-133</v>
       </c>
       <c r="C134" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Attachments Architecture Subsystem</v>
       </c>
       <c r="D134" t="str">
         <v>test_03_appointments.py</v>
@@ -4095,10 +4024,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="135">
@@ -4109,7 +4038,7 @@
         <v>API-134</v>
       </c>
       <c r="C135" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Delete Appointment Attachments Architecture Subsystem</v>
       </c>
       <c r="D135" t="str">
         <v>test_03_appointments.py</v>
@@ -4121,10 +4050,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="136">
@@ -4135,7 +4064,7 @@
         <v>API-135</v>
       </c>
       <c r="C136" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Clinic Locations Architecture Subsystem</v>
       </c>
       <c r="D136" t="str">
         <v>test_03_appointments.py</v>
@@ -4147,10 +4076,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="137">
@@ -4161,7 +4090,7 @@
         <v>API-136</v>
       </c>
       <c r="C137" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Clinic Location Architecture Subsystem</v>
       </c>
       <c r="D137" t="str">
         <v>test_03_appointments.py</v>
@@ -4173,10 +4102,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="138">
@@ -4187,7 +4116,7 @@
         <v>API-137</v>
       </c>
       <c r="C138" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Put Doctor Schedule Architecture Subsystem</v>
       </c>
       <c r="D138" t="str">
         <v>test_03_appointments.py</v>
@@ -4199,10 +4128,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="139">
@@ -4213,7 +4142,7 @@
         <v>API-138</v>
       </c>
       <c r="C139" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Doctor Vacation Architecture Subsystem</v>
       </c>
       <c r="D139" t="str">
         <v>test_03_appointments.py</v>
@@ -4225,10 +4154,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="140">
@@ -4239,7 +4168,7 @@
         <v>API-139</v>
       </c>
       <c r="C140" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment History Architecture Subsystem</v>
       </c>
       <c r="D140" t="str">
         <v>test_03_appointments.py</v>
@@ -4251,10 +4180,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="141">
@@ -4265,7 +4194,7 @@
         <v>API-140</v>
       </c>
       <c r="C141" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Qr Architecture Subsystem</v>
       </c>
       <c r="D141" t="str">
         <v>test_03_appointments.py</v>
@@ -4277,10 +4206,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="142">
@@ -4291,7 +4220,7 @@
         <v>API-141</v>
       </c>
       <c r="C142" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Rx Architecture Subsystem</v>
       </c>
       <c r="D142" t="str">
         <v>test_03_appointments.py</v>
@@ -4303,10 +4232,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="143">
@@ -4317,7 +4246,7 @@
         <v>API-142</v>
       </c>
       <c r="C143" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Pharmacy Architecture Subsystem</v>
       </c>
       <c r="D143" t="str">
         <v>test_03_appointments.py</v>
@@ -4329,10 +4258,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="144">
@@ -4343,7 +4272,7 @@
         <v>API-143</v>
       </c>
       <c r="C144" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Reminder Architecture Subsystem</v>
       </c>
       <c r="D144" t="str">
         <v>test_03_appointments.py</v>
@@ -4355,10 +4284,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="145">
@@ -4369,7 +4298,7 @@
         <v>API-144</v>
       </c>
       <c r="C145" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Reminder Architecture Subsystem</v>
       </c>
       <c r="D145" t="str">
         <v>test_03_appointments.py</v>
@@ -4381,10 +4310,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="146">
@@ -4395,7 +4324,7 @@
         <v>API-145</v>
       </c>
       <c r="C146" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Timezone Architecture Subsystem</v>
       </c>
       <c r="D146" t="str">
         <v>test_03_appointments.py</v>
@@ -4407,10 +4336,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="147">
@@ -4421,7 +4350,7 @@
         <v>API-146</v>
       </c>
       <c r="C147" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment No Architecture Subsystem</v>
       </c>
       <c r="D147" t="str">
         <v>test_03_appointments.py</v>
@@ -4433,10 +4362,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="148">
@@ -4447,7 +4376,7 @@
         <v>API-147</v>
       </c>
       <c r="C148" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Post Appointment Coupon Architecture Subsystem</v>
       </c>
       <c r="D148" t="str">
         <v>test_03_appointments.py</v>
@@ -4459,10 +4388,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.014Z</v>
       </c>
     </row>
     <row r="149">
@@ -4473,7 +4402,7 @@
         <v>API-148</v>
       </c>
       <c r="C149" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Get Appointment Cancellation Architecture Subsystem</v>
       </c>
       <c r="D149" t="str">
         <v>test_03_appointments.py</v>
@@ -4485,10 +4414,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.015Z</v>
       </c>
     </row>
     <row r="150">
@@ -4499,7 +4428,7 @@
         <v>API-149</v>
       </c>
       <c r="C150" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Put Appointment Notes Architecture Subsystem</v>
       </c>
       <c r="D150" t="str">
         <v>test_03_appointments.py</v>
@@ -4511,10 +4440,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.015Z</v>
       </c>
     </row>
     <row r="151">
@@ -4525,7 +4454,7 @@
         <v>API-150</v>
       </c>
       <c r="C151" t="str">
-        <v>Appointment Scheduling</v>
+        <v>Appointments Api Full Architecture Subsystem</v>
       </c>
       <c r="D151" t="str">
         <v>test_03_appointments.py</v>
@@ -4537,10 +4466,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T05:04:19.986Z</v>
+        <v>2026-08-06T05:06:56.015Z</v>
       </c>
     </row>
     <row r="152">
@@ -4551,7 +4480,7 @@
         <v>API-151</v>
       </c>
       <c r="C152" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Message Architecture Subsystem</v>
       </c>
       <c r="D152" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4563,10 +4492,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="153">
@@ -4577,7 +4506,7 @@
         <v>API-152</v>
       </c>
       <c r="C153" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Message Architecture Subsystem</v>
       </c>
       <c r="D153" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4589,10 +4518,10 @@
         <v>PASS</v>
       </c>
       <c r="G153">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="154">
@@ -4603,7 +4532,7 @@
         <v>API-153</v>
       </c>
       <c r="C154" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Conversations Architecture Subsystem</v>
       </c>
       <c r="D154" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4618,7 +4547,7 @@
         <v>10</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="155">
@@ -4629,7 +4558,7 @@
         <v>API-154</v>
       </c>
       <c r="C155" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Conversation Architecture Subsystem</v>
       </c>
       <c r="D155" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4641,10 +4570,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="156">
@@ -4655,7 +4584,7 @@
         <v>API-155</v>
       </c>
       <c r="C156" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Delete Chat Conversation Architecture Subsystem</v>
       </c>
       <c r="D156" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4667,10 +4596,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="157">
@@ -4681,7 +4610,7 @@
         <v>API-156</v>
       </c>
       <c r="C157" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Put Chat Conversation Architecture Subsystem</v>
       </c>
       <c r="D157" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4693,10 +4622,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="158">
@@ -4707,7 +4636,7 @@
         <v>API-157</v>
       </c>
       <c r="C158" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Message Architecture Subsystem</v>
       </c>
       <c r="D158" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4719,10 +4648,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="159">
@@ -4733,7 +4662,7 @@
         <v>API-158</v>
       </c>
       <c r="C159" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Message Architecture Subsystem</v>
       </c>
       <c r="D159" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4745,10 +4674,10 @@
         <v>PASS</v>
       </c>
       <c r="G159">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="160">
@@ -4759,7 +4688,7 @@
         <v>API-159</v>
       </c>
       <c r="C160" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Audio Architecture Subsystem</v>
       </c>
       <c r="D160" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4771,10 +4700,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="161">
@@ -4785,7 +4714,7 @@
         <v>API-160</v>
       </c>
       <c r="C161" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Feedback Architecture Subsystem</v>
       </c>
       <c r="D161" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4797,10 +4726,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="162">
@@ -4811,7 +4740,7 @@
         <v>API-161</v>
       </c>
       <c r="C162" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Regenerate Architecture Subsystem</v>
       </c>
       <c r="D162" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4823,10 +4752,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="163">
@@ -4837,7 +4766,7 @@
         <v>API-162</v>
       </c>
       <c r="C163" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat History Architecture Subsystem</v>
       </c>
       <c r="D163" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4849,10 +4778,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="164">
@@ -4863,7 +4792,7 @@
         <v>API-163</v>
       </c>
       <c r="C164" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Transcript Architecture Subsystem</v>
       </c>
       <c r="D164" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4875,10 +4804,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="165">
@@ -4889,7 +4818,7 @@
         <v>API-164</v>
       </c>
       <c r="C165" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Transcript Architecture Subsystem</v>
       </c>
       <c r="D165" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4901,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="166">
@@ -4915,7 +4844,7 @@
         <v>API-165</v>
       </c>
       <c r="C166" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Suggested Architecture Subsystem</v>
       </c>
       <c r="D166" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4927,10 +4856,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="167">
@@ -4941,7 +4870,7 @@
         <v>API-166</v>
       </c>
       <c r="C167" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Disclaimer Architecture Subsystem</v>
       </c>
       <c r="D167" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4953,10 +4882,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="168">
@@ -4967,7 +4896,7 @@
         <v>API-167</v>
       </c>
       <c r="C168" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Token Architecture Subsystem</v>
       </c>
       <c r="D168" t="str">
         <v>test_04_ai_chat.py</v>
@@ -4979,10 +4908,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="169">
@@ -4993,7 +4922,7 @@
         <v>API-168</v>
       </c>
       <c r="C169" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Persona Architecture Subsystem</v>
       </c>
       <c r="D169" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5005,10 +4934,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="170">
@@ -5019,7 +4948,7 @@
         <v>API-169</v>
       </c>
       <c r="C170" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Clear Architecture Subsystem</v>
       </c>
       <c r="D170" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5031,10 +4960,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="171">
@@ -5045,7 +4974,7 @@
         <v>API-170</v>
       </c>
       <c r="C171" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Glossary Architecture Subsystem</v>
       </c>
       <c r="D171" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5057,10 +4986,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="172">
@@ -5071,7 +5000,7 @@
         <v>API-171</v>
       </c>
       <c r="C172" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Medication Architecture Subsystem</v>
       </c>
       <c r="D172" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5083,10 +5012,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="173">
@@ -5097,7 +5026,7 @@
         <v>API-172</v>
       </c>
       <c r="C173" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Emergency Architecture Subsystem</v>
       </c>
       <c r="D173" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5109,10 +5038,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="174">
@@ -5123,7 +5052,7 @@
         <v>API-173</v>
       </c>
       <c r="C174" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Book Architecture Subsystem</v>
       </c>
       <c r="D174" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5135,10 +5064,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="175">
@@ -5149,7 +5078,7 @@
         <v>API-174</v>
       </c>
       <c r="C175" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Unread Architecture Subsystem</v>
       </c>
       <c r="D175" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5161,10 +5090,10 @@
         <v>PASS</v>
       </c>
       <c r="G175">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="176">
@@ -5175,7 +5104,7 @@
         <v>API-175</v>
       </c>
       <c r="C176" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Report Architecture Subsystem</v>
       </c>
       <c r="D176" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5187,10 +5116,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="177">
@@ -5201,7 +5130,7 @@
         <v>API-176</v>
       </c>
       <c r="C177" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Session Architecture Subsystem</v>
       </c>
       <c r="D177" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5213,10 +5142,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="178">
@@ -5227,7 +5156,7 @@
         <v>API-177</v>
       </c>
       <c r="C178" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Multi Architecture Subsystem</v>
       </c>
       <c r="D178" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5239,10 +5168,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="179">
@@ -5253,7 +5182,7 @@
         <v>API-178</v>
       </c>
       <c r="C179" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Rate Architecture Subsystem</v>
       </c>
       <c r="D179" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5265,10 +5194,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="180">
@@ -5279,7 +5208,7 @@
         <v>API-179</v>
       </c>
       <c r="C180" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Socket Architecture Subsystem</v>
       </c>
       <c r="D180" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5291,10 +5220,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="181">
@@ -5305,7 +5234,7 @@
         <v>API-180</v>
       </c>
       <c r="C181" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat System Architecture Subsystem</v>
       </c>
       <c r="D181" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5317,10 +5246,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="182">
@@ -5331,7 +5260,7 @@
         <v>API-181</v>
       </c>
       <c r="C182" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Code Architecture Subsystem</v>
       </c>
       <c r="D182" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5343,10 +5272,10 @@
         <v>PASS</v>
       </c>
       <c r="G182">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="183">
@@ -5357,7 +5286,7 @@
         <v>API-182</v>
       </c>
       <c r="C183" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Hyperlink Architecture Subsystem</v>
       </c>
       <c r="D183" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5369,10 +5298,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="184">
@@ -5383,7 +5312,7 @@
         <v>API-183</v>
       </c>
       <c r="C184" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Offline Architecture Subsystem</v>
       </c>
       <c r="D184" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5395,10 +5324,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="185">
@@ -5409,7 +5338,7 @@
         <v>API-184</v>
       </c>
       <c r="C185" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Context Architecture Subsystem</v>
       </c>
       <c r="D185" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5421,10 +5350,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="186">
@@ -5435,7 +5364,7 @@
         <v>API-185</v>
       </c>
       <c r="C186" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Stop Architecture Subsystem</v>
       </c>
       <c r="D186" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5447,10 +5376,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="187">
@@ -5461,7 +5390,7 @@
         <v>API-186</v>
       </c>
       <c r="C187" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Auto Architecture Subsystem</v>
       </c>
       <c r="D187" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5473,10 +5402,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="188">
@@ -5487,7 +5416,7 @@
         <v>API-187</v>
       </c>
       <c r="C188" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Pin Architecture Subsystem</v>
       </c>
       <c r="D188" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5499,10 +5428,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="189">
@@ -5513,7 +5442,7 @@
         <v>API-188</v>
       </c>
       <c r="C189" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Pinned Architecture Subsystem</v>
       </c>
       <c r="D189" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5525,10 +5454,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="190">
@@ -5539,7 +5468,7 @@
         <v>API-189</v>
       </c>
       <c r="C190" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Delete Chat Pinned Architecture Subsystem</v>
       </c>
       <c r="D190" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5551,10 +5480,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="191">
@@ -5565,7 +5494,7 @@
         <v>API-190</v>
       </c>
       <c r="C191" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Export Architecture Subsystem</v>
       </c>
       <c r="D191" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5577,10 +5506,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="192">
@@ -5591,7 +5520,7 @@
         <v>API-191</v>
       </c>
       <c r="C192" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Active Architecture Subsystem</v>
       </c>
       <c r="D192" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5606,7 +5535,7 @@
         <v>27</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="193">
@@ -5617,7 +5546,7 @@
         <v>API-192</v>
       </c>
       <c r="C193" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Inject Architecture Subsystem</v>
       </c>
       <c r="D193" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5629,10 +5558,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.026Z</v>
       </c>
     </row>
     <row r="194">
@@ -5643,7 +5572,7 @@
         <v>API-193</v>
       </c>
       <c r="C194" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Llm Architecture Subsystem</v>
       </c>
       <c r="D194" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5655,10 +5584,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="195">
@@ -5669,7 +5598,7 @@
         <v>API-194</v>
       </c>
       <c r="C195" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Audio Architecture Subsystem</v>
       </c>
       <c r="D195" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5681,10 +5610,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="196">
@@ -5695,7 +5624,7 @@
         <v>API-195</v>
       </c>
       <c r="C196" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Character Architecture Subsystem</v>
       </c>
       <c r="D196" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5707,10 +5636,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="197">
@@ -5721,7 +5650,7 @@
         <v>API-196</v>
       </c>
       <c r="C197" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Emoji Architecture Subsystem</v>
       </c>
       <c r="D197" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5733,10 +5662,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="198">
@@ -5747,7 +5676,7 @@
         <v>API-197</v>
       </c>
       <c r="C198" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Security Architecture Subsystem</v>
       </c>
       <c r="D198" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5759,10 +5688,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="199">
@@ -5773,7 +5702,7 @@
         <v>API-198</v>
       </c>
       <c r="C199" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Post Chat Voice Architecture Subsystem</v>
       </c>
       <c r="D199" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5785,10 +5714,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="200">
@@ -5799,7 +5728,7 @@
         <v>API-199</v>
       </c>
       <c r="C200" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Get Chat Audit Architecture Subsystem</v>
       </c>
       <c r="D200" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5811,10 +5740,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="201">
@@ -5825,7 +5754,7 @@
         <v>API-200</v>
       </c>
       <c r="C201" t="str">
-        <v>AI Consultation Chatbot</v>
+        <v>Ai Chat Api Architecture Subsystem</v>
       </c>
       <c r="D201" t="str">
         <v>test_04_ai_chat.py</v>
@@ -5837,10 +5766,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T05:04:19.998Z</v>
+        <v>2026-08-06T05:06:56.027Z</v>
       </c>
     </row>
     <row r="202">
@@ -5851,7 +5780,7 @@
         <v>API-201</v>
       </c>
       <c r="C202" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D202" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5863,10 +5792,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="203">
@@ -5877,7 +5806,7 @@
         <v>API-202</v>
       </c>
       <c r="C203" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D203" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5889,10 +5818,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="204">
@@ -5903,7 +5832,7 @@
         <v>API-203</v>
       </c>
       <c r="C204" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Upload Architecture Subsystem</v>
       </c>
       <c r="D204" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5915,10 +5844,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="205">
@@ -5929,7 +5858,7 @@
         <v>API-204</v>
       </c>
       <c r="C205" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Results Architecture Subsystem</v>
       </c>
       <c r="D205" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5941,10 +5870,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="206">
@@ -5955,7 +5884,7 @@
         <v>API-205</v>
       </c>
       <c r="C206" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Results Architecture Subsystem</v>
       </c>
       <c r="D206" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5967,10 +5896,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="207">
@@ -5981,7 +5910,7 @@
         <v>API-206</v>
       </c>
       <c r="C207" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Result Architecture Subsystem</v>
       </c>
       <c r="D207" t="str">
         <v>test_05_dental_scan.py</v>
@@ -5993,10 +5922,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="208">
@@ -6007,7 +5936,7 @@
         <v>API-207</v>
       </c>
       <c r="C208" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan History Architecture Subsystem</v>
       </c>
       <c r="D208" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6019,10 +5948,10 @@
         <v>PASS</v>
       </c>
       <c r="G208">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="209">
@@ -6033,7 +5962,7 @@
         <v>API-208</v>
       </c>
       <c r="C209" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D209" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6045,10 +5974,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="210">
@@ -6059,7 +5988,7 @@
         <v>API-209</v>
       </c>
       <c r="C210" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D210" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6071,10 +6000,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="211">
@@ -6085,7 +6014,7 @@
         <v>API-210</v>
       </c>
       <c r="C211" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Heatmap Architecture Subsystem</v>
       </c>
       <c r="D211" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6097,10 +6026,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="212">
@@ -6111,7 +6040,7 @@
         <v>API-211</v>
       </c>
       <c r="C212" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Analysis Architecture Subsystem</v>
       </c>
       <c r="D212" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6123,10 +6052,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="213">
@@ -6137,7 +6066,7 @@
         <v>API-212</v>
       </c>
       <c r="C213" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Compare Architecture Subsystem</v>
       </c>
       <c r="D213" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6149,10 +6078,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="214">
@@ -6163,7 +6092,7 @@
         <v>API-213</v>
       </c>
       <c r="C214" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Share Architecture Subsystem</v>
       </c>
       <c r="D214" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6175,10 +6104,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="215">
@@ -6189,7 +6118,7 @@
         <v>API-214</v>
       </c>
       <c r="C215" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Put Scan Annotations Architecture Subsystem</v>
       </c>
       <c r="D215" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6201,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="216">
@@ -6215,7 +6144,7 @@
         <v>API-215</v>
       </c>
       <c r="C216" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Annotations Architecture Subsystem</v>
       </c>
       <c r="D216" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6227,10 +6156,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="217">
@@ -6241,7 +6170,7 @@
         <v>API-216</v>
       </c>
       <c r="C217" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Annotation Architecture Subsystem</v>
       </c>
       <c r="D217" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6253,10 +6182,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="218">
@@ -6267,7 +6196,7 @@
         <v>API-217</v>
       </c>
       <c r="C218" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Quality Architecture Subsystem</v>
       </c>
       <c r="D218" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6279,10 +6208,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="219">
@@ -6293,7 +6222,7 @@
         <v>API-218</v>
       </c>
       <c r="C219" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Retake Architecture Subsystem</v>
       </c>
       <c r="D219" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6305,10 +6234,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="220">
@@ -6319,7 +6248,7 @@
         <v>API-219</v>
       </c>
       <c r="C220" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Confidence Architecture Subsystem</v>
       </c>
       <c r="D220" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6331,10 +6260,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="221">
@@ -6345,7 +6274,7 @@
         <v>API-220</v>
       </c>
       <c r="C221" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Measure Architecture Subsystem</v>
       </c>
       <c r="D221" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6357,10 +6286,10 @@
         <v>PASS</v>
       </c>
       <c r="G221">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="222">
@@ -6371,7 +6300,7 @@
         <v>API-221</v>
       </c>
       <c r="C222" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Measure Architecture Subsystem</v>
       </c>
       <c r="D222" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6383,10 +6312,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="223">
@@ -6397,7 +6326,7 @@
         <v>API-222</v>
       </c>
       <c r="C223" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Fdi Architecture Subsystem</v>
       </c>
       <c r="D223" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6412,7 +6341,7 @@
         <v>21</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="224">
@@ -6423,7 +6352,7 @@
         <v>API-223</v>
       </c>
       <c r="C224" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Universal Architecture Subsystem</v>
       </c>
       <c r="D224" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6435,10 +6364,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="225">
@@ -6449,7 +6378,7 @@
         <v>API-224</v>
       </c>
       <c r="C225" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Rotate Architecture Subsystem</v>
       </c>
       <c r="D225" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6464,7 +6393,7 @@
         <v>18</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="226">
@@ -6475,7 +6404,7 @@
         <v>API-225</v>
       </c>
       <c r="C226" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Crop Architecture Subsystem</v>
       </c>
       <c r="D226" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6487,10 +6416,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="227">
@@ -6501,7 +6430,7 @@
         <v>API-226</v>
       </c>
       <c r="C227" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Put Scan Brightness Architecture Subsystem</v>
       </c>
       <c r="D227" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6513,10 +6442,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="228">
@@ -6527,7 +6456,7 @@
         <v>API-227</v>
       </c>
       <c r="C228" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Negative Architecture Subsystem</v>
       </c>
       <c r="D228" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6539,10 +6468,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="229">
@@ -6553,7 +6482,7 @@
         <v>API-228</v>
       </c>
       <c r="C229" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Magnifying Architecture Subsystem</v>
       </c>
       <c r="D229" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6565,10 +6494,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="230">
@@ -6579,7 +6508,7 @@
         <v>API-229</v>
       </c>
       <c r="C230" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Second Architecture Subsystem</v>
       </c>
       <c r="D230" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6591,10 +6520,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="231">
@@ -6605,7 +6534,7 @@
         <v>API-230</v>
       </c>
       <c r="C231" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Second Architecture Subsystem</v>
       </c>
       <c r="D231" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6617,10 +6546,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="232">
@@ -6631,7 +6560,7 @@
         <v>API-231</v>
       </c>
       <c r="C232" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D232" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6646,7 +6575,7 @@
         <v>27</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="233">
@@ -6657,7 +6586,7 @@
         <v>API-232</v>
       </c>
       <c r="C233" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D233" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6669,10 +6598,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="234">
@@ -6683,7 +6612,7 @@
         <v>API-233</v>
       </c>
       <c r="C234" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Delete Scan Batch Architecture Subsystem</v>
       </c>
       <c r="D234" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6695,10 +6624,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="235">
@@ -6709,7 +6638,7 @@
         <v>API-234</v>
       </c>
       <c r="C235" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Print Architecture Subsystem</v>
       </c>
       <c r="D235" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6721,10 +6650,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.042Z</v>
       </c>
     </row>
     <row r="236">
@@ -6735,7 +6664,7 @@
         <v>API-235</v>
       </c>
       <c r="C236" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Ai Architecture Subsystem</v>
       </c>
       <c r="D236" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6747,10 +6676,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="237">
@@ -6761,7 +6690,7 @@
         <v>API-236</v>
       </c>
       <c r="C237" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Tag Architecture Subsystem</v>
       </c>
       <c r="D237" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6773,10 +6702,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="238">
@@ -6787,7 +6716,7 @@
         <v>API-237</v>
       </c>
       <c r="C238" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scans By Architecture Subsystem</v>
       </c>
       <c r="D238" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6799,10 +6728,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="239">
@@ -6813,7 +6742,7 @@
         <v>API-238</v>
       </c>
       <c r="C239" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scans Date Architecture Subsystem</v>
       </c>
       <c r="D239" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6825,10 +6754,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="240">
@@ -6839,7 +6768,7 @@
         <v>API-239</v>
       </c>
       <c r="C240" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Watermark Architecture Subsystem</v>
       </c>
       <c r="D240" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6851,10 +6780,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="241">
@@ -6865,7 +6794,7 @@
         <v>API-240</v>
       </c>
       <c r="C241" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Exif Architecture Subsystem</v>
       </c>
       <c r="D241" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6877,10 +6806,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="242">
@@ -6891,7 +6820,7 @@
         <v>API-241</v>
       </c>
       <c r="C242" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Strip Architecture Subsystem</v>
       </c>
       <c r="D242" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6903,10 +6832,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="243">
@@ -6917,7 +6846,7 @@
         <v>API-242</v>
       </c>
       <c r="C243" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Thumbnail Architecture Subsystem</v>
       </c>
       <c r="D243" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6929,10 +6858,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="244">
@@ -6943,7 +6872,7 @@
         <v>API-243</v>
       </c>
       <c r="C244" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Color Architecture Subsystem</v>
       </c>
       <c r="D244" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6955,10 +6884,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="245">
@@ -6969,7 +6898,7 @@
         <v>API-244</v>
       </c>
       <c r="C245" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Sharpness Architecture Subsystem</v>
       </c>
       <c r="D245" t="str">
         <v>test_05_dental_scan.py</v>
@@ -6981,10 +6910,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="246">
@@ -6995,7 +6924,7 @@
         <v>API-245</v>
       </c>
       <c r="C246" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Dicom Architecture Subsystem</v>
       </c>
       <c r="D246" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7007,10 +6936,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="247">
@@ -7021,7 +6950,7 @@
         <v>API-246</v>
       </c>
       <c r="C247" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Iou Architecture Subsystem</v>
       </c>
       <c r="D247" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7033,10 +6962,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="248">
@@ -7047,7 +6976,7 @@
         <v>API-247</v>
       </c>
       <c r="C248" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Plaque Architecture Subsystem</v>
       </c>
       <c r="D248" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7059,10 +6988,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="249">
@@ -7073,7 +7002,7 @@
         <v>API-248</v>
       </c>
       <c r="C249" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Get Scan Gingivitis Architecture Subsystem</v>
       </c>
       <c r="D249" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7085,10 +7014,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="250">
@@ -7099,7 +7028,7 @@
         <v>API-249</v>
       </c>
       <c r="C250" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Post Scan Reprocess Architecture Subsystem</v>
       </c>
       <c r="D250" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7111,10 +7040,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="251">
@@ -7125,7 +7054,7 @@
         <v>API-250</v>
       </c>
       <c r="C251" t="str">
-        <v>Dental Vision Scanner</v>
+        <v>Dental Scan Api Architecture Subsystem</v>
       </c>
       <c r="D251" t="str">
         <v>test_05_dental_scan.py</v>
@@ -7137,10 +7066,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T05:04:20.012Z</v>
+        <v>2026-08-06T05:06:56.043Z</v>
       </c>
     </row>
     <row r="252">
@@ -7151,7 +7080,7 @@
         <v>API-251</v>
       </c>
       <c r="C252" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Articles Architecture Subsystem</v>
       </c>
       <c r="D252" t="str">
         <v>test_06_education_export.py</v>
@@ -7163,10 +7092,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="253">
@@ -7177,7 +7106,7 @@
         <v>API-252</v>
       </c>
       <c r="C253" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Articles Architecture Subsystem</v>
       </c>
       <c r="D253" t="str">
         <v>test_06_education_export.py</v>
@@ -7189,10 +7118,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="254">
@@ -7203,7 +7132,7 @@
         <v>API-253</v>
       </c>
       <c r="C254" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Articles Architecture Subsystem</v>
       </c>
       <c r="D254" t="str">
         <v>test_06_education_export.py</v>
@@ -7215,10 +7144,10 @@
         <v>PASS</v>
       </c>
       <c r="G254">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="255">
@@ -7229,7 +7158,7 @@
         <v>API-254</v>
       </c>
       <c r="C255" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Article Architecture Subsystem</v>
       </c>
       <c r="D255" t="str">
         <v>test_06_education_export.py</v>
@@ -7241,10 +7170,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="256">
@@ -7255,7 +7184,7 @@
         <v>API-255</v>
       </c>
       <c r="C256" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Post Education Bookmark Architecture Subsystem</v>
       </c>
       <c r="D256" t="str">
         <v>test_06_education_export.py</v>
@@ -7270,7 +7199,7 @@
         <v>19</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="257">
@@ -7281,7 +7210,7 @@
         <v>API-256</v>
       </c>
       <c r="C257" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Delete Education Bookmark Architecture Subsystem</v>
       </c>
       <c r="D257" t="str">
         <v>test_06_education_export.py</v>
@@ -7293,10 +7222,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="258">
@@ -7307,7 +7236,7 @@
         <v>API-257</v>
       </c>
       <c r="C258" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Bookmarks Architecture Subsystem</v>
       </c>
       <c r="D258" t="str">
         <v>test_06_education_export.py</v>
@@ -7319,10 +7248,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="259">
@@ -7333,7 +7262,7 @@
         <v>API-258</v>
       </c>
       <c r="C259" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Article Architecture Subsystem</v>
       </c>
       <c r="D259" t="str">
         <v>test_06_education_export.py</v>
@@ -7345,10 +7274,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="260">
@@ -7359,7 +7288,7 @@
         <v>API-259</v>
       </c>
       <c r="C260" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Video Architecture Subsystem</v>
       </c>
       <c r="D260" t="str">
         <v>test_06_education_export.py</v>
@@ -7371,10 +7300,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="261">
@@ -7385,7 +7314,7 @@
         <v>API-260</v>
       </c>
       <c r="C261" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Post Education Quiz Architecture Subsystem</v>
       </c>
       <c r="D261" t="str">
         <v>test_06_education_export.py</v>
@@ -7400,7 +7329,7 @@
         <v>15</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="262">
@@ -7411,7 +7340,7 @@
         <v>API-261</v>
       </c>
       <c r="C262" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Daily Architecture Subsystem</v>
       </c>
       <c r="D262" t="str">
         <v>test_06_education_export.py</v>
@@ -7423,10 +7352,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="263">
@@ -7437,7 +7366,7 @@
         <v>API-262</v>
       </c>
       <c r="C263" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Education Infographic Architecture Subsystem</v>
       </c>
       <c r="D263" t="str">
         <v>test_06_education_export.py</v>
@@ -7449,10 +7378,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="264">
@@ -7463,7 +7392,7 @@
         <v>API-263</v>
       </c>
       <c r="C264" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Doctor Architecture Subsystem</v>
       </c>
       <c r="D264" t="str">
         <v>test_06_education_export.py</v>
@@ -7475,10 +7404,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="265">
@@ -7489,7 +7418,7 @@
         <v>API-264</v>
       </c>
       <c r="C265" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Common Architecture Subsystem</v>
       </c>
       <c r="D265" t="str">
         <v>test_06_education_export.py</v>
@@ -7504,7 +7433,7 @@
         <v>12</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="266">
@@ -7515,7 +7444,7 @@
         <v>API-265</v>
       </c>
       <c r="C266" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Cancellation Architecture Subsystem</v>
       </c>
       <c r="D266" t="str">
         <v>test_06_education_export.py</v>
@@ -7527,10 +7456,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="267">
@@ -7541,7 +7470,7 @@
         <v>API-266</v>
       </c>
       <c r="C267" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Doctor Architecture Subsystem</v>
       </c>
       <c r="D267" t="str">
         <v>test_06_education_export.py</v>
@@ -7553,10 +7482,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="268">
@@ -7567,7 +7496,7 @@
         <v>API-267</v>
       </c>
       <c r="C268" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Export Architecture Subsystem</v>
       </c>
       <c r="D268" t="str">
         <v>test_06_education_export.py</v>
@@ -7579,10 +7508,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="269">
@@ -7593,7 +7522,7 @@
         <v>API-268</v>
       </c>
       <c r="C269" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Export Architecture Subsystem</v>
       </c>
       <c r="D269" t="str">
         <v>test_06_education_export.py</v>
@@ -7605,10 +7534,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="270">
@@ -7619,7 +7548,7 @@
         <v>API-269</v>
       </c>
       <c r="C270" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Clinic Architecture Subsystem</v>
       </c>
       <c r="D270" t="str">
         <v>test_06_education_export.py</v>
@@ -7631,10 +7560,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="271">
@@ -7645,7 +7574,7 @@
         <v>API-270</v>
       </c>
       <c r="C271" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Patient Architecture Subsystem</v>
       </c>
       <c r="D271" t="str">
         <v>test_06_education_export.py</v>
@@ -7657,10 +7586,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="272">
@@ -7671,7 +7600,7 @@
         <v>API-271</v>
       </c>
       <c r="C272" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Revenue Architecture Subsystem</v>
       </c>
       <c r="D272" t="str">
         <v>test_06_education_export.py</v>
@@ -7683,10 +7612,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="273">
@@ -7697,7 +7626,7 @@
         <v>API-272</v>
       </c>
       <c r="C273" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Weekly Architecture Subsystem</v>
       </c>
       <c r="D273" t="str">
         <v>test_06_education_export.py</v>
@@ -7709,10 +7638,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="274">
@@ -7723,7 +7652,7 @@
         <v>API-273</v>
       </c>
       <c r="C274" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics Patient Architecture Subsystem</v>
       </c>
       <c r="D274" t="str">
         <v>test_06_education_export.py</v>
@@ -7735,10 +7664,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="275">
@@ -7749,7 +7678,7 @@
         <v>API-274</v>
       </c>
       <c r="C275" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Analytics High Architecture Subsystem</v>
       </c>
       <c r="D275" t="str">
         <v>test_06_education_export.py</v>
@@ -7761,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="276">
@@ -7775,7 +7704,7 @@
         <v>API-275</v>
       </c>
       <c r="C276" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Audit Logs Architecture Subsystem</v>
       </c>
       <c r="D276" t="str">
         <v>test_06_education_export.py</v>
@@ -7787,10 +7716,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="277">
@@ -7801,7 +7730,7 @@
         <v>API-276</v>
       </c>
       <c r="C277" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Audit Logs Architecture Subsystem</v>
       </c>
       <c r="D277" t="str">
         <v>test_06_education_export.py</v>
@@ -7813,10 +7742,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="278">
@@ -7827,7 +7756,7 @@
         <v>API-277</v>
       </c>
       <c r="C278" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Audit Logs Architecture Subsystem</v>
       </c>
       <c r="D278" t="str">
         <v>test_06_education_export.py</v>
@@ -7839,10 +7768,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="279">
@@ -7853,7 +7782,7 @@
         <v>API-278</v>
       </c>
       <c r="C279" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Notifications Unread Architecture Subsystem</v>
       </c>
       <c r="D279" t="str">
         <v>test_06_education_export.py</v>
@@ -7865,10 +7794,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="280">
@@ -7879,7 +7808,7 @@
         <v>API-279</v>
       </c>
       <c r="C280" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Notifications List Architecture Subsystem</v>
       </c>
       <c r="D280" t="str">
         <v>test_06_education_export.py</v>
@@ -7891,10 +7820,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="281">
@@ -7905,7 +7834,7 @@
         <v>API-280</v>
       </c>
       <c r="C281" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Put Notifications Read Architecture Subsystem</v>
       </c>
       <c r="D281" t="str">
         <v>test_06_education_export.py</v>
@@ -7917,10 +7846,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="282">
@@ -7931,7 +7860,7 @@
         <v>API-281</v>
       </c>
       <c r="C282" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Put Notifications Read Architecture Subsystem</v>
       </c>
       <c r="D282" t="str">
         <v>test_06_education_export.py</v>
@@ -7946,7 +7875,7 @@
         <v>24</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="283">
@@ -7957,7 +7886,7 @@
         <v>API-282</v>
       </c>
       <c r="C283" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Put Notification Settings Architecture Subsystem</v>
       </c>
       <c r="D283" t="str">
         <v>test_06_education_export.py</v>
@@ -7969,10 +7898,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="284">
@@ -7983,7 +7912,7 @@
         <v>API-283</v>
       </c>
       <c r="C284" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Notification Settings Architecture Subsystem</v>
       </c>
       <c r="D284" t="str">
         <v>test_06_education_export.py</v>
@@ -7995,10 +7924,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="285">
@@ -8009,7 +7938,7 @@
         <v>API-284</v>
       </c>
       <c r="C285" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Post Notifications Browser Architecture Subsystem</v>
       </c>
       <c r="D285" t="str">
         <v>test_06_education_export.py</v>
@@ -8021,10 +7950,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="286">
@@ -8035,7 +7964,7 @@
         <v>API-285</v>
       </c>
       <c r="C286" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Delete Notifications Browser Architecture Subsystem</v>
       </c>
       <c r="D286" t="str">
         <v>test_06_education_export.py</v>
@@ -8047,10 +7976,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="287">
@@ -8061,7 +7990,7 @@
         <v>API-286</v>
       </c>
       <c r="C287" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get System Health Architecture Subsystem</v>
       </c>
       <c r="D287" t="str">
         <v>test_06_education_export.py</v>
@@ -8073,10 +8002,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="288">
@@ -8087,7 +8016,7 @@
         <v>API-287</v>
       </c>
       <c r="C288" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Post System Feedback Architecture Subsystem</v>
       </c>
       <c r="D288" t="str">
         <v>test_06_education_export.py</v>
@@ -8099,10 +8028,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="289">
@@ -8113,7 +8042,7 @@
         <v>API-288</v>
       </c>
       <c r="C289" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get System Release Architecture Subsystem</v>
       </c>
       <c r="D289" t="str">
         <v>test_06_education_export.py</v>
@@ -8125,10 +8054,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="290">
@@ -8139,7 +8068,7 @@
         <v>API-289</v>
       </c>
       <c r="C290" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get System Privacy Architecture Subsystem</v>
       </c>
       <c r="D290" t="str">
         <v>test_06_education_export.py</v>
@@ -8151,10 +8080,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="291">
@@ -8165,7 +8094,7 @@
         <v>API-290</v>
       </c>
       <c r="C291" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get System Terms Architecture Subsystem</v>
       </c>
       <c r="D291" t="str">
         <v>test_06_education_export.py</v>
@@ -8177,10 +8106,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="292">
@@ -8191,7 +8120,7 @@
         <v>API-291</v>
       </c>
       <c r="C292" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Post Export Full Architecture Subsystem</v>
       </c>
       <c r="D292" t="str">
         <v>test_06_education_export.py</v>
@@ -8203,10 +8132,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T05:04:20.024Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="293">
@@ -8217,7 +8146,7 @@
         <v>API-292</v>
       </c>
       <c r="C293" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Export Job Architecture Subsystem</v>
       </c>
       <c r="D293" t="str">
         <v>test_06_education_export.py</v>
@@ -8229,10 +8158,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="294">
@@ -8243,7 +8172,7 @@
         <v>API-293</v>
       </c>
       <c r="C294" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Export Download Architecture Subsystem</v>
       </c>
       <c r="D294" t="str">
         <v>test_06_education_export.py</v>
@@ -8255,10 +8184,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="295">
@@ -8269,7 +8198,7 @@
         <v>API-294</v>
       </c>
       <c r="C295" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Options Education Cors Architecture Subsystem</v>
       </c>
       <c r="D295" t="str">
         <v>test_06_education_export.py</v>
@@ -8281,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="296">
@@ -8295,7 +8224,7 @@
         <v>API-295</v>
       </c>
       <c r="C296" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Security Csp Architecture Subsystem</v>
       </c>
       <c r="D296" t="str">
         <v>test_06_education_export.py</v>
@@ -8307,10 +8236,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="297">
@@ -8321,7 +8250,7 @@
         <v>API-296</v>
       </c>
       <c r="C297" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Security Hsts Architecture Subsystem</v>
       </c>
       <c r="D297" t="str">
         <v>test_06_education_export.py</v>
@@ -8333,10 +8262,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="298">
@@ -8347,7 +8276,7 @@
         <v>API-297</v>
       </c>
       <c r="C298" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Security Rbac Architecture Subsystem</v>
       </c>
       <c r="D298" t="str">
         <v>test_06_education_export.py</v>
@@ -8359,10 +8288,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="299">
@@ -8373,7 +8302,7 @@
         <v>API-298</v>
       </c>
       <c r="C299" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Security Rbac Architecture Subsystem</v>
       </c>
       <c r="D299" t="str">
         <v>test_06_education_export.py</v>
@@ -8388,7 +8317,7 @@
         <v>22</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="300">
@@ -8399,7 +8328,7 @@
         <v>API-299</v>
       </c>
       <c r="C300" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Get Security Rate Architecture Subsystem</v>
       </c>
       <c r="D300" t="str">
         <v>test_06_education_export.py</v>
@@ -8411,10 +8340,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
     <row r="301">
@@ -8425,7 +8354,7 @@
         <v>API-300</v>
       </c>
       <c r="C301" t="str">
-        <v>Educational Feed &amp; Analytics</v>
+        <v>Education Export Api Architecture Subsystem</v>
       </c>
       <c r="D301" t="str">
         <v>test_06_education_export.py</v>
@@ -8437,10 +8366,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T05:04:20.025Z</v>
+        <v>2026-08-06T05:06:56.054Z</v>
       </c>
     </row>
   </sheetData>
